--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -567,7 +567,7 @@
         <v>45615</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>45252</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44850.83328703704</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44375</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45810.54824074074</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>44406</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>45568.63905092593</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>45099</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44060</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44320</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>45138</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44484</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45218</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45099</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>45616.38605324074</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>44472</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45021</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44789</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>45670</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45138</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45615</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>44280</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>44375</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>44512</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>44713.59363425926</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>44679</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>44320</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>45537.64484953704</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>45698.46697916667</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45250</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>45645</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>45537.64261574074</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>45104.3483912037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45782.5300462963</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>45783.66537037037</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>45475.92849537037</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>45518</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>45614.68287037037</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44949</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>44536</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>45614.68596064814</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>45845.75491898148</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45845.75751157408</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>45516.42667824074</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45471.56265046296</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>45440.3184375</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>45827.53077546296</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>45832.56153935185</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>45575.54934027778</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45281</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>45478.39592592593</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>45645</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>45618.58876157407</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v>44522</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>44151</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>44242</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>44260.30453703704</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>44069</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>44069</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44295.61297453703</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>44123</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>44063</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44104</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44889.5746875</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44126</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44267</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44431.69783564815</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44853.61925925926</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44495.87667824074</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44447.51184027778</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>44228</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44453</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>44445.4953587963</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>44484</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>44126</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>44508</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>44284.70511574074</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44271</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>44176</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44327</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>44167</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44503</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>44462</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>44613</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44386</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>44210</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>44280</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44427.75243055556</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>44145</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>44300</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>44441.66886574074</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>44431.69723379629</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>44332</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>44722.78552083333</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>44721.53951388889</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44862</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>44577.82805555555</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>44171</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>44460</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>44481</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>44754</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44714</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>44627</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>44638</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44790</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>44676</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>44377</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44377.44943287037</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>44053</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>44069</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>44630</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44603</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44862</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>44629</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44063</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>44713.61145833333</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44123</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>44375</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44671</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44706.65927083333</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>44069</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44061.61920138889</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>44224</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>44102</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>44102</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>44113</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>44468.34099537037</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>44085</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>44068</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>44257</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44259</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>44260.31335648148</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>44577.84596064815</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>44671</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>44505.36354166667</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44273</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>44418.58454861111</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44546.67978009259</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44375</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44187</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44326</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>44823.37396990741</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44325</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>44378.55319444444</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>44071</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>44183</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>44073</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>44162</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44076</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>44635.51386574074</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>44522.87423611111</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>44361</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>44126</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>44053.45215277778</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>44357</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>44130</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>44820</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>44085</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>44434.74203703704</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>44693.66775462963</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>44484.56523148148</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>44694.29309027778</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>44305</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>44691</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>44505</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>44490</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>44629</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>44425.40128472223</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>44665</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>44459.57613425926</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44447</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>44432.68241898148</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>44594</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>44889.68100694445</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>44432</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44091</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>44332.74105324074</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>44728</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>44326.7296412037</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44113</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>44487.51556712963</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>44463</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44602</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>44497</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44650.47945601852</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44456</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>44384.56912037037</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>44819</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>44453</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>44479.58512731481</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>44733.71126157408</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>44536</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>44618</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>44420.60616898148</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>44076</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>44860</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>44636.46935185185</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>44389</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44672</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>44451</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>44151</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>44873.47148148148</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>44098</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>44825.99293981482</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>44438.30614583333</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>44114</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>44088</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>44449</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>44622.69101851852</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>44665</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>44777</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>44451.78710648148</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>44875.47543981481</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>44334.60293981482</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>44533</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>44491</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>44088</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>44536</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>44116</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44179</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>44107</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>44088</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>44502.49809027778</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>44502</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>44208</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>44067</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>44055.38027777777</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>44481.34877314815</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>44363</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>44267</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>44268.55900462963</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>44376</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>44491</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15865,7 +15865,7 @@
         <v>44511.39611111111</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>44607.64115740741</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>44608</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>44389</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>44539.31923611111</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>44539</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>44784</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>44490</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>44526</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>44698.62354166667</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>44784.38697916667</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>44389</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>45189.38135416667</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44069</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>45749</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44389</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45766.33309027777</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>45211</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45338</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>45139.64328703703</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>45575.65721064815</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>45575.57104166667</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>44446</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45744.32981481482</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>45471.38995370371</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45738.43714120371</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>45082.31421296296</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>45194</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>44378.46403935185</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>44566</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45057</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>44389</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>44990</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45085</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>45093.48221064815</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>44865.600625</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>45303</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45523.31621527778</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>44865.87770833333</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>45274</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>45667</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45355.70009259259</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>45170</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>45412.54541666667</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45251</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>45736.30940972222</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>45103.53614583334</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>44431</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>45077</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>45077</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>45077</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>45036</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45075.44152777778</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>45744.57673611111</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>45091.39362268519</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>44300</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>45699.65424768518</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>44946.54424768518</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>44319</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>45698</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>45698</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>45698</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45411.42858796296</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>45072.42776620371</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>44301</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>44457</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>44902</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>45611.44960648148</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>45264.38084490741</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45222</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45393.35787037037</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>44564</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20069,7 +20069,7 @@
         <v>45106</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>45043.40300925926</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>45433.58099537037</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45537.64621527777</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45384</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>45548</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>45435.57399305556</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44928</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44425.40297453704</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>45243</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45243.62420138889</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20721,7 +20721,7 @@
         <v>45243</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>44890.46174768519</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>45769.66260416667</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>45554.71863425926</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45252.78021990741</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45604.58837962963</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>45471.52878472222</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>45749</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44927.72487268518</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>45618.59456018519</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45518.71048611111</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>45525.7374537037</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>45532</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>45667</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>45061.52474537037</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>45461.62924768519</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>44809</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>45719.52871527777</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44876.35706018518</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>44276</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>45520.32997685186</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>45520.33112268519</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45344.623125</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>45749.42258101852</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>45600.60071759259</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>45707</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>44866.79668981482</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>45183.48666666666</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>45664</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>44833</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>44484</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>44445</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>45316</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>45520.32887731482</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>44169</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>44424.61709490741</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45454.49679398148</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>45568.64523148148</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>45341.56577546296</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45334</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>44902</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>45177.31795138889</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45751.50498842593</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45516.42043981481</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45273</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45670.69458333333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45099</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>45323</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>45404.55681712963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>45108.7553587963</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>45751.5056712963</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>45530</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45218</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>45702</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>45462</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>44438</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45516.59447916667</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45568.62625</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>45618.58962962963</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>44984</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45111</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>45168.92155092592</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>45103</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>44064</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>45112.67952546296</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>45119.46452546296</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45274</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>45152.34586805556</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45518.71721064814</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>45134.68158564815</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>45107</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>45471.40384259259</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>44410.61837962963</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>45694</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45714.31533564815</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>44389</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>44883</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45103</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>45729.65171296296</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>45439.56605324074</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>45538.34460648148</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>45441.30899305556</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>45441.30998842593</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>44531.3575</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>45005.35967592592</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>45005.47820601852</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>45702</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>45534.54032407407</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25902,7 +25902,7 @@
         <v>45488.42258101852</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45538</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>45487.40550925926</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>45615.69570601852</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>44978</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>45586.55451388889</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26249,7 +26249,7 @@
         <v>45384.43418981481</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26306,7 +26306,7 @@
         <v>45400.6709837963</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26368,7 +26368,7 @@
         <v>45520.3320949074</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>45575.53331018519</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>45575.54489583334</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>45162.5978125</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>45702</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>45279</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>45519.51627314815</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>45519.52232638889</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>45537.42240740741</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>45441.48670138889</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>45618.58622685185</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>44602.45490740741</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>45776.65518518518</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>45107</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>44602.45162037037</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>45373.34383101852</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>45777.41673611111</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>45329</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>45777.43878472222</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45534.54596064815</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>45733.60959490741</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>45777.42628472222</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>45777</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>45538</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>45738.42981481482</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45373.30434027778</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>45005</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45608</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>44988</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45546.68743055555</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>45783.71833333333</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45509.73383101852</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45516.4221412037</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28344,7 +28344,7 @@
         <v>45567.68003472222</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>45460.46358796296</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>45393.3562962963</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45726.33763888889</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>45726.34090277777</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>45571.71736111111</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>45104.34107638889</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44909</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>44544</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44841</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45538.34796296297</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>45218.488125</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44551</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>44480.58034722223</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>45645.3712037037</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>44124</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>45289</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>45280</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>45541.66916666667</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>45519.52319444445</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>44981</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>45786</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29648,7 +29648,7 @@
         <v>45569.3533912037</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>45148</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45253</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>45203.45681712963</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>45141.76530092592</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>45113</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>44908.49152777778</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>45267.69052083333</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45518.71482638889</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>45749</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30228,7 +30228,7 @@
         <v>45749</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>45618</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30347,7 +30347,7 @@
         <v>44574.50425925926</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>45741.64491898148</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30461,7 +30461,7 @@
         <v>45518.71202546296</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>45518.71591435185</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>45653.53664351852</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30632,7 +30632,7 @@
         <v>45593.59681712963</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>44553.35407407407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30746,7 +30746,7 @@
         <v>45643</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30803,7 +30803,7 @@
         <v>45785.4253125</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>45537.665</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45229.66430555555</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>45399.56596064815</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31046,7 +31046,7 @@
         <v>44594.84091435185</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>45537.65305555556</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>45007</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45614.5968287037</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>45618</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>45400.66995370371</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>45140</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>45646.63482638889</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31517,7 +31517,7 @@
         <v>45687</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>45574.65189814815</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45788.42467592593</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>45546.28121527778</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>45170.45921296296</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>45201</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
         <v>45565</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>45343.58587962963</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>44888.4577662037</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32045,7 +32045,7 @@
         <v>45487.39873842592</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32102,7 +32102,7 @@
         <v>45562.61158564815</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>45565.40700231482</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>45404.68190972223</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>45553</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>44974.55693287037</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>45559</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>45791.50862268519</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>45219</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32578,7 +32578,7 @@
         <v>44949</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>45330</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>45181</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45586</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45639.30934027778</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>44943.73792824074</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>45729.76231481481</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>45575.55273148148</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>45575.5547337963</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33111,7 +33111,7 @@
         <v>45575.55684027778</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>45575.56686342593</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>45575.56820601852</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>45418.66800925926</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>44979</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33411,7 +33411,7 @@
         <v>45177.33091435185</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45440.5433912037</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45667</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>45793.61047453704</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>44522</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45796.44885416667</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>45201</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>45201.60283564815</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>44621.85737268518</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>45796</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>45835.68443287037</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>45054</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>45795.70912037037</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>45218</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>45796</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>45796.45054398148</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>45794.33498842592</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34430,7 +34430,7 @@
         <v>45838.46408564815</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>45229.66262731481</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>45744.57851851852</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>45794.3419212963</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>45194</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>45795.71300925926</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34787,7 +34787,7 @@
         <v>44740.66997685185</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>44441.70047453704</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34901,7 +34901,7 @@
         <v>45394.51289351852</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34958,7 +34958,7 @@
         <v>45554.7158912037</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>45582.57542824074</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>45769.98449074074</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>45795.71547453704</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>45244</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35253,7 +35253,7 @@
         <v>45838.46456018519</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>45387.24732638889</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35372,7 +35372,7 @@
         <v>45387.2521875</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35429,7 +35429,7 @@
         <v>45456.48927083334</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35486,7 +35486,7 @@
         <v>45411.65641203704</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>44236</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>45793.62422453704</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>45131</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>45310</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>45377.48265046296</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>45548</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>45548</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>44683</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>45729.60775462963</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>45569.35209490741</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>45667</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>45610</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>44378.46857638889</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45840</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45173</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>44445.55690972223</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>45095</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45095</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45251.696875</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45737.3846412037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>44963.37709490741</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45590.37590277778</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>45642</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>45434.65854166666</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36956,7 +36956,7 @@
         <v>45168.94197916667</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>45618</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>45155.5653125</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>45372.40246527778</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>45456.90869212963</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>44735.62539351852</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45645.3737962963</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>45077</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45266.58394675926</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>45628.59233796296</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>44967.60165509259</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37603,7 +37603,7 @@
         <v>45203.510625</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>45188</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>44267</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>44970.51849537037</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37831,7 +37831,7 @@
         <v>45348</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>45099.27354166667</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37950,7 +37950,7 @@
         <v>45580.73525462963</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>45845.75200231482</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38069,7 +38069,7 @@
         <v>45804.45474537037</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>45844.57328703703</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>45844.57527777777</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>45635.69581018519</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>45803.39776620371</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>45845.49216435185</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>44577.83484953704</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>45803</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38540,7 +38540,7 @@
         <v>45845.4855787037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38597,7 +38597,7 @@
         <v>44675</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>45804.45584490741</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>44950</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>45594.63747685185</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>45125.41458333333</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>45845.76005787037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45804.67795138889</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45061.53414351852</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>44822</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45844.5775</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39177,7 +39177,7 @@
         <v>45097.39893518519</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45173.39315972223</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45628.58975694444</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45344.6027662037</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45393.36060185185</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>45177.33991898148</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>45034.5174537037</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>45685</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45194</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>44231</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>44420</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>45523.58565972222</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>45645</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>45009.64217592592</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>44503</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40047,7 +40047,7 @@
         <v>44258</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>45145</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>45159.44525462963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40223,7 +40223,7 @@
         <v>45707</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>45516.42424768519</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>45516.42789351852</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>45488.41480324074</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>45078.82620370371</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>45265.64142361111</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40575,7 +40575,7 @@
         <v>45538.34193287037</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40637,7 +40637,7 @@
         <v>45511.39445601852</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>45511.40297453704</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>45646</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>44951.5830324074</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>45642.66184027777</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>45158.41768518519</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>44425</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>45194</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41103,7 +41103,7 @@
         <v>44342.39703703704</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>44791</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>45139.63480324074</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>45812.57452546297</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>45812.57604166667</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>45812.57143518519</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>45812.56952546296</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>45854</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>44161</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>45635.63706018519</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>45233.42121527778</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41770,7 +41770,7 @@
         <v>45749.47251157407</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>45305</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>45229</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45813.68209490741</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45755.68247685185</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>44665</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45149</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42231,7 +42231,7 @@
         <v>45736</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42288,7 +42288,7 @@
         <v>45646.63839120371</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45756.49009259259</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45328</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42464,7 +42464,7 @@
         <v>45860.3857175926</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>45227.31859953704</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42578,7 +42578,7 @@
         <v>45357.34521990741</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42640,7 +42640,7 @@
         <v>45694</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>45769.98603009259</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>45170</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>45254.68105324074</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>45072</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42940,7 +42940,7 @@
         <v>45817.6455324074</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45768.49947916667</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45440</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45860.36222222223</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45854</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>44753</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45820.61684027778</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43339,7 +43339,7 @@
         <v>44546.6679050926</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45138</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>45369</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43515,7 +43515,7 @@
         <v>45113</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43572,7 +43572,7 @@
         <v>44389</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>45310.87931712963</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43686,7 +43686,7 @@
         <v>44990</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43743,7 +43743,7 @@
         <v>45477.70315972222</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43800,7 +43800,7 @@
         <v>45821.37199074074</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45821.44521990741</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>45821.46486111111</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43986,7 +43986,7 @@
         <v>45821.46135416667</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44048,7 +44048,7 @@
         <v>45274</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44105,7 +44105,7 @@
         <v>44970</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>45729.65061342593</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>45530</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>44803.64361111111</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45821.59353009259</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44395,7 +44395,7 @@
         <v>45714</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>45030</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45265.49225694445</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>45685</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>45272.57385416667</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45691.36253472222</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>45826.52024305556</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>45749</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>45194</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44918,7 +44918,7 @@
         <v>45827.51862268519</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44980,7 +44980,7 @@
         <v>45827.51753472222</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45042,7 +45042,7 @@
         <v>45827.51956018519</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45827.56939814815</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45827.51628472222</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45832.74418981482</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>44355</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>44900.36149305556</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45409,7 +45409,7 @@
         <v>45079</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>45079</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45523</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45590,7 +45590,7 @@
         <v>45832.51028935185</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>45272.36168981482</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>45736.308125</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45766,7 +45766,7 @@
         <v>44511</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45870</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45880,7 +45880,7 @@
         <v>45832.55810185185</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>45684.5790162037</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>45831</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>45831</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46113,7 +46113,7 @@
         <v>45832.49325231482</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>45832.51255787037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45574.65087962963</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>45571.72288194444</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46361,7 +46361,7 @@
         <v>45832.49579861111</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>45832.5902662037</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45874.40503472222</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45832.72778935185</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>45587</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45471.52072916667</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>45257.48188657407</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45832.76491898148</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46842,7 +46842,7 @@
         <v>45097.38688657407</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45876.59166666667</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>45832.76100694444</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47018,7 +47018,7 @@
         <v>45769.17</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47075,7 +47075,7 @@
         <v>45575.55570601852</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>44546.67222222222</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>45229</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45048</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47308,7 +47308,7 @@
         <v>45047.7181712963</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47365,7 +47365,7 @@
         <v>45471.42659722222</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47422,7 +47422,7 @@
         <v>45547.36590277778</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>44175</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>44227</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47593,7 +47593,7 @@
         <v>44473.6343287037</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47650,7 +47650,7 @@
         <v>44371.47609953704</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>44449</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47764,7 +47764,7 @@
         <v>45008</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>44895</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47883,7 +47883,7 @@
         <v>44916</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47940,7 +47940,7 @@
         <v>44979</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47997,7 +47997,7 @@
         <v>45575.53690972222</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48059,7 +48059,7 @@
         <v>45575.56256944445</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48121,7 +48121,7 @@
         <v>45166.68493055556</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48183,7 +48183,7 @@
         <v>44259</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48240,7 +48240,7 @@
         <v>45404.55239583334</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>45404.55601851852</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>44902</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>45107</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48478,7 +48478,7 @@
         <v>45189</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>44306.6371412037</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48592,7 +48592,7 @@
         <v>44308</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>44853.79818287037</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48711,7 +48711,7 @@
         <v>45497</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>44906.73321759259</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>44083</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48887,7 +48887,7 @@
         <v>45237.67819444444</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48944,7 +48944,7 @@
         <v>45614.68083333333</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49001,7 +49001,7 @@
         <v>45474.65005787037</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49063,7 +49063,7 @@
         <v>45068</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49120,7 +49120,7 @@
         <v>45610.7466087963</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49177,7 +49177,7 @@
         <v>44577.81121527778</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49234,7 +49234,7 @@
         <v>45628.94579861111</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49291,7 +49291,7 @@
         <v>45618.59219907408</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45211</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>44721.52627314815</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49472,7 +49472,7 @@
         <v>45119</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45583</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>45453.36664351852</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49658,7 +49658,7 @@
         <v>44734.64337962963</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49715,7 +49715,7 @@
         <v>44946</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49772,7 +49772,7 @@
         <v>44958.58982638889</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49829,7 +49829,7 @@
         <v>44978</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49886,7 +49886,7 @@
         <v>45546.46497685185</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49948,7 +49948,7 @@
         <v>44846</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50005,7 +50005,7 @@
         <v>45376.70292824074</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>45327</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45590.39471064815</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45254</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50243,7 +50243,7 @@
         <v>45762.61817129629</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>45074</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
         <v>44431</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50414,7 +50414,7 @@
         <v>44868.36924768519</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -567,7 +567,7 @@
         <v>45615</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>45252</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44850.83328703704</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44375</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45810.54824074074</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>44406</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>45568.63905092593</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>45099</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>44060</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44320</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>45138</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44484</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45218</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45099</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>45616.38605324074</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>44472</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45021</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44789</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>45670</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45138</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45615</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>44280</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>44375</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>44512</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>44713.59363425926</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>44679</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>44320</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>45537.64484953704</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>45698.46697916667</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45250</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>45645</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>45537.64261574074</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>45104.3483912037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45782.5300462963</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>45783.66537037037</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>45475.92849537037</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>45518</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>45614.68287037037</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44949</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>44536</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>45614.68596064814</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>45845.75491898148</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45845.75751157408</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>45516.42667824074</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45471.56265046296</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>45440.3184375</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>45827.53077546296</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>45832.56153935185</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>45575.54934027778</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45281</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>45478.39592592593</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>45645</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>45618.58876157407</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v>44522</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>44151</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>44242</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>44260.30453703704</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>44069</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>44069</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44295.61297453703</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>44123</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>44063</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44104</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44889.5746875</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44126</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44267</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44431.69783564815</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44853.61925925926</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44495.87667824074</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44447.51184027778</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>44228</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44453</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>44445.4953587963</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>44484</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>44126</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>44508</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>44284.70511574074</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44271</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>44176</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44327</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>44167</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44503</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>44462</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>44613</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44386</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>44210</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>44280</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44427.75243055556</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>44145</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>44300</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>44441.66886574074</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>44431.69723379629</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>44332</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>44722.78552083333</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>44721.53951388889</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44862</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>44577.82805555555</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>44171</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>44460</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>44481</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>44754</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44714</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>44627</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>44638</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44790</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>44676</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>44377</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44377.44943287037</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>44053</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>44069</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>44630</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44603</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44862</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>44629</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44063</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>44713.61145833333</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44123</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>44375</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44671</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44706.65927083333</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>44069</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44061.61920138889</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>44224</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>44102</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>44102</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>44113</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>44468.34099537037</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>44085</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>44068</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>44257</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44259</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>44260.31335648148</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>44577.84596064815</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>44671</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>44505.36354166667</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44273</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>44418.58454861111</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44546.67978009259</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44375</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44187</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44326</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>44823.37396990741</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44325</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>44378.55319444444</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>44071</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>44183</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>44073</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>44162</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44076</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>44635.51386574074</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>44522.87423611111</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>44361</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>44126</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>44053.45215277778</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>44357</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>44130</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>44820</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>44085</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>44434.74203703704</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>44693.66775462963</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>44484.56523148148</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>44694.29309027778</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>44305</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>44691</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>44505</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>44490</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>44629</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>44425.40128472223</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>44665</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>44459.57613425926</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44447</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>44432.68241898148</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>44594</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>44889.68100694445</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>44432</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44091</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>44332.74105324074</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>44728</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>44326.7296412037</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44113</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>44487.51556712963</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>44463</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44602</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>44497</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44650.47945601852</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44456</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>44384.56912037037</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>44819</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>44453</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>44479.58512731481</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>44733.71126157408</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>44536</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>44618</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>44420.60616898148</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>44076</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>44860</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>44636.46935185185</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>44389</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44672</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>44451</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>44151</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>44873.47148148148</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>44098</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>44825.99293981482</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>44438.30614583333</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>44114</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>44088</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>44449</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>44622.69101851852</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>44665</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>44777</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>44451.78710648148</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>44875.47543981481</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>44334.60293981482</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>44533</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>44491</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>44088</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>44536</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>44116</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44179</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>44107</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>44088</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>44502.49809027778</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>44502</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>44208</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>44067</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>44055.38027777777</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>44481.34877314815</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>44363</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>44267</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>44268.55900462963</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>44376</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>44491</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15865,7 +15865,7 @@
         <v>44511.39611111111</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>44607.64115740741</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>44608</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>44389</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>44539.31923611111</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>44539</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>44784</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>44490</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>44526</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>44698.62354166667</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>44784.38697916667</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>44389</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>45189.38135416667</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44069</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>45749</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44389</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45766.33309027777</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>45211</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45338</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>45139.64328703703</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>45575.65721064815</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>45575.57104166667</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>44446</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45744.32981481482</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>45471.38995370371</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45738.43714120371</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>45082.31421296296</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>45194</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>44378.46403935185</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>44566</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45057</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>44389</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>44990</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45085</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>45093.48221064815</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>44865.600625</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>45303</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45523.31621527778</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>44865.87770833333</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>45274</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>45667</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45355.70009259259</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>45170</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>45412.54541666667</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45251</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>45736.30940972222</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>45103.53614583334</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>44431</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>45077</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>45077</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>45077</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>45036</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45075.44152777778</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>45744.57673611111</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>45091.39362268519</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>44300</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>45699.65424768518</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>44946.54424768518</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>44319</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>45698</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>45698</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>45698</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45411.42858796296</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>45072.42776620371</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>44301</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>44457</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>44902</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>45611.44960648148</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>45264.38084490741</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45222</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45393.35787037037</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>44564</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20069,7 +20069,7 @@
         <v>45106</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>45043.40300925926</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>45433.58099537037</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45537.64621527777</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45384</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>45548</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>45435.57399305556</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44928</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44425.40297453704</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>45243</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45243.62420138889</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20721,7 +20721,7 @@
         <v>45243</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>44890.46174768519</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>45769.66260416667</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>45554.71863425926</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45252.78021990741</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45604.58837962963</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>45471.52878472222</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>45749</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44927.72487268518</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>45618.59456018519</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45518.71048611111</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>45525.7374537037</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>45532</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>45667</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>45061.52474537037</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>45461.62924768519</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>44809</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>45719.52871527777</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44876.35706018518</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>44276</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>45520.32997685186</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>45520.33112268519</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45344.623125</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>45749.42258101852</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>45600.60071759259</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>45707</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>44866.79668981482</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>45183.48666666666</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>45664</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>44833</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>44484</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>44445</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>45316</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>45520.32887731482</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>44169</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>44424.61709490741</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45454.49679398148</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>45568.64523148148</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>45341.56577546296</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45334</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>44902</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>45177.31795138889</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45751.50498842593</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45516.42043981481</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45273</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45670.69458333333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45099</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>45323</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>45404.55681712963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>45108.7553587963</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>45751.5056712963</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>45530</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45218</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>45702</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>45462</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>44438</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45516.59447916667</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45568.62625</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>45618.58962962963</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>44984</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45111</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>45168.92155092592</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>45103</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>44064</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>45112.67952546296</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>45119.46452546296</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45274</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>45152.34586805556</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45518.71721064814</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>45134.68158564815</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>45107</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>45471.40384259259</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>44410.61837962963</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>45694</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45714.31533564815</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>44389</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>44883</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45103</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>45729.65171296296</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>45439.56605324074</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>45538.34460648148</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>45441.30899305556</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>45441.30998842593</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>44531.3575</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>45005.35967592592</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>45005.47820601852</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>45702</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>45534.54032407407</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25902,7 +25902,7 @@
         <v>45488.42258101852</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45538</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>45487.40550925926</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>45615.69570601852</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>44978</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>45586.55451388889</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26249,7 +26249,7 @@
         <v>45384.43418981481</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26306,7 +26306,7 @@
         <v>45400.6709837963</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26368,7 +26368,7 @@
         <v>45520.3320949074</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>45575.53331018519</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>45575.54489583334</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>45162.5978125</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>45702</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>45279</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>45519.51627314815</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>45519.52232638889</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>45537.42240740741</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>45441.48670138889</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>45618.58622685185</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>44602.45490740741</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>45776.65518518518</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>45107</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>44602.45162037037</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>45373.34383101852</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>45777.41673611111</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>45329</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>45777.43878472222</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45534.54596064815</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>45733.60959490741</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>45777.42628472222</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>45777</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>45538</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>45738.42981481482</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45373.30434027778</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>45005</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45608</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>44988</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45546.68743055555</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>45783.71833333333</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45509.73383101852</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45516.4221412037</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28344,7 +28344,7 @@
         <v>45567.68003472222</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>45460.46358796296</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>45393.3562962963</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45726.33763888889</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>45726.34090277777</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>45571.71736111111</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>45104.34107638889</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44909</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>44544</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44841</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45538.34796296297</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>45218.488125</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44551</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>44480.58034722223</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>45645.3712037037</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>44124</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>45289</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>45280</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>45541.66916666667</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>45519.52319444445</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>44981</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>45786</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29648,7 +29648,7 @@
         <v>45569.3533912037</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>45148</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45253</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>45203.45681712963</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>45141.76530092592</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>45113</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>44908.49152777778</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>45267.69052083333</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45518.71482638889</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>45749</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30228,7 +30228,7 @@
         <v>45749</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>45618</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30347,7 +30347,7 @@
         <v>44574.50425925926</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>45741.64491898148</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30461,7 +30461,7 @@
         <v>45518.71202546296</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>45518.71591435185</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>45653.53664351852</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30632,7 +30632,7 @@
         <v>45593.59681712963</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>44553.35407407407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30746,7 +30746,7 @@
         <v>45643</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30803,7 +30803,7 @@
         <v>45785.4253125</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>45537.665</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45229.66430555555</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>45399.56596064815</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31046,7 +31046,7 @@
         <v>44594.84091435185</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>45537.65305555556</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>45007</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45614.5968287037</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>45618</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>45400.66995370371</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>45140</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>45646.63482638889</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31517,7 +31517,7 @@
         <v>45687</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>45574.65189814815</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45788.42467592593</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>45546.28121527778</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>45170.45921296296</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>45201</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
         <v>45565</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>45343.58587962963</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>44888.4577662037</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32045,7 +32045,7 @@
         <v>45487.39873842592</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32102,7 +32102,7 @@
         <v>45562.61158564815</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>45565.40700231482</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>45404.68190972223</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>45553</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>44974.55693287037</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>45559</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>45791.50862268519</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>45219</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32578,7 +32578,7 @@
         <v>44949</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>45330</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>45181</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45586</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45639.30934027778</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>44943.73792824074</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>45729.76231481481</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>45575.55273148148</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>45575.5547337963</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33111,7 +33111,7 @@
         <v>45575.55684027778</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>45575.56686342593</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>45575.56820601852</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>45418.66800925926</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>44979</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33411,7 +33411,7 @@
         <v>45177.33091435185</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45440.5433912037</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45667</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>45793.61047453704</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>44522</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45796.44885416667</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>45201</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>45201.60283564815</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>44621.85737268518</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>45796</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>45835.68443287037</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>45054</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>45795.70912037037</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>45218</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>45796</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>45796.45054398148</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>45794.33498842592</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34430,7 +34430,7 @@
         <v>45838.46408564815</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>45229.66262731481</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>45744.57851851852</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>45794.3419212963</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>45194</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>45795.71300925926</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34787,7 +34787,7 @@
         <v>44740.66997685185</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>44441.70047453704</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34901,7 +34901,7 @@
         <v>45394.51289351852</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34958,7 +34958,7 @@
         <v>45554.7158912037</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>45582.57542824074</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>45769.98449074074</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>45795.71547453704</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>45244</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35253,7 +35253,7 @@
         <v>45838.46456018519</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>45387.24732638889</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35372,7 +35372,7 @@
         <v>45387.2521875</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35429,7 +35429,7 @@
         <v>45456.48927083334</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35486,7 +35486,7 @@
         <v>45411.65641203704</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>44236</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>45793.62422453704</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>45131</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>45310</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>45377.48265046296</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>45548</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>45548</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>44683</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>45729.60775462963</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>45569.35209490741</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>45667</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>45610</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>44378.46857638889</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45840</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45173</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>44445.55690972223</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>45095</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45095</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45251.696875</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45737.3846412037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>44963.37709490741</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45590.37590277778</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>45642</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>45434.65854166666</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36956,7 +36956,7 @@
         <v>45168.94197916667</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>45618</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>45155.5653125</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>45372.40246527778</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>45456.90869212963</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>44735.62539351852</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45645.3737962963</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>45077</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45266.58394675926</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>45628.59233796296</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>44967.60165509259</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37603,7 +37603,7 @@
         <v>45203.510625</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>45188</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>44267</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>44970.51849537037</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37831,7 +37831,7 @@
         <v>45348</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>45099.27354166667</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37950,7 +37950,7 @@
         <v>45580.73525462963</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>45845.75200231482</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38069,7 +38069,7 @@
         <v>45804.45474537037</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>45844.57328703703</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>45844.57527777777</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>45635.69581018519</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>45803.39776620371</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>45845.49216435185</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>44577.83484953704</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>45803</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38540,7 +38540,7 @@
         <v>45845.4855787037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38597,7 +38597,7 @@
         <v>44675</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>45804.45584490741</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>44950</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>45594.63747685185</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>45125.41458333333</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>45845.76005787037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45804.67795138889</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45061.53414351852</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>44822</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45844.5775</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39177,7 +39177,7 @@
         <v>45097.39893518519</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45173.39315972223</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45628.58975694444</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45344.6027662037</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45393.36060185185</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>45177.33991898148</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>45034.5174537037</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>45685</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45194</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>44231</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>44420</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>45523.58565972222</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>45645</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>45009.64217592592</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>44503</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40047,7 +40047,7 @@
         <v>44258</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>45145</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>45159.44525462963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40223,7 +40223,7 @@
         <v>45707</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>45516.42424768519</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>45516.42789351852</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>45488.41480324074</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>45078.82620370371</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>45265.64142361111</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40575,7 +40575,7 @@
         <v>45538.34193287037</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40637,7 +40637,7 @@
         <v>45511.39445601852</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>45511.40297453704</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>45646</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>44951.5830324074</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>45642.66184027777</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>45158.41768518519</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>44425</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>45194</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41103,7 +41103,7 @@
         <v>44342.39703703704</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>44791</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>45139.63480324074</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>45812.57452546297</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>45812.57604166667</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>45812.57143518519</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>45812.56952546296</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>45854</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>44161</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>45635.63706018519</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>45233.42121527778</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41770,7 +41770,7 @@
         <v>45749.47251157407</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>45305</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>45229</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45813.68209490741</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45755.68247685185</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>44665</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45149</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42231,7 +42231,7 @@
         <v>45736</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42288,7 +42288,7 @@
         <v>45646.63839120371</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45756.49009259259</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45328</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42464,7 +42464,7 @@
         <v>45860.3857175926</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>45227.31859953704</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42578,7 +42578,7 @@
         <v>45357.34521990741</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42640,7 +42640,7 @@
         <v>45694</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>45769.98603009259</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>45170</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>45254.68105324074</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>45072</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42940,7 +42940,7 @@
         <v>45817.6455324074</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45768.49947916667</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45440</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45860.36222222223</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45854</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>44753</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45820.61684027778</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43339,7 +43339,7 @@
         <v>44546.6679050926</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45138</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>45369</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43515,7 +43515,7 @@
         <v>45113</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43572,7 +43572,7 @@
         <v>44389</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>45310.87931712963</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43686,7 +43686,7 @@
         <v>44990</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43743,7 +43743,7 @@
         <v>45477.70315972222</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43800,7 +43800,7 @@
         <v>45821.37199074074</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45821.44521990741</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>45821.46486111111</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43986,7 +43986,7 @@
         <v>45821.46135416667</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44048,7 +44048,7 @@
         <v>45274</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44105,7 +44105,7 @@
         <v>44970</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>45729.65061342593</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>45530</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>44803.64361111111</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45821.59353009259</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44395,7 +44395,7 @@
         <v>45714</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>45030</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45265.49225694445</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>45685</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>45272.57385416667</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45691.36253472222</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>45826.52024305556</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>45749</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>45194</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44918,7 +44918,7 @@
         <v>45827.51862268519</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44980,7 +44980,7 @@
         <v>45827.51753472222</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45042,7 +45042,7 @@
         <v>45827.51956018519</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45827.56939814815</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45827.51628472222</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45832.74418981482</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>44355</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>44900.36149305556</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45409,7 +45409,7 @@
         <v>45079</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>45079</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45523</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45590,7 +45590,7 @@
         <v>45832.51028935185</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>45272.36168981482</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>45736.308125</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45766,7 +45766,7 @@
         <v>44511</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45870</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45880,7 +45880,7 @@
         <v>45832.55810185185</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>45684.5790162037</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>45831</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>45831</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46113,7 +46113,7 @@
         <v>45832.49325231482</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>45832.51255787037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45574.65087962963</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>45571.72288194444</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46361,7 +46361,7 @@
         <v>45832.49579861111</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>45832.5902662037</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45874.40503472222</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45832.72778935185</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>45587</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45471.52072916667</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>45257.48188657407</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45832.76491898148</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46842,7 +46842,7 @@
         <v>45097.38688657407</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45876.59166666667</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>45832.76100694444</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47018,7 +47018,7 @@
         <v>45769.17</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47075,7 +47075,7 @@
         <v>45575.55570601852</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>44546.67222222222</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>45229</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45048</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47308,7 +47308,7 @@
         <v>45047.7181712963</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47365,7 +47365,7 @@
         <v>45471.42659722222</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47422,7 +47422,7 @@
         <v>45547.36590277778</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>44175</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>44227</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47593,7 +47593,7 @@
         <v>44473.6343287037</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47650,7 +47650,7 @@
         <v>44371.47609953704</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>44449</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47764,7 +47764,7 @@
         <v>45008</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>44895</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47883,7 +47883,7 @@
         <v>44916</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47940,7 +47940,7 @@
         <v>44979</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47997,7 +47997,7 @@
         <v>45575.53690972222</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48059,7 +48059,7 @@
         <v>45575.56256944445</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48121,7 +48121,7 @@
         <v>45166.68493055556</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48183,7 +48183,7 @@
         <v>44259</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48240,7 +48240,7 @@
         <v>45404.55239583334</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>45404.55601851852</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>44902</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>45107</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48478,7 +48478,7 @@
         <v>45189</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>44306.6371412037</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48592,7 +48592,7 @@
         <v>44308</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>44853.79818287037</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48711,7 +48711,7 @@
         <v>45497</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>44906.73321759259</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>44083</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48887,7 +48887,7 @@
         <v>45237.67819444444</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48944,7 +48944,7 @@
         <v>45614.68083333333</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49001,7 +49001,7 @@
         <v>45474.65005787037</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49063,7 +49063,7 @@
         <v>45068</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49120,7 +49120,7 @@
         <v>45610.7466087963</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49177,7 +49177,7 @@
         <v>44577.81121527778</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49234,7 +49234,7 @@
         <v>45628.94579861111</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49291,7 +49291,7 @@
         <v>45618.59219907408</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45211</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>44721.52627314815</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49472,7 +49472,7 @@
         <v>45119</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45583</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>45453.36664351852</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49658,7 +49658,7 @@
         <v>44734.64337962963</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49715,7 +49715,7 @@
         <v>44946</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49772,7 +49772,7 @@
         <v>44958.58982638889</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49829,7 +49829,7 @@
         <v>44978</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49886,7 +49886,7 @@
         <v>45546.46497685185</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49948,7 +49948,7 @@
         <v>44846</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50005,7 +50005,7 @@
         <v>45376.70292824074</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>45327</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45590.39471064815</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45254</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50243,7 +50243,7 @@
         <v>45762.61817129629</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>45074</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
         <v>44431</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50414,7 +50414,7 @@
         <v>44868.36924768519</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -567,7 +567,7 @@
         <v>45615</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         <v>45252</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44850.83328703704</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>44375</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45810.54824074074</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>44406</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>45568.63905092593</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>45099</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>44060</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>44320</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>45138</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44484</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45218</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>45099</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45616.38605324074</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>44472</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>44789</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45615</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>44280</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45021</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>45138</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>45670</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>44375</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>44512</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>44713.59363425926</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>44679</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>44320</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45698.46697916667</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>45250</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45782.5300462963</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45104.3483912037</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>45783.66537037037</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45475.92849537037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>45614.68287037037</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>44536</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>45845.75491898148</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>45845.75751157408</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45614.68596064814</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>45537.64261574074</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>45518</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>45827.53077546296</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45440.3184375</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>45832.56153935185</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>44949</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>45575.54934027778</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>45281</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>45478.39592592593</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>45516.42667824074</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>45645</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>45618.58876157407</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>45471.56265046296</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>44522</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>45537.64484953704</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>45645</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>44151</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>44242</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>44260.30453703704</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>44069</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44069</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>44295.61297453703</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>44063</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44123</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44104</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44889.5746875</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44126</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>44267</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44431.69783564815</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44853.61925925926</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44495.87667824074</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44453</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>44447.51184027778</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>44228</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>44445.4953587963</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44484</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44126</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44508</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44284.70511574074</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>44271</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>44327</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44176</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44167</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>44503</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>44462</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>44613</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44386</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>44210</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44280</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>44145</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44427.75243055556</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44300</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44441.66886574074</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>44431.69723379629</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44332</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>44721.53951388889</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44722.78552083333</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>44577.82805555555</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>44862</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>44171</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44460</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>44790</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44481</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>44676</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44754</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44714</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>44627</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44638</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>44377</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>44377.44943287037</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>44069</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>44630</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>44603</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>44862</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>44629</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44063</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>44713.61145833333</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>44123</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>44671</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>44375</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>44706.65927083333</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>44069</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44224</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>44260.31335648148</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44061.61920138889</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>44068</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>44102</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>44113</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>44468.34099537037</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>44102</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>44085</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>44257</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>44259</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>44577.84596064815</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>44505.36354166667</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>44418.58454861111</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>44671</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>44273</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>44375</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>44546.67978009259</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>44187</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>44326</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44823.37396990741</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>44325</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>44378.55319444444</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>44071</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>44073</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>44183</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44076</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44162</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>44522.87423611111</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44635.51386574074</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>44126</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>44130</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>44357</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>44820</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>44085</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>44434.74203703704</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>44693.66775462963</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>44484.56523148148</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>44691</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>44305</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>44694.29309027778</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>44505</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44490</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44629</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44425.40128472223</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>44665</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>44459.57613425926</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>44447</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>44432.68241898148</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>44594</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>44432</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>44326.7296412037</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44487.51556712963</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>44463</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>44497</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44650.47945601852</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>44456</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>44819</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>44384.56912037037</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         <v>44733.71126157408</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>44479.58512731481</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>44453</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>44076</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44618</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>44536</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>44420.60616898148</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>44860</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>44636.46935185185</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>44389</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>44672</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>44151</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>44451</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>44098</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>44825.99293981482</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>44873.47148148148</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>44438.30614583333</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>44114</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>44088</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>44449</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>44665</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13981,7 +13981,7 @@
         <v>44622.69101851852</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>44777</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>44451.78710648148</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>44875.47543981481</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>44334.60293981482</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>44533</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>44491</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>44088</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>44536</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>44116</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>44179</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>44107</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>44502.49809027778</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>44502</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
         <v>44088</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>44208</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>44067</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>44481.34877314815</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>44268.55900462963</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>44491</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>44267</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>44376</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>44363</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>44511.39611111111</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>44607.64115740741</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44608</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>44526</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>44784</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>44389</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44539.31923611111</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44539</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44389</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44091</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44490</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44698.62354166667</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>44784.38697916667</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         <v>44332.74105324074</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>44446</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>44728</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>44889.68100694445</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44113</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>44069</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>44389</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>45355.70009259259</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16514,7 +16514,7 @@
         <v>45338</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>45412.54541666667</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>45168.92155092592</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>44602</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>45103</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>44064</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>45091.39362268519</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>45119.46452546296</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>44300</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45194</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>44378.46403935185</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>44319</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>45698</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>45698</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>45698</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>45103</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>45107</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45729.65171296296</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45694</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>44301</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>45439.56605324074</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
         <v>45222</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>45433.58099537037</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45384</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>45435.57399305556</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45702</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45534.54032407407</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>45538</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>45243</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>45243.62420138889</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>45243</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>45615.69570601852</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>44890.46174768519</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45384.43418981481</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45400.6709837963</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>45520.3320949074</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>44531.3575</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>45554.71863425926</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>45471.52878472222</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>45702</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45518.71048611111</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45776.65518518518</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>45274</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>45575.53331018519</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>45575.54489583334</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45777.41673611111</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45777.43878472222</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45733.60959490741</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45777.42628472222</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>45162.5978125</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45777</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>45279</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45519.51627314815</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45519.52232638889</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45537.42240740741</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45107</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>45061.52474537037</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45373.30434027778</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>45783.71833333333</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>45005</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>45509.73383101852</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45608</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45546.68743055555</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45567.68003472222</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>45460.46358796296</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45104.34107638889</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>44551</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>44480.58034722223</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>45786</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45289</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44981</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>45569.3533912037</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>45253</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>45203.45681712963</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>45148</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45267.69052083333</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45141.76530092592</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45113</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45785.4253125</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45537.665</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45229.66430555555</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>45537.65305555556</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45518.71202546296</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>45518.71591435185</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>45653.53664351852</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>45618</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>45593.59681712963</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45643</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>45461.62924768519</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45399.56596064815</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45614.5968287037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>45788.42467592593</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>45546.28121527778</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>45140</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22047,7 +22047,7 @@
         <v>45646.63482638889</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>45791.50862268519</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44809</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45181</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>45170.45921296296</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>45639.30934027778</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>45418.66800925926</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>45343.58587962963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>44876.35706018518</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>45440.5433912037</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>45667</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>45793.61047453704</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45796.44885416667</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>45559</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>45796</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45795.70912037037</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22999,7 +22999,7 @@
         <v>45219</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23061,7 +23061,7 @@
         <v>45796</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>45796.45054398148</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>45794.33498842592</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>45330</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>45794.3419212963</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>45795.71300925926</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>45729.76231481481</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45575.55273148148</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>45575.5547337963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45575.55684027778</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>45575.56686342593</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>45575.56820601852</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45795.71547453704</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>45177.33091435185</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>45244</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45456.48927083334</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>45793.62422453704</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>44522</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>45729.60775462963</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>44621.85737268518</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         <v>45054</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>45590.37590277778</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>45218</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45618</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>45155.5653125</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>45456.90869212963</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>45845.75200231482</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45411.65641203704</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45804.45474537037</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45844.57328703703</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45844.57527777777</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>45803.39776620371</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45131</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>45845.49216435185</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45310</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45803</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45845.4855787037</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>45804.45584490741</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>44683</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45667</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>45610</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>45845.76005787037</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45804.67795138889</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>44378.46857638889</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>45173</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45844.5775</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>44866.79668981482</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>45737.3846412037</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44445</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>45520.32887731482</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>45642</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44169</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45168.94197916667</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>44424.61709490741</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>45372.40246527778</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>45454.49679398148</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>44902</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45645.3737962963</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>45628.59233796296</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45203.510625</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>45099</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>45323</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>45188</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>45112.67952546296</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>45274</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>45152.34586805556</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>45518.71721064814</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>45134.68158564815</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>44577.83484953704</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>44675</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>44410.61837962963</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27233,7 +27233,7 @@
         <v>45125.41458333333</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27290,7 +27290,7 @@
         <v>44389</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>45061.53414351852</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>44822</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>44883</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>45097.39893518519</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>45173.39315972223</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27637,7 +27637,7 @@
         <v>45538.34460648148</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>45441.30899305556</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>45441.30998842593</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>45812.57452546297</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>45812.57604166667</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27947,7 +27947,7 @@
         <v>45812.57143518519</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>45177.33991898148</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>45685</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>45812.56952546296</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>45854</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>45005.35967592592</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>45005.47820601852</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>44420</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>45523.58565972222</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>45488.42258101852</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>44978</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>45586.55451388889</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28651,7 +28651,7 @@
         <v>44258</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>45707</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
         <v>45813.68209490741</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>45441.48670138889</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>45618.58622685185</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>44602.45490740741</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>44602.45162037037</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>45373.34383101852</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>45329</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>45534.54596064815</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>45538</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>45265.64142361111</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>45860.3857175926</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45738.42981481482</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>44988</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>45158.41768518519</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>45817.6455324074</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29645,7 +29645,7 @@
         <v>45393.3562962963</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>44425</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45726.33763888889</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29826,7 +29826,7 @@
         <v>45726.34090277777</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>45860.36222222223</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>45854</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>45571.71736111111</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>45194</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>44909</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>44544</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30230,7 +30230,7 @@
         <v>44841</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30287,7 +30287,7 @@
         <v>45538.34796296297</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>45218.488125</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>45645.3712037037</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>44124</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45820.61684027778</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45139.63480324074</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45280</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>45541.66916666667</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30773,7 +30773,7 @@
         <v>45519.52319444445</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         <v>45233.42121527778</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>45821.37199074074</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>45821.44521990741</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45749.47251157407</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>45305</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>45821.46486111111</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>45821.46135416667</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>45821.59353009259</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>45229</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         <v>44908.49152777778</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>45518.71482638889</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>45749</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>45749</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45618</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>45826.52024305556</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>45756.49009259259</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>44574.50425925926</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45741.64491898148</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31958,7 +31958,7 @@
         <v>44553.35407407407</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32015,7 +32015,7 @@
         <v>45827.51862268519</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>44594.84091435185</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45328</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>45827.51753472222</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>45827.51956018519</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>45007</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>45827.56939814815</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45400.66995370371</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>45227.31859953704</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>45357.34521990741</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>45827.51628472222</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45832.74418981482</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32749,7 +32749,7 @@
         <v>45769.98603009259</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>45254.68105324074</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>45768.49947916667</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32925,7 +32925,7 @@
         <v>45440</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>45687</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>45523</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45832.51028935185</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>44753</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>45574.65189814815</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>45832.55810185185</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>45831</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>45832.49325231482</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45832.51255787037</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>45369</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>45832.49579861111</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33639,7 +33639,7 @@
         <v>45832.5902662037</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45201</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>45565</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>45874.40503472222</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>45310.87931712963</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>45832.72778935185</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>45587</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45477.70315972222</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>44888.4577662037</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34172,7 +34172,7 @@
         <v>45562.61158564815</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>45274</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>45565.40700231482</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>44970</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>45729.65061342593</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>45404.68190972223</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45553</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44803.64361111111</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>45832.76491898148</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>44974.55693287037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34757,7 +34757,7 @@
         <v>45265.49225694445</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>45876.59166666667</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>45832.76100694444</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34933,7 +34933,7 @@
         <v>45870</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>45272.57385416667</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>45877.64605324074</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>45079</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>45079</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45880.46056712963</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35290,7 +35290,7 @@
         <v>44949</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45272.36168981482</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>45736.308125</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>45877.63989583333</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>45877.64144675926</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>45838.46456018519</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45684.5790162037</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45586</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>45835.68443287037</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45574.65087962963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45838.46408564815</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>45877.64847222222</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45880.28673611111</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45571.72288194444</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>45877.64230324074</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45877.64431712963</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45877.64776620371</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>45877.65075231482</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45880.3172337963</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>44943.73792824074</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45840</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45516.4221412037</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45831</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>44979</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>45880</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36780,7 +36780,7 @@
         <v>45881.43759259259</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>45881.42446759259</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>45487.40550925926</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>45471.52072916667</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37008,7 +37008,7 @@
         <v>45257.48188657407</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37065,7 +37065,7 @@
         <v>45201</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>45201.60283564815</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>45880</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45881.42791666667</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>45881.59550925926</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>45884.38858796296</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>45870</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>45884</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>45097.38688657407</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>45769.17</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>45229.66262731481</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37707,7 +37707,7 @@
         <v>45744.57851851852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37769,7 +37769,7 @@
         <v>45194</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45575.55570601852</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>44740.66997685185</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37945,7 +37945,7 @@
         <v>44546.67222222222</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>45229</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>44441.70047453704</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>45048</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38173,7 +38173,7 @@
         <v>45047.7181712963</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38230,7 +38230,7 @@
         <v>45394.51289351852</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38287,7 +38287,7 @@
         <v>45471.42659722222</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>45554.7158912037</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>45582.57542824074</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>45769.98449074074</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38525,7 +38525,7 @@
         <v>45547.36590277778</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38582,7 +38582,7 @@
         <v>45387.24732638889</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>45387.2521875</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>44175</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>44227</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>44473.6343287037</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>44236</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45377.48265046296</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45548</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39063,7 +39063,7 @@
         <v>45548</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>45569.35209490741</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>44371.47609953704</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>44445.55690972223</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39301,7 +39301,7 @@
         <v>45095</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45095</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39415,7 +39415,7 @@
         <v>44449</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>45008</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>45251.696875</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>44963.37709490741</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>45434.65854166666</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>44735.62539351852</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45077</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45266.58394675926</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>44967.60165509259</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>44895</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>44916</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         <v>44267</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44970.51849537037</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>44979</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45348</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>45575.53690972222</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40347,7 +40347,7 @@
         <v>45575.56256944445</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40409,7 +40409,7 @@
         <v>45099.27354166667</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>45580.73525462963</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>45166.68493055556</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>44259</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45635.69581018519</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>44950</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45594.63747685185</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40823,7 +40823,7 @@
         <v>45628.58975694444</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40880,7 +40880,7 @@
         <v>45344.6027662037</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40937,7 +40937,7 @@
         <v>45393.36060185185</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40999,7 +40999,7 @@
         <v>45404.55239583334</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41061,7 +41061,7 @@
         <v>45404.55601851852</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>44902</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>45034.5174537037</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45107</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>45194</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>44231</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>45189</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>45645</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41527,7 +41527,7 @@
         <v>44306.6371412037</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>44308</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41646,7 +41646,7 @@
         <v>45009.64217592592</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>44503</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>45145</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>45159.44525462963</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>44853.79818287037</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45497</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>45516.42789351852</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45488.41480324074</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45078.82620370371</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>44906.73321759259</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45538.34193287037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42288,7 +42288,7 @@
         <v>45511.39445601852</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45511.40297453704</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45646</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42464,7 +42464,7 @@
         <v>44951.5830324074</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>44083</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42583,7 +42583,7 @@
         <v>45237.67819444444</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42640,7 +42640,7 @@
         <v>45642.66184027777</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>45614.68083333333</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>45474.65005787037</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>45068</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42873,7 +42873,7 @@
         <v>44342.39703703704</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>45610.7466087963</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42992,7 +42992,7 @@
         <v>44577.81121527778</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>44791</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>45628.94579861111</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43163,7 +43163,7 @@
         <v>45618.59219907408</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>44161</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45635.63706018519</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45211</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>44721.52627314815</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45119</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>45755.68247685185</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43582,7 +43582,7 @@
         <v>44665</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43639,7 +43639,7 @@
         <v>45149</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45583</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>45453.36664351852</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45736</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45646.63839120371</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43939,7 +43939,7 @@
         <v>44734.64337962963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43996,7 +43996,7 @@
         <v>44946</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>44958.58982638889</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44110,7 +44110,7 @@
         <v>45694</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>45170</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44229,7 +44229,7 @@
         <v>44978</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44286,7 +44286,7 @@
         <v>45072</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44348,7 +44348,7 @@
         <v>45546.46497685185</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>44546.6679050926</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45138</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44529,7 +44529,7 @@
         <v>45113</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>44846</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44643,7 +44643,7 @@
         <v>45376.70292824074</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>44389</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>45327</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45590.39471064815</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>44990</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45254</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>45762.61817129629</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45052,7 +45052,7 @@
         <v>45074</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45109,7 +45109,7 @@
         <v>44431</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45530</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45223,7 +45223,7 @@
         <v>44868.36924768519</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>45714</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45030</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45189.38135416667</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>45685</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>45691.36253472222</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>45749</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45749</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45689,7 +45689,7 @@
         <v>45139.64328703703</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45751,7 +45751,7 @@
         <v>45575.65721064815</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45575.57104166667</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>45194</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>45471.38995370371</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45984,7 +45984,7 @@
         <v>45057</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46041,7 +46041,7 @@
         <v>44355</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>44900.36149305556</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45085</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45093.48221064815</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>44865.600625</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46331,7 +46331,7 @@
         <v>45303</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>44511</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45523.31621527778</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>44865.87770833333</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>45667</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46621,7 +46621,7 @@
         <v>45766.33309027777</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46678,7 +46678,7 @@
         <v>45211</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46735,7 +46735,7 @@
         <v>45170</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46797,7 +46797,7 @@
         <v>45744.32981481482</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46854,7 +46854,7 @@
         <v>45103.53614583334</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46911,7 +46911,7 @@
         <v>45738.43714120371</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46968,7 +46968,7 @@
         <v>45082.31421296296</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47030,7 +47030,7 @@
         <v>45036</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47087,7 +47087,7 @@
         <v>44566</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47144,7 +47144,7 @@
         <v>45699.65424768518</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47201,7 +47201,7 @@
         <v>44389</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>44990</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45411.42858796296</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>45072.42776620371</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47439,7 +47439,7 @@
         <v>44902</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47496,7 +47496,7 @@
         <v>45611.44960648148</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45043.40300925926</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47610,7 +47610,7 @@
         <v>45251</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>45736.30940972222</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>44431</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45077</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45077</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45077</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>45604.58837962963</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48024,7 +48024,7 @@
         <v>45075.44152777778</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45749</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>45744.57673611111</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>44946.54424768518</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>45525.7374537037</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         <v>45532</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>45667</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>45719.52871527777</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48495,7 +48495,7 @@
         <v>44457</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>44276</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48609,7 +48609,7 @@
         <v>45520.32997685186</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48671,7 +48671,7 @@
         <v>45520.33112268519</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48733,7 +48733,7 @@
         <v>45264.38084490741</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48790,7 +48790,7 @@
         <v>45393.35787037037</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48852,7 +48852,7 @@
         <v>44564</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48909,7 +48909,7 @@
         <v>45106</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48966,7 +48966,7 @@
         <v>45537.64621527777</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49028,7 +49028,7 @@
         <v>45548</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>44928</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>44425.40297453704</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49209,7 +49209,7 @@
         <v>45769.66260416667</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49266,7 +49266,7 @@
         <v>45252.78021990741</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>45183.48666666666</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49380,7 +49380,7 @@
         <v>45664</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49437,7 +49437,7 @@
         <v>44927.72487268518</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49494,7 +49494,7 @@
         <v>44833</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49551,7 +49551,7 @@
         <v>45618.59456018519</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>44484</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49670,7 +49670,7 @@
         <v>45568.64523148148</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49732,7 +49732,7 @@
         <v>45341.56577546296</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49794,7 +49794,7 @@
         <v>45334</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49851,7 +49851,7 @@
         <v>45273</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49908,7 +49908,7 @@
         <v>45670.69458333333</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49965,7 +49965,7 @@
         <v>45344.623125</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50022,7 +50022,7 @@
         <v>45404.55681712963</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50084,7 +50084,7 @@
         <v>45530</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50141,7 +50141,7 @@
         <v>45218</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50203,7 +50203,7 @@
         <v>45749.42258101852</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>45462</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50317,7 +50317,7 @@
         <v>45600.60071759259</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50374,7 +50374,7 @@
         <v>44438</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50436,7 +50436,7 @@
         <v>45516.59447916667</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50493,7 +50493,7 @@
         <v>45707</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45568.62625</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
         <v>45618.58962962963</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50674,7 +50674,7 @@
         <v>44984</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>45111</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50788,7 +50788,7 @@
         <v>45316</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>45177.31795138889</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45751.50498842593</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45108.7553587963</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45751.5056712963</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45471.40384259259</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>45702</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>45714.31533564815</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -567,7 +567,7 @@
         <v>45615</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         <v>45252</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44850.83328703704</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>44375</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45810.54824074074</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>44406</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>45568.63905092593</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>45099</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>44060</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>44320</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>45138</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44484</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45218</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>45099</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45616.38605324074</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>44472</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>44789</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45615</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>44280</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45021</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>45138</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>45670</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>44375</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>44512</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>44713.59363425926</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>44679</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>44320</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45698.46697916667</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>45250</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45782.5300462963</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45104.3483912037</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>45783.66537037037</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45475.92849537037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>45614.68287037037</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>44536</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>45845.75491898148</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>45845.75751157408</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45614.68596064814</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>45537.64261574074</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>45518</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>45827.53077546296</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45440.3184375</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>45832.56153935185</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>44949</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>45575.54934027778</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>45281</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>45478.39592592593</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>45516.42667824074</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>45645</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>45618.58876157407</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>45471.56265046296</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>44522</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>45537.64484953704</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>45645</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>44151</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>44242</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>44260.30453703704</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>44069</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44069</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>44295.61297453703</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>44063</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44123</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44104</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44889.5746875</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44126</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>44267</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44431.69783564815</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44853.61925925926</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44495.87667824074</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44453</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>44447.51184027778</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>44228</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>44445.4953587963</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44484</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44126</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44508</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44284.70511574074</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>44271</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>44327</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44176</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44167</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>44503</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>44462</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>44613</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44386</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>44210</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44280</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>44145</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44427.75243055556</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44300</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44441.66886574074</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>44431.69723379629</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44332</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>44721.53951388889</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44722.78552083333</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>44577.82805555555</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>44862</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>44171</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44460</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>44790</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44481</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>44676</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44754</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44714</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>44627</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44638</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>44377</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>44377.44943287037</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>44069</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>44630</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>44603</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>44862</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>44629</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44063</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>44713.61145833333</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>44123</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>44671</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>44375</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>44706.65927083333</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>44069</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44224</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>44260.31335648148</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44061.61920138889</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>44068</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>44102</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>44113</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>44468.34099537037</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>44102</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>44085</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>44257</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>44259</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>44577.84596064815</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>44505.36354166667</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>44418.58454861111</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>44671</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>44273</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>44375</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>44546.67978009259</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>44187</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>44326</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44823.37396990741</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>44325</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>44378.55319444444</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>44071</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>44073</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>44183</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44076</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44162</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>44522.87423611111</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44635.51386574074</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>44126</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>44130</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>44357</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>44820</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>44085</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>44434.74203703704</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>44693.66775462963</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>44484.56523148148</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>44691</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>44305</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>44694.29309027778</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>44505</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44490</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44629</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44425.40128472223</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>44665</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>44459.57613425926</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>44447</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>44432.68241898148</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>44594</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>44432</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>44326.7296412037</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44487.51556712963</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>44463</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>44497</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44650.47945601852</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>44456</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>44819</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>44384.56912037037</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         <v>44733.71126157408</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>44479.58512731481</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>44453</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>44076</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44618</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>44536</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>44420.60616898148</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>44860</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>44636.46935185185</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>44389</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>44672</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>44151</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>44451</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>44098</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>44825.99293981482</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>44873.47148148148</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>44438.30614583333</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>44114</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>44088</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>44449</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>44665</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13981,7 +13981,7 @@
         <v>44622.69101851852</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>44777</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>44451.78710648148</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>44875.47543981481</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>44334.60293981482</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>44533</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>44491</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>44088</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>44536</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>44116</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>44179</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>44107</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>44502.49809027778</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>44502</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
         <v>44088</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>44208</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>44067</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>44481.34877314815</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>44268.55900462963</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>44491</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>44267</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>44376</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>44363</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>44511.39611111111</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>44607.64115740741</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44608</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>44526</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>44784</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>44389</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44539.31923611111</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44539</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44389</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44091</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44490</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44698.62354166667</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>44784.38697916667</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         <v>44332.74105324074</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>44446</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>44728</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>44889.68100694445</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44113</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>44069</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>44389</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>45355.70009259259</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16514,7 +16514,7 @@
         <v>45338</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>45412.54541666667</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>45168.92155092592</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>44602</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>45103</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>44064</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>45091.39362268519</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>45119.46452546296</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>44300</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45194</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>44378.46403935185</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>44319</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>45698</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>45698</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>45698</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>45103</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>45107</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45729.65171296296</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45694</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>44301</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>45439.56605324074</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
         <v>45222</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>45433.58099537037</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45384</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>45435.57399305556</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45702</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45534.54032407407</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>45538</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>45243</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>45243.62420138889</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>45243</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>45615.69570601852</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>44890.46174768519</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45384.43418981481</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45400.6709837963</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>45520.3320949074</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>44531.3575</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>45554.71863425926</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>45471.52878472222</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>45702</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45518.71048611111</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45776.65518518518</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>45274</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>45575.53331018519</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>45575.54489583334</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45777.41673611111</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45777.43878472222</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45733.60959490741</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45777.42628472222</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>45162.5978125</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45777</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>45279</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45519.51627314815</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45519.52232638889</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45537.42240740741</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45107</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>45061.52474537037</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45373.30434027778</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>45783.71833333333</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>45005</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>45509.73383101852</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45608</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45546.68743055555</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45567.68003472222</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>45460.46358796296</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45104.34107638889</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>44551</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>44480.58034722223</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>45786</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45289</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44981</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>45569.3533912037</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>45253</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>45203.45681712963</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>45148</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45267.69052083333</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45141.76530092592</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45113</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45785.4253125</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45537.665</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45229.66430555555</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>45537.65305555556</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45518.71202546296</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>45518.71591435185</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>45653.53664351852</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>45618</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>45593.59681712963</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45643</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>45461.62924768519</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45399.56596064815</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45614.5968287037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>45788.42467592593</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>45546.28121527778</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>45140</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22047,7 +22047,7 @@
         <v>45646.63482638889</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>45791.50862268519</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44809</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45181</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>45170.45921296296</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>45639.30934027778</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>45418.66800925926</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>45343.58587962963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>44876.35706018518</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>45440.5433912037</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>45667</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>45793.61047453704</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45796.44885416667</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>45559</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>45796</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45795.70912037037</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22999,7 +22999,7 @@
         <v>45219</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23061,7 +23061,7 @@
         <v>45796</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>45796.45054398148</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>45794.33498842592</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>45330</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>45794.3419212963</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>45795.71300925926</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>45729.76231481481</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45575.55273148148</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>45575.5547337963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45575.55684027778</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>45575.56686342593</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>45575.56820601852</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45795.71547453704</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>45177.33091435185</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>45244</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45456.48927083334</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>45793.62422453704</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>44522</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>45729.60775462963</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>44621.85737268518</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         <v>45054</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>45590.37590277778</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>45218</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45618</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>45155.5653125</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>45456.90869212963</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>45845.75200231482</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45411.65641203704</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45804.45474537037</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45844.57328703703</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45844.57527777777</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>45803.39776620371</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45131</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>45845.49216435185</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45310</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45803</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45845.4855787037</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>45804.45584490741</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>44683</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45667</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>45610</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>45845.76005787037</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45804.67795138889</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>44378.46857638889</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>45173</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45844.5775</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>44866.79668981482</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>45737.3846412037</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44445</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>45520.32887731482</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>45642</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44169</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45168.94197916667</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>44424.61709490741</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>45372.40246527778</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>45454.49679398148</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>44902</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45645.3737962963</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>45628.59233796296</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45203.510625</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>45099</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>45323</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>45188</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>45112.67952546296</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>45274</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>45152.34586805556</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>45518.71721064814</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>45134.68158564815</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>44577.83484953704</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>44675</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>44410.61837962963</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27233,7 +27233,7 @@
         <v>45125.41458333333</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27290,7 +27290,7 @@
         <v>44389</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>45061.53414351852</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>44822</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>44883</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>45097.39893518519</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>45173.39315972223</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27637,7 +27637,7 @@
         <v>45538.34460648148</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>45441.30899305556</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>45441.30998842593</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>45812.57452546297</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>45812.57604166667</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27947,7 +27947,7 @@
         <v>45812.57143518519</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>45177.33991898148</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>45685</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>45812.56952546296</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>45854</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>45005.35967592592</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>45005.47820601852</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>44420</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>45523.58565972222</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>45488.42258101852</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>44978</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>45586.55451388889</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28651,7 +28651,7 @@
         <v>44258</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>45707</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
         <v>45813.68209490741</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>45441.48670138889</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>45618.58622685185</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>44602.45490740741</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>44602.45162037037</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>45373.34383101852</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>45329</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>45534.54596064815</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>45538</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>45265.64142361111</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>45860.3857175926</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45738.42981481482</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>44988</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>45158.41768518519</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>45817.6455324074</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29645,7 +29645,7 @@
         <v>45393.3562962963</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>44425</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45726.33763888889</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29826,7 +29826,7 @@
         <v>45726.34090277777</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>45860.36222222223</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>45854</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>45571.71736111111</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>45194</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>44909</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>44544</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30230,7 +30230,7 @@
         <v>44841</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30287,7 +30287,7 @@
         <v>45538.34796296297</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>45218.488125</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>45645.3712037037</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>44124</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45820.61684027778</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45139.63480324074</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45280</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>45541.66916666667</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30773,7 +30773,7 @@
         <v>45519.52319444445</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         <v>45233.42121527778</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>45821.37199074074</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>45821.44521990741</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45749.47251157407</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>45305</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>45821.46486111111</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>45821.46135416667</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>45821.59353009259</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>45229</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         <v>44908.49152777778</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>45518.71482638889</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>45749</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>45749</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45618</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>45826.52024305556</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>45756.49009259259</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>44574.50425925926</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45741.64491898148</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31958,7 +31958,7 @@
         <v>44553.35407407407</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32015,7 +32015,7 @@
         <v>45827.51862268519</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>44594.84091435185</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45328</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>45827.51753472222</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>45827.51956018519</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>45007</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>45827.56939814815</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45400.66995370371</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>45227.31859953704</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>45357.34521990741</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>45827.51628472222</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45832.74418981482</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32749,7 +32749,7 @@
         <v>45769.98603009259</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>45254.68105324074</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>45768.49947916667</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32925,7 +32925,7 @@
         <v>45440</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>45687</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>45523</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45832.51028935185</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>44753</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>45574.65189814815</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>45832.55810185185</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>45831</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>45832.49325231482</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45832.51255787037</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>45369</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>45832.49579861111</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33639,7 +33639,7 @@
         <v>45832.5902662037</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45201</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>45565</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>45874.40503472222</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>45310.87931712963</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>45832.72778935185</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>45587</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45477.70315972222</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>44888.4577662037</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34172,7 +34172,7 @@
         <v>45562.61158564815</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>45274</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>45565.40700231482</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>44970</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>45729.65061342593</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>45404.68190972223</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45553</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44803.64361111111</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>45832.76491898148</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>44974.55693287037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34757,7 +34757,7 @@
         <v>45265.49225694445</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>45876.59166666667</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>45832.76100694444</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34933,7 +34933,7 @@
         <v>45870</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>45272.57385416667</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>45877.64605324074</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>45079</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>45079</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45880.46056712963</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35290,7 +35290,7 @@
         <v>44949</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45272.36168981482</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>45736.308125</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>45877.63989583333</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>45877.64144675926</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>45838.46456018519</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45684.5790162037</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45586</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>45835.68443287037</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45574.65087962963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45838.46408564815</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>45877.64847222222</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45880.28673611111</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45571.72288194444</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>45877.64230324074</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45877.64431712963</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45877.64776620371</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>45877.65075231482</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45880.3172337963</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>44943.73792824074</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45840</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45516.4221412037</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45831</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>44979</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>45880</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36780,7 +36780,7 @@
         <v>45881.43759259259</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>45881.42446759259</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>45487.40550925926</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>45471.52072916667</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37008,7 +37008,7 @@
         <v>45257.48188657407</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37065,7 +37065,7 @@
         <v>45201</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>45201.60283564815</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>45880</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45881.42791666667</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>45881.59550925926</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>45884.38858796296</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>45870</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>45884</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>45097.38688657407</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>45769.17</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>45229.66262731481</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37707,7 +37707,7 @@
         <v>45744.57851851852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37769,7 +37769,7 @@
         <v>45194</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45575.55570601852</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>44740.66997685185</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37945,7 +37945,7 @@
         <v>44546.67222222222</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>45229</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>44441.70047453704</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>45048</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38173,7 +38173,7 @@
         <v>45047.7181712963</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38230,7 +38230,7 @@
         <v>45394.51289351852</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38287,7 +38287,7 @@
         <v>45471.42659722222</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>45554.7158912037</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>45582.57542824074</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>45769.98449074074</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38525,7 +38525,7 @@
         <v>45547.36590277778</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38582,7 +38582,7 @@
         <v>45387.24732638889</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>45387.2521875</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>44175</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>44227</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>44473.6343287037</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>44236</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45377.48265046296</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45548</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39063,7 +39063,7 @@
         <v>45548</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>45569.35209490741</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>44371.47609953704</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>44445.55690972223</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39301,7 +39301,7 @@
         <v>45095</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45095</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39415,7 +39415,7 @@
         <v>44449</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>45008</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>45251.696875</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>44963.37709490741</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>45434.65854166666</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>44735.62539351852</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45077</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45266.58394675926</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>44967.60165509259</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>44895</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>44916</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         <v>44267</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44970.51849537037</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>44979</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45348</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>45575.53690972222</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40347,7 +40347,7 @@
         <v>45575.56256944445</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40409,7 +40409,7 @@
         <v>45099.27354166667</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>45580.73525462963</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>45166.68493055556</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>44259</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45635.69581018519</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>44950</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45594.63747685185</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40823,7 +40823,7 @@
         <v>45628.58975694444</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40880,7 +40880,7 @@
         <v>45344.6027662037</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40937,7 +40937,7 @@
         <v>45393.36060185185</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40999,7 +40999,7 @@
         <v>45404.55239583334</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41061,7 +41061,7 @@
         <v>45404.55601851852</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>44902</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>45034.5174537037</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45107</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>45194</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>44231</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>45189</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>45645</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41527,7 +41527,7 @@
         <v>44306.6371412037</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>44308</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41646,7 +41646,7 @@
         <v>45009.64217592592</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>44503</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>45145</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>45159.44525462963</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>44853.79818287037</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45497</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>45516.42789351852</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45488.41480324074</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45078.82620370371</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>44906.73321759259</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45538.34193287037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42288,7 +42288,7 @@
         <v>45511.39445601852</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45511.40297453704</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45646</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42464,7 +42464,7 @@
         <v>44951.5830324074</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>44083</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42583,7 +42583,7 @@
         <v>45237.67819444444</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42640,7 +42640,7 @@
         <v>45642.66184027777</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>45614.68083333333</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>45474.65005787037</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>45068</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42873,7 +42873,7 @@
         <v>44342.39703703704</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>45610.7466087963</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42992,7 +42992,7 @@
         <v>44577.81121527778</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>44791</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>45628.94579861111</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43163,7 +43163,7 @@
         <v>45618.59219907408</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>44161</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45635.63706018519</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45211</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>44721.52627314815</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45119</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>45755.68247685185</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43582,7 +43582,7 @@
         <v>44665</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43639,7 +43639,7 @@
         <v>45149</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45583</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>45453.36664351852</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45736</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45646.63839120371</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43939,7 +43939,7 @@
         <v>44734.64337962963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43996,7 +43996,7 @@
         <v>44946</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>44958.58982638889</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44110,7 +44110,7 @@
         <v>45694</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>45170</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44229,7 +44229,7 @@
         <v>44978</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44286,7 +44286,7 @@
         <v>45072</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44348,7 +44348,7 @@
         <v>45546.46497685185</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>44546.6679050926</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45138</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44529,7 +44529,7 @@
         <v>45113</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>44846</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44643,7 +44643,7 @@
         <v>45376.70292824074</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>44389</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>45327</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45590.39471064815</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>44990</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45254</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>45762.61817129629</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45052,7 +45052,7 @@
         <v>45074</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45109,7 +45109,7 @@
         <v>44431</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45530</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45223,7 +45223,7 @@
         <v>44868.36924768519</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>45714</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45030</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45189.38135416667</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>45685</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>45691.36253472222</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>45749</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45749</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45689,7 +45689,7 @@
         <v>45139.64328703703</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45751,7 +45751,7 @@
         <v>45575.65721064815</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45575.57104166667</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>45194</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>45471.38995370371</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45984,7 +45984,7 @@
         <v>45057</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46041,7 +46041,7 @@
         <v>44355</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>44900.36149305556</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45085</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45093.48221064815</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>44865.600625</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46331,7 +46331,7 @@
         <v>45303</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>44511</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45523.31621527778</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>44865.87770833333</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>45667</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46621,7 +46621,7 @@
         <v>45766.33309027777</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46678,7 +46678,7 @@
         <v>45211</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46735,7 +46735,7 @@
         <v>45170</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46797,7 +46797,7 @@
         <v>45744.32981481482</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46854,7 +46854,7 @@
         <v>45103.53614583334</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46911,7 +46911,7 @@
         <v>45738.43714120371</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46968,7 +46968,7 @@
         <v>45082.31421296296</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47030,7 +47030,7 @@
         <v>45036</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47087,7 +47087,7 @@
         <v>44566</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47144,7 +47144,7 @@
         <v>45699.65424768518</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47201,7 +47201,7 @@
         <v>44389</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>44990</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45411.42858796296</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>45072.42776620371</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47439,7 +47439,7 @@
         <v>44902</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47496,7 +47496,7 @@
         <v>45611.44960648148</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>45043.40300925926</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47610,7 +47610,7 @@
         <v>45251</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>45736.30940972222</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>44431</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45077</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45077</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45077</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>45604.58837962963</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48024,7 +48024,7 @@
         <v>45075.44152777778</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45749</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>45744.57673611111</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>44946.54424768518</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>45525.7374537037</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         <v>45532</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>45667</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>45719.52871527777</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48495,7 +48495,7 @@
         <v>44457</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>44276</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48609,7 +48609,7 @@
         <v>45520.32997685186</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48671,7 +48671,7 @@
         <v>45520.33112268519</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48733,7 +48733,7 @@
         <v>45264.38084490741</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48790,7 +48790,7 @@
         <v>45393.35787037037</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48852,7 +48852,7 @@
         <v>44564</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48909,7 +48909,7 @@
         <v>45106</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48966,7 +48966,7 @@
         <v>45537.64621527777</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49028,7 +49028,7 @@
         <v>45548</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>44928</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>44425.40297453704</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49209,7 +49209,7 @@
         <v>45769.66260416667</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49266,7 +49266,7 @@
         <v>45252.78021990741</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>45183.48666666666</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49380,7 +49380,7 @@
         <v>45664</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49437,7 +49437,7 @@
         <v>44927.72487268518</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49494,7 +49494,7 @@
         <v>44833</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49551,7 +49551,7 @@
         <v>45618.59456018519</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>44484</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49670,7 +49670,7 @@
         <v>45568.64523148148</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49732,7 +49732,7 @@
         <v>45341.56577546296</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49794,7 +49794,7 @@
         <v>45334</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49851,7 +49851,7 @@
         <v>45273</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49908,7 +49908,7 @@
         <v>45670.69458333333</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49965,7 +49965,7 @@
         <v>45344.623125</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50022,7 +50022,7 @@
         <v>45404.55681712963</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50084,7 +50084,7 @@
         <v>45530</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50141,7 +50141,7 @@
         <v>45218</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50203,7 +50203,7 @@
         <v>45749.42258101852</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>45462</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50317,7 +50317,7 @@
         <v>45600.60071759259</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50374,7 +50374,7 @@
         <v>44438</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50436,7 +50436,7 @@
         <v>45516.59447916667</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50493,7 +50493,7 @@
         <v>45707</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45568.62625</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
         <v>45618.58962962963</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50674,7 +50674,7 @@
         <v>44984</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>45111</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50788,7 +50788,7 @@
         <v>45316</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>45177.31795138889</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45751.50498842593</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45108.7553587963</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45751.5056712963</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45471.40384259259</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>45702</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>45714.31533564815</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -567,7 +567,7 @@
         <v>45615</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
         <v>45252</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>44850.83328703704</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>44375</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>45810.54824074074</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44406</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45568.63905092593</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45099</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>44320</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>45138</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>45888.67560185185</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>44484</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>45099</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45218</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>45616.38605324074</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45887.5708912037</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>45888.67765046296</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>44472</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>45138</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45615</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44280</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>45021</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>44789</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45670</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>44375</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>44512</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>44713.59363425926</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>44679</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>44320</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>45518</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>45537.64484953704</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>45614.68287037037</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45618.58876157407</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45575.54934027778</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>45698.46697916667</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>45471.56265046296</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>45645</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>45782.5300462963</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>45783.66537037037</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45478.39592592593</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>44949</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>45614.68596064814</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>44536</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>45281</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>45537.64261574074</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>45645</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>45250</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>45827.53077546296</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45832.56153935185</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>45104.3483912037</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>45881.42446759259</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>44522</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45845.75491898148</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>45845.75751157408</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>45475.92849537037</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>45440.3184375</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>44151</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>44242</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>44069</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44069</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44260.30453703704</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>44295.61297453703</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>44123</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>44889.5746875</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>44104</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>44267</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>44126</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>44431.69783564815</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>44853.61925925926</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>44495.87667824074</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>44447.51184027778</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>44453</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>44228</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>44445.4953587963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44126</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>44484</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>44508</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>44284.70511574074</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44271</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44176</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44327</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>44167</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>44503</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>44613</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44462</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>44386</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>44210</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>44280</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>44427.75243055556</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44145</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>44441.66886574074</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>44300</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>44431.69723379629</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>44332</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>44722.78552083333</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>44721.53951388889</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>44862</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>44577.82805555555</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>44171</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>44460</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44481</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>44638</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>44790</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>44754</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>44714</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>44676</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>44627</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>44377</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>44377.44943287037</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>44069</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>44603</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>44630</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>44862</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>44629</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>44713.61145833333</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>44123</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>44375</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>44671</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>44706.65927083333</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         <v>44069</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>44224</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>44260.31335648148</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>44068</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>44113</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>44468.34099537037</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>44085</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44257</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>44259</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44102</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>44102</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         <v>44577.84596064815</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>44418.58454861111</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>44671</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>44505.36354166667</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>44546.67978009259</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>44375</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44187</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>44326</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>44823.37396990741</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>44273</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44325</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>44378.55319444444</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>44071</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>44183</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>44073</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>44076</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44162</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>44522.87423611111</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>44635.51386574074</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>44126</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>44130</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>44357</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44820</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>44085</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44434.74203703704</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>44693.66775462963</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>44484.56523148148</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44691</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>44694.29309027778</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44305</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>44505</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>44490</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>44629</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>44425.40128472223</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>44665</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>44459.57613425926</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>44447</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>44432.68241898148</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>44432</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44594</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>44889.68100694445</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44091</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>44332.74105324074</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>44728</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>44326.7296412037</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>44113</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>44487.51556712963</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>44463</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>44497</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44456</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>44602</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44384.56912037037</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>44650.47945601852</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>44819</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>44453</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>44536</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44733.71126157408</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>44479.58512731481</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>44618</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>44420.60616898148</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>44860</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>44076</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>44636.46935185185</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44389</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>44451</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>44151</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>44873.47148148148</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>44672</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>44088</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>44098</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>44825.99293981482</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>44438.30614583333</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>44665</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>44777</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>44114</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>44451.78710648148</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>44533</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>44088</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>44536</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         <v>44116</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>44179</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44449</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44622.69101851852</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44107</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>44502.49809027778</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44502</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>44875.47543981481</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>44088</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>44208</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>44334.60293981482</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>44481.34877314815</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44268.55900462963</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>44491</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44491</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>44363</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>44511.39611111111</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>44267</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>44376</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>44784</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>44067</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>44607.64115740741</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>44490</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>44698.62354166667</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>44784.38697916667</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>44608</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>44227</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>45565</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>44069</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45310</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>45736.30940972222</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>45714.31533564815</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>44389</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>44539.31923611111</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>44539</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>45411.65641203704</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45008</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>45518.71482638889</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>45113</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>44970</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>44526</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>45571.72288194444</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>44389</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>45229</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>45530</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>45289</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>44531.3575</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>44446</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>44231</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45095</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45377.48265046296</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45538.34460648148</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44967.60165509259</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44389</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44445</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>45439.56605324074</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>44342.39703703704</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>44355</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45664</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45736</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44511</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>45203.510625</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>45274</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45112.67952546296</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>45229.66262731481</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>45280</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>45628.94579861111</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>45107</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>44378.46403935185</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>45532</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>44974.55693287037</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>44602.45490740741</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>44267</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45030</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>45404.55681712963</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>45574.65087962963</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>45085</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>45611.44960648148</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>44890.46174768519</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45334</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45738.43714120371</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>44683</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>45516.59447916667</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45604.58837962963</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>44276</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>44753</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>45229</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45565.40700231482</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>45538.34796296297</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>45384.43418981481</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45646.63482638889</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>45755.68247685185</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>45303</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45140</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45471.38995370371</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45751.50498842593</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>44161</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>44943.73792824074</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>44734.64337962963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>44906.73321759259</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>45047.7181712963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45054</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>44424.61709490741</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45580.73525462963</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>45583</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>45568.62625</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45614.5968287037</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>44984</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>45273</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>45183.48666666666</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45769.17</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45158.41768518519</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>45251.696875</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>45643</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45749</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>45394.51289351852</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45569.35209490741</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44236</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>45653.53664351852</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45139.64328703703</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>45618.59219907408</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45194</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45575.53690972222</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>45575.56256944445</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45618.59456018519</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45488.41480324074</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>45119</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>44946.54424768518</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>45618.58622685185</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45698</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>44853.79818287037</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45568.64523148148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44809</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>45355.70009259259</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45702</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45075.44152777778</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>45310.87931712963</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>45264.38084490741</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45305</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>44979</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>44319</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>45769.98603009259</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45435.57399305556</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>45097.38688657407</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44958.58982638889</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>45344.6027662037</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>45702</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45330</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>44564</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>45219</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45043.40300925926</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44665</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>45327</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>45749.42258101852</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>45608</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>45749</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>45694</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>45751.5056712963</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>45233.42121527778</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>44259</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>45243</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>44981</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45642.66184027777</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>45610.7466087963</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>45243.62420138889</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45243</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>45177.31795138889</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>45211</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>45541.66916666667</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45593.59681712963</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>45538.34193287037</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>45005.35967592592</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>45005.47820601852</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>45628.59233796296</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>45749</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>45749.47251157407</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>45453.36664351852</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44445.55690972223</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>45404.55239583334</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>45404.55601851852</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>45777.42628472222</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>45777.41673611111</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45272.57385416667</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>44546.6679050926</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>45768.49947916667</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45733.60959490741</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>45777</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>45777.43878472222</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>45194</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>45776.65518518518</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>44721.52627314815</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>44876.35706018518</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>45537.64621527777</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>45783.71833333333</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44988</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>45497</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>45567.68003472222</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>45509.73383101852</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45057</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>44803.64361111111</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>45145</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>45534.54032407407</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>45460.46358796296</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>45534.54596064815</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>44410.61837962963</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>45166.68493055556</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>45569.3533912037</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45253</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>45203.45681712963</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45369</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>45785.4253125</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>45229.66430555555</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>45338</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45267.69052083333</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>45635.63706018519</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>44441.70047453704</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>45726.33763888889</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45726.34090277777</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45537.65305555556</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>45159.44525462963</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>45788.42467592593</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>45461.62924768519</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>44378.46857638889</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>45103.53614583334</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
         <v>45077</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45162.5978125</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45744.57851851852</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45537.665</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>45061.53414351852</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>45433.58099537037</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>45691.36253472222</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>45749</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>45279</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>45104.34107638889</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45523.31621527778</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>44833</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>44888.4577662037</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>44928</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
         <v>45272.36168981482</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28676,7 +28676,7 @@
         <v>44902</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>44927.72487268518</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45737.3846412037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45559</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>45108.7553587963</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>45274</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>45786</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>45639.30934027778</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45791.50862268519</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45149</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45744.57673611111</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>45181</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29390,7 +29390,7 @@
         <v>45418.66800925926</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>45523.58565972222</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>45766.33309027777</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>45618</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45173.39315972223</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         <v>45007</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45600.60071759259</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>45036</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>44258</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>45667</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>45546.28121527778</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>45440.5433912037</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>45168.92155092592</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30141,7 +30141,7 @@
         <v>45168.94197916667</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>45741.64491898148</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>44389</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>45518.71048611111</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30379,7 +30379,7 @@
         <v>45518.71202546296</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45518.71591435185</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>45441.30899305556</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>45441.30998842593</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>45793.61047453704</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>45548</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>44979</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>45793.62422453704</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>45456.90869212963</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45795.71300925926</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45795.70912037037</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>45155.5653125</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>45244</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>45645.3712037037</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>45796.44885416667</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>44300</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>45794.33498842592</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45125.41458333333</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>45113</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>45796</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>45794.3419212963</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>44480.58034722223</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>44841</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45796</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31797,7 +31797,7 @@
         <v>45796.45054398148</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>45061.52474537037</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>45170</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>45795.71547453704</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32035,7 +32035,7 @@
         <v>45456.48927083334</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>45562.61158564815</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>44371.47609953704</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>45474.65005787037</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>45511.40297453704</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>44978</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>44963.37709490741</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45201</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>45201.60283564815</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>45329</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>45518.71721064814</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>45547.36590277778</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>45048</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44574.50425925926</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>45610</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44551</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>44389</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>44675</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>45373.30434027778</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>45729.60775462963</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>45618</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>45005</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>45034.5174537037</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>45590.37590277778</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>44909</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>45803</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>45582.57542824074</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33619,7 +33619,7 @@
         <v>45803.39776620371</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>44425</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>45804.45474537037</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45804.67795138889</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>45635.69581018519</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>45376.70292824074</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>44865.600625</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>45804.45584490741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>45103</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>44740.66997685185</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34194,7 +34194,7 @@
         <v>44546.67222222222</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>44431</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45194</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>44908.49152777778</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>45471.40384259259</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>45411.42858796296</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34536,7 +34536,7 @@
         <v>45194</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>45615.69570601852</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>45707</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45575.65721064815</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>45471.52878472222</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>45628.58975694444</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>45148</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>45152.34586805556</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45707</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>45189.38135416667</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>44577.81121527778</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45738.42981481482</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>45519.51627314815</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>44900.36149305556</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>45756.49009259259</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>45099</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>45694</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>44503</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>44553.35407407407</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>45702</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>45575.55570601852</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>45594.63747685185</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>44951.5830324074</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>45373.34383101852</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>45218</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>45131</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36053,7 +36053,7 @@
         <v>45078.82620370371</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>45854</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>45812.56952546296</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>45068</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44457</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36343,7 +36343,7 @@
         <v>44301</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>45590.39471064815</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>45434.65854166666</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>45188</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>45812.57143518519</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>45812.57452546297</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>45812.57604166667</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45813.68209490741</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45218</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>45266.58394675926</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>45082.31421296296</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37000,7 +37000,7 @@
         <v>45170</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37062,7 +37062,7 @@
         <v>45227.31859953704</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45817.6455324074</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>45384</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>45072</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45575.55273148148</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>45575.5547337963</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>45575.55684027778</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>45537.42240740741</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>45519.52319444445</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>45714</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>45642</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>45412.54541666667</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>45854</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37828,7 +37828,7 @@
         <v>45860.36222222223</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>45387.24732638889</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>45387.2521875</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>45554.7158912037</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>45091.39362268519</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45201</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>45618.58962962963</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>45538</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38304,7 +38304,7 @@
         <v>45860.3857175926</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>45257.48188657407</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44420</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>45265.64142361111</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>45685</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>45614.68083333333</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>45141.76530092592</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>45400.66995370371</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>44389</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45820.61684027778</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>44431</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>45821.59353009259</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>44970.51849537037</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45821.37199074074</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>45119.46452546296</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39179,7 +39179,7 @@
         <v>45194</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>45218.488125</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>44866.79668981482</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45821.46135416667</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39417,7 +39417,7 @@
         <v>44175</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>45821.46486111111</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>45538</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>45821.44521990741</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>45348</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>45729.65171296296</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>45138</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39831,7 +39831,7 @@
         <v>45488.42258101852</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45586</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39950,7 +39950,7 @@
         <v>45827.51862268519</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45826.52024305556</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45316</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45827.56939814815</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>45393.3562962963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>45393.36060185185</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40317,7 +40317,7 @@
         <v>44621.85737268518</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>45827.51753472222</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>45827.51956018519</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>45009.64217592592</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>44566</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>45827.51628472222</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44083</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>45523</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>45831</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>45222</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40907,7 +40907,7 @@
         <v>44949</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>44895</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41021,7 +41021,7 @@
         <v>45587</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>45667</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
         <v>45667</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>45139.63480324074</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>45575.57104166667</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>45874.40503472222</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>45323</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41435,7 +41435,7 @@
         <v>45832.76100694444</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41497,7 +41497,7 @@
         <v>45832.76491898148</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>45106</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41616,7 +41616,7 @@
         <v>45832.49325231482</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41678,7 +41678,7 @@
         <v>45832.51255787037</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>44990</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45832.55810185185</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>44602.45162037037</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41916,7 +41916,7 @@
         <v>45832.72778935185</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>45832.5902662037</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>45832.74418981482</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>45103</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>45357.34521990741</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>45832.49579861111</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45832.51028935185</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45511.39445601852</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45877.64847222222</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42464,7 +42464,7 @@
         <v>44735.62539351852</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42526,7 +42526,7 @@
         <v>45877.63989583333</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>45877.64144675926</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42650,7 +42650,7 @@
         <v>45835.68443287037</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42707,7 +42707,7 @@
         <v>45877.64230324074</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42769,7 +42769,7 @@
         <v>45877.64431712963</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>45877.64776620371</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>45877.65075231482</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42955,7 +42955,7 @@
         <v>45111</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43012,7 +43012,7 @@
         <v>45554.71863425926</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45769.98449074074</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43131,7 +43131,7 @@
         <v>44950</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43188,7 +43188,7 @@
         <v>45072.42776620371</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>44883</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43307,7 +43307,7 @@
         <v>45254.68105324074</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43369,7 +43369,7 @@
         <v>45477.70315972222</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>45525.7374537037</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>45177.33991898148</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>45251</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43602,7 +43602,7 @@
         <v>45404.68190972223</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>45252.78021990741</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>44577.83484953704</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45077</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>45077</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43902,7 +43902,7 @@
         <v>45077</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43964,7 +43964,7 @@
         <v>45393.35787037037</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44026,7 +44026,7 @@
         <v>45762.61817129629</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>45877.64605324074</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>45876.59166666667</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>45107</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44259,7 +44259,7 @@
         <v>44902</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>45870</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44373,7 +44373,7 @@
         <v>45744.32981481482</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44430,7 +44430,7 @@
         <v>45519.52232638889</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
         <v>45107</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44554,7 +44554,7 @@
         <v>45881.43759259259</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>45454.49679398148</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
         <v>44846</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44725,7 +44725,7 @@
         <v>45719.52871527777</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44787,7 +44787,7 @@
         <v>45880.28673611111</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>45880.46056712963</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>45618</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44963,7 +44963,7 @@
         <v>44594.84091435185</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>45645.3737962963</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>45881.59550925926</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>44169</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>44822</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>45274</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>45177.33091435185</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>45574.65189814815</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45880.3172337963</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45496,7 +45496,7 @@
         <v>45838.46456018519</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45838.46408564815</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45620,7 +45620,7 @@
         <v>45881.42791666667</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>45516.4221412037</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45739,7 +45739,7 @@
         <v>45687</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45796,7 +45796,7 @@
         <v>45093.48221064815</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45853,7 +45853,7 @@
         <v>44438</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>45840</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45972,7 +45972,7 @@
         <v>45254</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45769.66260416667</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>45736.308125</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45265.49225694445</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>45344.623125</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45095</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>45880</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45571.71736111111</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45880</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46495,7 +46495,7 @@
         <v>44425.40297453704</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
         <v>45575.56686342593</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45575.56820601852</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45699.65424768518</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46738,7 +46738,7 @@
         <v>45844.5775</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46800,7 +46800,7 @@
         <v>45546.46497685185</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45845.49216435185</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45884.38858796296</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>44916</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45170.45921296296</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45520.32887731482</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47157,7 +47157,7 @@
         <v>45870</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47214,7 +47214,7 @@
         <v>44449</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47271,7 +47271,7 @@
         <v>44522</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45546.68743055555</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45343.58587962963</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45211</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45684.5790162037</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45887.56101851852</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45134.68158564815</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45844.57328703703</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45844.57527777777</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
         <v>45884</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>44544</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>45845.4855787037</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47980,7 +47980,7 @@
         <v>45237.67819444444</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45729.76231481481</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>45845.76005787037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45749</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45845.75200231482</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45889.66935185185</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>45889.67577546297</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48389,7 +48389,7 @@
         <v>44473.6343287037</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48446,7 +48446,7 @@
         <v>45889.67290509259</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>44978</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48565,7 +48565,7 @@
         <v>44484</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48622,7 +48622,7 @@
         <v>45471.42659722222</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48679,7 +48679,7 @@
         <v>44868.36924768519</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48741,7 +48741,7 @@
         <v>45645</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48803,7 +48803,7 @@
         <v>45667</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48860,7 +48860,7 @@
         <v>44124</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>45471.52072916667</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>45530</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49031,7 +49031,7 @@
         <v>45831</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>44865.87770833333</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49145,7 +49145,7 @@
         <v>44990</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49202,7 +49202,7 @@
         <v>45698</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49264,7 +49264,7 @@
         <v>45698</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>44946</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45189</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49440,7 +49440,7 @@
         <v>45400.6709837963</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49502,7 +49502,7 @@
         <v>45173</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49559,7 +49559,7 @@
         <v>45372.40246527778</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>44791</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49673,7 +49673,7 @@
         <v>44902</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49735,7 +49735,7 @@
         <v>45079</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49797,7 +49797,7 @@
         <v>45079</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45462</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45575.53331018519</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45575.54489583334</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45399.56596064815</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
         <v>45099.27354166667</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>45685</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>45670.69458333333</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>44308</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50340,7 +50340,7 @@
         <v>45441.48670138889</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>44306.6371412037</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50454,7 +50454,7 @@
         <v>45586.55451388889</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50511,7 +50511,7 @@
         <v>45553</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50573,7 +50573,7 @@
         <v>45646</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>45729.65061342593</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50692,7 +50692,7 @@
         <v>45097.39893518519</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50749,7 +50749,7 @@
         <v>45548</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50811,7 +50811,7 @@
         <v>45548</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45440</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45328</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>45646.63839120371</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51049,7 +51049,7 @@
         <v>45341.56577546296</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -567,7 +567,7 @@
         <v>45615</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
         <v>45252</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>44850.83328703704</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>44375</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>45810.54824074074</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44406</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>45568.63905092593</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45099</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>44320</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>45138</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>45888.67560185185</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>44484</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>45099</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45218</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>45616.38605324074</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45887.5708912037</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>45888.67765046296</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>44472</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>45138</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45615</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44280</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>45021</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>44789</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45670</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>44375</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>44512</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>44713.59363425926</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>44679</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>44320</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>45518</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>45537.64484953704</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>45614.68287037037</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45618.58876157407</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45575.54934027778</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>45698.46697916667</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>45471.56265046296</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>45645</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>45782.5300462963</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>45783.66537037037</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45478.39592592593</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>44949</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>45614.68596064814</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>44536</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>45281</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>45537.64261574074</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>45645</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>45250</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>45827.53077546296</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45832.56153935185</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>45104.3483912037</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>45881.42446759259</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>44522</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45845.75491898148</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>45845.75751157408</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>45475.92849537037</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>45440.3184375</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>44151</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>44242</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>44069</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44069</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44260.30453703704</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>44295.61297453703</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>44123</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>44889.5746875</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>44104</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>44267</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>44126</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>44431.69783564815</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>44853.61925925926</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>44495.87667824074</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>44447.51184027778</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>44453</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>44228</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>44445.4953587963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44126</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>44484</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>44508</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>44284.70511574074</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44271</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44176</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44327</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>44167</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>44503</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>44613</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44462</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>44386</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>44210</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>44280</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>44427.75243055556</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44145</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>44441.66886574074</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>44300</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>44431.69723379629</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>44332</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>44722.78552083333</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>44721.53951388889</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>44862</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>44577.82805555555</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>44171</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>44460</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44481</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>44638</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>44790</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>44754</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>44714</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>44676</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>44627</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>44377</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>44377.44943287037</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>44069</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>44603</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>44630</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>44862</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>44629</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>44713.61145833333</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>44123</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>44375</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>44671</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>44706.65927083333</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         <v>44069</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>44224</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>44260.31335648148</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>44068</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>44113</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>44468.34099537037</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>44085</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44257</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>44259</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44102</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>44102</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         <v>44577.84596064815</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>44418.58454861111</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>44671</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>44505.36354166667</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>44546.67978009259</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>44375</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44187</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>44326</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>44823.37396990741</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>44273</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44325</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>44378.55319444444</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>44071</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>44183</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>44073</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>44076</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44162</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>44522.87423611111</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>44635.51386574074</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>44126</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>44130</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>44357</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44820</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>44085</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44434.74203703704</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>44693.66775462963</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>44484.56523148148</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44691</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>44694.29309027778</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44305</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>44505</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>44490</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>44629</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>44425.40128472223</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>44665</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>44459.57613425926</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>44447</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>44432.68241898148</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>44432</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44594</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>44889.68100694445</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44091</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>44332.74105324074</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>44728</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>44326.7296412037</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>44113</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>44487.51556712963</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>44463</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>44497</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44456</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>44602</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44384.56912037037</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>44650.47945601852</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>44819</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>44453</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>44536</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44733.71126157408</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>44479.58512731481</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>44618</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>44420.60616898148</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>44860</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>44076</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>44636.46935185185</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44389</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>44451</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>44151</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>44873.47148148148</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>44672</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>44088</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>44098</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>44825.99293981482</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>44438.30614583333</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>44665</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>44777</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>44114</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>44451.78710648148</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>44533</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>44088</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>44536</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         <v>44116</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>44179</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44449</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44622.69101851852</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44107</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>44502.49809027778</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44502</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>44875.47543981481</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>44088</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>44208</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>44334.60293981482</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>44481.34877314815</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44268.55900462963</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>44491</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44491</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>44363</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>44511.39611111111</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>44267</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>44376</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>44784</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>44067</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>44607.64115740741</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>44490</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>44698.62354166667</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>44784.38697916667</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>44608</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>44227</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>45565</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>44069</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45310</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>45736.30940972222</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>45714.31533564815</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>44389</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>44539.31923611111</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>44539</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>45411.65641203704</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45008</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>45518.71482638889</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>45113</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>44970</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>44526</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>45571.72288194444</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>44389</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>45229</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>45530</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>45289</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>44531.3575</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>44446</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>44231</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45095</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45377.48265046296</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45538.34460648148</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44967.60165509259</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44389</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44445</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>45439.56605324074</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>44342.39703703704</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>44355</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45664</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45736</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44511</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>45203.510625</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>45274</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45112.67952546296</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>45229.66262731481</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>45280</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>45628.94579861111</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>45107</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>44378.46403935185</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>45532</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>44974.55693287037</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>44602.45490740741</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>44267</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45030</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>45404.55681712963</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>45574.65087962963</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>45085</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>45611.44960648148</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>44890.46174768519</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45334</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45738.43714120371</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>44683</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>45516.59447916667</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45604.58837962963</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>44276</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>44753</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>45229</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45565.40700231482</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>45538.34796296297</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>45384.43418981481</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45646.63482638889</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>45755.68247685185</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>45303</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45140</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45471.38995370371</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45751.50498842593</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>44161</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>44943.73792824074</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>44734.64337962963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>44906.73321759259</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>45047.7181712963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45054</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>44424.61709490741</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45580.73525462963</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>45583</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>45568.62625</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45614.5968287037</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>44984</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>45273</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>45183.48666666666</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45769.17</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45158.41768518519</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>45251.696875</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>45643</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45749</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>45394.51289351852</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45569.35209490741</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44236</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>45653.53664351852</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45139.64328703703</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>45618.59219907408</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45194</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45575.53690972222</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>45575.56256944445</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45618.59456018519</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45488.41480324074</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>45119</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>44946.54424768518</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>45618.58622685185</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45698</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>44853.79818287037</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45568.64523148148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44809</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>45355.70009259259</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45702</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45075.44152777778</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>45310.87931712963</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>45264.38084490741</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45305</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>44979</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>44319</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>45769.98603009259</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45435.57399305556</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>45097.38688657407</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44958.58982638889</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>45344.6027662037</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>45702</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45330</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>44564</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>45219</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45043.40300925926</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44665</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>45327</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>45749.42258101852</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>45608</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>45749</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>45694</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>45751.5056712963</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>45233.42121527778</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>44259</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>45243</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>44981</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45642.66184027777</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>45610.7466087963</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>45243.62420138889</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45243</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>45177.31795138889</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>45211</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>45541.66916666667</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45593.59681712963</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>45538.34193287037</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>45005.35967592592</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>45005.47820601852</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>45628.59233796296</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>45749</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>45749.47251157407</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>45453.36664351852</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44445.55690972223</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>45404.55239583334</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>45404.55601851852</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>45777.42628472222</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>45777.41673611111</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45272.57385416667</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>44546.6679050926</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>45768.49947916667</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45733.60959490741</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>45777</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>45777.43878472222</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>45194</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>45776.65518518518</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>44721.52627314815</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>44876.35706018518</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>45537.64621527777</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>45783.71833333333</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44988</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>45497</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>45567.68003472222</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>45509.73383101852</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45057</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>44803.64361111111</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>45145</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>45534.54032407407</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>45460.46358796296</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>45534.54596064815</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>44410.61837962963</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>45166.68493055556</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>45569.3533912037</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45253</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>45203.45681712963</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45369</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>45785.4253125</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>45229.66430555555</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>45338</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45267.69052083333</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>45635.63706018519</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>44441.70047453704</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>45726.33763888889</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45726.34090277777</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45537.65305555556</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>45159.44525462963</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>45788.42467592593</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>45461.62924768519</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>44378.46857638889</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>45103.53614583334</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
         <v>45077</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45162.5978125</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45744.57851851852</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45537.665</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>45061.53414351852</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>45433.58099537037</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>45691.36253472222</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>45749</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>45279</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>45104.34107638889</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45523.31621527778</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>44833</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>44888.4577662037</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>44928</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
         <v>45272.36168981482</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28676,7 +28676,7 @@
         <v>44902</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>44927.72487268518</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45737.3846412037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45559</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>45108.7553587963</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>45274</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>45786</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>45639.30934027778</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45791.50862268519</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45149</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45744.57673611111</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>45181</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29390,7 +29390,7 @@
         <v>45418.66800925926</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>45523.58565972222</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>45766.33309027777</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>45618</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45173.39315972223</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         <v>45007</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45600.60071759259</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>45036</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>44258</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>45667</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>45546.28121527778</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>45440.5433912037</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>45168.92155092592</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30141,7 +30141,7 @@
         <v>45168.94197916667</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>45741.64491898148</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>44389</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>45518.71048611111</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30379,7 +30379,7 @@
         <v>45518.71202546296</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45518.71591435185</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>45441.30899305556</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>45441.30998842593</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>45793.61047453704</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>45548</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>44979</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>45793.62422453704</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>45456.90869212963</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45795.71300925926</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45795.70912037037</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>45155.5653125</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>45244</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>45645.3712037037</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>45796.44885416667</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>44300</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>45794.33498842592</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45125.41458333333</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>45113</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>45796</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>45794.3419212963</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>44480.58034722223</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>44841</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45796</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31797,7 +31797,7 @@
         <v>45796.45054398148</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>45061.52474537037</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>45170</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>45795.71547453704</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32035,7 +32035,7 @@
         <v>45456.48927083334</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>45562.61158564815</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>44371.47609953704</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>45474.65005787037</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>45511.40297453704</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>44978</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>44963.37709490741</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45201</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>45201.60283564815</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>45329</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>45518.71721064814</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>45547.36590277778</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>45048</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44574.50425925926</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>45610</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44551</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>44389</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>44675</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>45373.30434027778</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>45729.60775462963</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>45618</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>45005</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>45034.5174537037</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>45590.37590277778</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>44909</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>45803</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>45582.57542824074</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33619,7 +33619,7 @@
         <v>45803.39776620371</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>44425</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>45804.45474537037</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45804.67795138889</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>45635.69581018519</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>45376.70292824074</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>44865.600625</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>45804.45584490741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>45103</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>44740.66997685185</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34194,7 +34194,7 @@
         <v>44546.67222222222</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>44431</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45194</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>44908.49152777778</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>45471.40384259259</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>45411.42858796296</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34536,7 +34536,7 @@
         <v>45194</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>45615.69570601852</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>45707</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45575.65721064815</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>45471.52878472222</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>45628.58975694444</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>45148</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>45152.34586805556</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45707</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>45189.38135416667</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>44577.81121527778</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45738.42981481482</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>45519.51627314815</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>44900.36149305556</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>45756.49009259259</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>45099</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>45694</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>44503</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>44553.35407407407</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>45702</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>45575.55570601852</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>45594.63747685185</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>44951.5830324074</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>45373.34383101852</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>45218</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>45131</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36053,7 +36053,7 @@
         <v>45078.82620370371</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>45854</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>45812.56952546296</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>45068</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44457</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36343,7 +36343,7 @@
         <v>44301</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>45590.39471064815</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>45434.65854166666</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>45188</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>45812.57143518519</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>45812.57452546297</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>45812.57604166667</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>45813.68209490741</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45218</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>45266.58394675926</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>45082.31421296296</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37000,7 +37000,7 @@
         <v>45170</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37062,7 +37062,7 @@
         <v>45227.31859953704</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45817.6455324074</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>45384</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>45072</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45575.55273148148</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>45575.5547337963</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>45575.55684027778</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>45537.42240740741</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>45519.52319444445</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>45714</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>45642</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>45412.54541666667</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>45854</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37828,7 +37828,7 @@
         <v>45860.36222222223</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>45387.24732638889</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>45387.2521875</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>45554.7158912037</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>45091.39362268519</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45201</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>45618.58962962963</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>45538</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38304,7 +38304,7 @@
         <v>45860.3857175926</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>45257.48188657407</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44420</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>45265.64142361111</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>45685</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>45614.68083333333</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>45141.76530092592</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>45400.66995370371</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>44389</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45820.61684027778</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>44431</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>45821.59353009259</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>44970.51849537037</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45821.37199074074</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>45119.46452546296</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39179,7 +39179,7 @@
         <v>45194</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>45218.488125</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>44866.79668981482</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45821.46135416667</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39417,7 +39417,7 @@
         <v>44175</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>45821.46486111111</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>45538</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>45821.44521990741</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>45348</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>45729.65171296296</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>45138</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39831,7 +39831,7 @@
         <v>45488.42258101852</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45586</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39950,7 +39950,7 @@
         <v>45827.51862268519</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45826.52024305556</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45316</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45827.56939814815</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>45393.3562962963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>45393.36060185185</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40317,7 +40317,7 @@
         <v>44621.85737268518</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>45827.51753472222</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>45827.51956018519</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>45009.64217592592</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>44566</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>45827.51628472222</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44083</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>45523</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>45831</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>45222</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40907,7 +40907,7 @@
         <v>44949</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>44895</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41021,7 +41021,7 @@
         <v>45587</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>45667</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
         <v>45667</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>45139.63480324074</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>45575.57104166667</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>45874.40503472222</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>45323</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41435,7 +41435,7 @@
         <v>45832.76100694444</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41497,7 +41497,7 @@
         <v>45832.76491898148</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>45106</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41616,7 +41616,7 @@
         <v>45832.49325231482</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41678,7 +41678,7 @@
         <v>45832.51255787037</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>44990</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45832.55810185185</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>44602.45162037037</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41916,7 +41916,7 @@
         <v>45832.72778935185</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>45832.5902662037</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>45832.74418981482</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>45103</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>45357.34521990741</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>45832.49579861111</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45832.51028935185</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45511.39445601852</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45877.64847222222</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42464,7 +42464,7 @@
         <v>44735.62539351852</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42526,7 +42526,7 @@
         <v>45877.63989583333</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>45877.64144675926</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42650,7 +42650,7 @@
         <v>45835.68443287037</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42707,7 +42707,7 @@
         <v>45877.64230324074</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42769,7 +42769,7 @@
         <v>45877.64431712963</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>45877.64776620371</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>45877.65075231482</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42955,7 +42955,7 @@
         <v>45111</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43012,7 +43012,7 @@
         <v>45554.71863425926</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45769.98449074074</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43131,7 +43131,7 @@
         <v>44950</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43188,7 +43188,7 @@
         <v>45072.42776620371</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>44883</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43307,7 +43307,7 @@
         <v>45254.68105324074</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43369,7 +43369,7 @@
         <v>45477.70315972222</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>45525.7374537037</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>45177.33991898148</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>45251</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43602,7 +43602,7 @@
         <v>45404.68190972223</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>45252.78021990741</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>44577.83484953704</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45077</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>45077</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43902,7 +43902,7 @@
         <v>45077</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43964,7 +43964,7 @@
         <v>45393.35787037037</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44026,7 +44026,7 @@
         <v>45762.61817129629</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>45877.64605324074</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>45876.59166666667</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>45107</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44259,7 +44259,7 @@
         <v>44902</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>45870</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44373,7 +44373,7 @@
         <v>45744.32981481482</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44430,7 +44430,7 @@
         <v>45519.52232638889</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
         <v>45107</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44554,7 +44554,7 @@
         <v>45881.43759259259</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>45454.49679398148</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
         <v>44846</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44725,7 +44725,7 @@
         <v>45719.52871527777</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44787,7 +44787,7 @@
         <v>45880.28673611111</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>45880.46056712963</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>45618</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44963,7 +44963,7 @@
         <v>44594.84091435185</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>45645.3737962963</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>45881.59550925926</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>44169</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>44822</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>45274</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>45177.33091435185</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>45574.65189814815</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45880.3172337963</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45496,7 +45496,7 @@
         <v>45838.46456018519</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45838.46408564815</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45620,7 +45620,7 @@
         <v>45881.42791666667</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>45516.4221412037</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45739,7 +45739,7 @@
         <v>45687</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45796,7 +45796,7 @@
         <v>45093.48221064815</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45853,7 +45853,7 @@
         <v>44438</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>45840</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45972,7 +45972,7 @@
         <v>45254</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45769.66260416667</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>45736.308125</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45265.49225694445</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>45344.623125</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45095</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>45880</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45571.71736111111</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45880</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46495,7 +46495,7 @@
         <v>44425.40297453704</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
         <v>45575.56686342593</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45575.56820601852</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45699.65424768518</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46738,7 +46738,7 @@
         <v>45844.5775</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46800,7 +46800,7 @@
         <v>45546.46497685185</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45845.49216435185</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45884.38858796296</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>44916</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45170.45921296296</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45520.32887731482</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47157,7 +47157,7 @@
         <v>45870</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47214,7 +47214,7 @@
         <v>44449</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47271,7 +47271,7 @@
         <v>44522</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45546.68743055555</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45343.58587962963</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45211</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45684.5790162037</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45887.56101851852</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45134.68158564815</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45844.57328703703</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45844.57527777777</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
         <v>45884</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>44544</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>45845.4855787037</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47980,7 +47980,7 @@
         <v>45237.67819444444</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45729.76231481481</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>45845.76005787037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45749</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45845.75200231482</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45889.66935185185</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>45889.67577546297</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48389,7 +48389,7 @@
         <v>44473.6343287037</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48446,7 +48446,7 @@
         <v>45889.67290509259</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>44978</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48565,7 +48565,7 @@
         <v>44484</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48622,7 +48622,7 @@
         <v>45471.42659722222</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48679,7 +48679,7 @@
         <v>44868.36924768519</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48741,7 +48741,7 @@
         <v>45645</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48803,7 +48803,7 @@
         <v>45667</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48860,7 +48860,7 @@
         <v>44124</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>45471.52072916667</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>45530</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49031,7 +49031,7 @@
         <v>45831</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>44865.87770833333</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49145,7 +49145,7 @@
         <v>44990</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49202,7 +49202,7 @@
         <v>45698</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49264,7 +49264,7 @@
         <v>45698</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>44946</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45189</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49440,7 +49440,7 @@
         <v>45400.6709837963</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49502,7 +49502,7 @@
         <v>45173</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49559,7 +49559,7 @@
         <v>45372.40246527778</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>44791</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49673,7 +49673,7 @@
         <v>44902</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49735,7 +49735,7 @@
         <v>45079</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49797,7 +49797,7 @@
         <v>45079</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45462</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45575.53331018519</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45575.54489583334</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45399.56596064815</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
         <v>45099.27354166667</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>45685</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>45670.69458333333</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>44308</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50340,7 +50340,7 @@
         <v>45441.48670138889</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>44306.6371412037</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50454,7 +50454,7 @@
         <v>45586.55451388889</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50511,7 +50511,7 @@
         <v>45553</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50573,7 +50573,7 @@
         <v>45646</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>45729.65061342593</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50692,7 +50692,7 @@
         <v>45097.39893518519</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50749,7 +50749,7 @@
         <v>45548</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50811,7 +50811,7 @@
         <v>45548</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45440</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45328</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>45646.63839120371</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51049,7 +51049,7 @@
         <v>45341.56577546296</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -567,7 +567,7 @@
         <v>45615</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         <v>45252</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>44850.83328703704</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>44375</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>45810.54824074074</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44406</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45568.63905092593</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>45099</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44320</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>45888.67560185185</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>45138</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>44484</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>45888.67765046296</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45887.5708912037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>45218</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>45099</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>45616.38605324074</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>44472</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44789</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>45615</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>44280</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45670</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>45021</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>45138</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>44375</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>44512</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44713.59363425926</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>44679</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>44320</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>45698.46697916667</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>45250</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>45782.5300462963</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45104.3483912037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>45783.66537037037</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>45475.92849537037</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>45614.68287037037</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>44536</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>45614.68596064814</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>45518</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44949</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>45827.53077546296</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>45832.56153935185</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>45881.42446759259</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>45440.3184375</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>45845.75751157408</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>45845.75491898148</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45537.64484953704</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>45575.54934027778</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>45281</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>45478.39592592593</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45645</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>45618.58876157407</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44522</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>45645</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44151</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>44242</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>44260.30453703704</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>44295.61297453703</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>44123</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44889.5746875</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>44104</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>44126</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44267</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44431.69783564815</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>44853.61925925926</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>44495.87667824074</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>44447.51184027778</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44453</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>44228</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44445.4953587963</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44484</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>44126</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44508</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44284.70511574074</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44271</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44176</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>44327</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>44167</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>44503</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>44462</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>44613</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>44386</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>44210</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>44280</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44427.75243055556</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>44145</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44300</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44441.66886574074</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44431.69723379629</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>44332</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44722.78552083333</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>44721.53951388889</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44862</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>44577.82805555555</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>44171</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>44460</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>44481</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>44754</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44714</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>44627</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44790</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>44676</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44638</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44377</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>44377.44943287037</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44630</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>44862</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>44603</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>44629</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>44713.61145833333</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44123</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>44671</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44375</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44706.65927083333</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>44224</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>44113</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>44260.31335648148</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>44468.34099537037</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>44085</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>44102</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44102</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>44257</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44259</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44577.84596064815</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>44671</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>44505.36354166667</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>44273</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>44418.58454861111</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>44546.67978009259</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>44375</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>44187</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>44326</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>44325</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44823.37396990741</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>44378.55319444444</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>44073</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>44183</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44162</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>44076</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>44522.87423611111</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>44635.51386574074</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44126</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44130</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44357</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>44820</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>44085</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44434.74203703704</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44693.66775462963</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>44484.56523148148</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44694.29309027778</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>44305</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>44691</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>44505</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44490</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>44629</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>44425.40128472223</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>44459.57613425926</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>44447</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>44665</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>44432.68241898148</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>44594</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>44432</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>44326.7296412037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>44487.51556712963</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>44332.74105324074</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44602</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>44463</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>44113</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>44497</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>44456</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>44819</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>44650.47945601852</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44384.56912037037</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>44733.71126157408</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>44076</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>44479.58512731481</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>44453</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>44536</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>44618</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>44420.60616898148</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>44860</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>44636.46935185185</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>44389</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>44672</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>44151</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>44098</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>44825.99293981482</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>44438.30614583333</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>44451</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>44873.47148148148</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>44114</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>44665</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44449</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44777</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>44622.69101851852</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44088</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>44451.78710648148</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>44875.47543981481</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>44334.60293981482</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>44491</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>44088</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>44536</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>44116</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>44179</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>44502.49809027778</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>44502</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44208</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>44481.34877314815</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>44107</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>44268.55900462963</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>44491</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>44088</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>44267</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>44376</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>44363</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>44607.64115740741</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>44784</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>44511.39611111111</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>44608</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>44526</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>44389</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>44539.31923611111</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>44539</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>44091</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>44389</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>44490</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>44698.62354166667</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>44446</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>44784.38697916667</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>44889.68100694445</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>44389</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>45338</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>45274</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>45168.92155092592</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45103</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45355.70009259259</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>45119.46452546296</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>45103</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45412.54541666667</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>45194</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>44378.46403935185</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>45729.65171296296</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>45107</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45091.39362268519</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>44300</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45439.56605324074</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>45694</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>44319</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45698</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45698</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>45698</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>45702</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>44301</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45534.54032407407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>45538</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>45615.69570601852</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45384.43418981481</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>45400.6709837963</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>45702</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45222</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>45433.58099537037</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>45776.65518518518</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>45384</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>45435.57399305556</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>44531.3575</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45777.41673611111</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>45243</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45777.43878472222</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45243.62420138889</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45243</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45733.60959490741</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>44890.46174768519</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45777.42628472222</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>45777</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>45554.71863425926</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45471.52878472222</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18433,7 +18433,7 @@
         <v>45518.71048611111</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>45575.53331018519</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>45575.54489583334</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>45061.52474537037</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>45162.5978125</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>45783.71833333333</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>45509.73383101852</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>45279</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>45461.62924768519</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>45519.51627314815</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>45519.52232638889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>44809</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45537.42240740741</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45567.68003472222</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>45460.46358796296</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45107</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>44876.35706018518</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>45104.34107638889</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45786</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>45569.3533912037</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45253</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>45203.45681712963</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>44866.79668981482</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45373.30434027778</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>45267.69052083333</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>45005</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45608</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>44445</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>44169</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>44424.61709490741</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45546.68743055555</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>45454.49679398148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>45785.4253125</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>44902</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>45537.665</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>45229.66430555555</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>45537.65305555556</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>45618</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>45099</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>44551</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45323</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>44480.58034722223</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>45289</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>44981</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45148</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>45141.76530092592</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>45788.42467592593</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>45113</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45546.28121527778</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>45112.67952546296</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>45518.71202546296</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>45518.71591435185</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>45274</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>45653.53664351852</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45791.50862268519</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>45593.59681712963</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>45152.34586805556</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>45643</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45518.71721064814</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45134.68158564815</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45399.56596064815</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>44410.61837962963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>45181</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45614.5968287037</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>45639.30934027778</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45140</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22325,7 +22325,7 @@
         <v>45646.63482638889</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45418.66800925926</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45440.5433912037</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>45667</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>45170.45921296296</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>45793.61047453704</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44389</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>45796.44885416667</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>44883</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45796</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45343.58587962963</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>45795.70912037037</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>45796</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45796.45054398148</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>45794.33498842592</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45794.3419212963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45795.71300925926</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45538.34460648148</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>45441.30899305556</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45441.30998842593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>45559</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>45795.71547453704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>45244</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>45456.48927083334</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>45219</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>45793.62422453704</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45005.35967592592</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45005.47820601852</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>45488.42258101852</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>45729.60775462963</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45330</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>44978</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>45586.55451388889</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>45729.76231481481</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24338,7 +24338,7 @@
         <v>45575.55273148148</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>45575.5547337963</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>45590.37590277778</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>45575.55684027778</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>45575.56686342593</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>45575.56820601852</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>45618</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>45155.5653125</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>45456.90869212963</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>45177.33091435185</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45441.48670138889</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>45618.58622685185</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>44602.45490740741</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>44602.45162037037</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>45373.34383101852</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45329</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>44522</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>45534.54596064815</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>45538</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44621.85737268518</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>45054</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45218</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>45738.42981481482</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>45804.45474537037</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>45803.39776620371</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>45803</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44988</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>45804.45584490741</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>45804.67795138889</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>45393.3562962963</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>45726.33763888889</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>45726.34090277777</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>45571.71736111111</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>44909</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>44544</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44841</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45538.34796296297</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>45218.488125</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>45645.3712037037</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>44124</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45280</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45541.66916666667</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>45519.52319444445</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>45411.65641203704</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>45131</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45310</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>44683</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45667</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>45610</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>44378.46857638889</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>45173</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>44908.49152777778</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45737.3846412037</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>45518.71482638889</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>45749</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>45749</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45812.57452546297</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>45812.57604166667</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45812.57143518519</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45618</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45812.56952546296</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>44574.50425925926</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>45741.64491898148</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>45642</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>45168.94197916667</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44553.35407407407</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>45372.40246527778</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44594.84091435185</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>45007</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>45645.3737962963</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>45400.66995370371</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>45628.59233796296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>45203.510625</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>45860.3857175926</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>45687</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>45574.65189814815</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>45188</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45817.6455324074</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>45201</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>45565</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>45860.36222222223</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45820.61684027778</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>44888.4577662037</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>45562.61158564815</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45565.40700231482</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45404.68190972223</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29410,7 +29410,7 @@
         <v>45553</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>44974.55693287037</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>44949</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>45821.37199074074</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29648,7 +29648,7 @@
         <v>45821.44521990741</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>45821.46486111111</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29772,7 +29772,7 @@
         <v>45586</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>45821.46135416667</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>44943.73792824074</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>45821.59353009259</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44577.83484953704</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>44979</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44675</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>45125.41458333333</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>45201</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>45201.60283564815</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>45061.53414351852</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>44822</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>45826.52024305556</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>45097.39893518519</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>45827.51862268519</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         <v>45173.39315972223</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>45229.66262731481</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>45744.57851851852</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>45194</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>44740.66997685185</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45827.51753472222</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>45827.51956018519</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>45827.56939814815</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>44441.70047453704</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>45394.51289351852</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>45554.7158912037</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>45582.57542824074</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45827.51628472222</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31448,7 +31448,7 @@
         <v>45769.98449074074</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31505,7 +31505,7 @@
         <v>45832.74418981482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>45177.33991898148</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45685</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45387.24732638889</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>45387.2521875</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>44236</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31877,7 +31877,7 @@
         <v>45523</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>45832.51028935185</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>45832.55810185185</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>44420</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45523.58565972222</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>45377.48265046296</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32229,7 +32229,7 @@
         <v>45831</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32286,7 +32286,7 @@
         <v>45832.49325231482</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>45832.51255787037</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>45548</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32472,7 +32472,7 @@
         <v>45548</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>45832.49579861111</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45832.5902662037</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>45569.35209490741</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>45874.40503472222</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>45832.72778935185</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>44445.55690972223</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>44258</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>45095</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>45095</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>45707</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>45251.696875</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44963.37709490741</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>45434.65854166666</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>45265.64142361111</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>45158.41768518519</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44735.62539351852</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>44425</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>45077</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>45266.58394675926</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>45194</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>44967.60165509259</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>45832.76491898148</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>45876.59166666667</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>45832.76100694444</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33952,7 +33952,7 @@
         <v>44267</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34009,7 +34009,7 @@
         <v>45139.63480324074</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34071,7 +34071,7 @@
         <v>44970.51849537037</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>45348</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45870</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>45877.64605324074</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>45880.46056712963</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45877.63989583333</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>45877.64144675926</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>45838.46456018519</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>45099.27354166667</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>45580.73525462963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34671,7 +34671,7 @@
         <v>45835.68443287037</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>45838.46408564815</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>45877.64847222222</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34852,7 +34852,7 @@
         <v>45880.28673611111</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>45233.42121527778</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45877.64230324074</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>45877.64431712963</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>45877.64776620371</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45877.65075231482</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45880.3172337963</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>45749.47251157407</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         <v>45305</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>45840</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35504,7 +35504,7 @@
         <v>45516.4221412037</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45635.69581018519</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45880</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>45881.43759259259</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35737,7 +35737,7 @@
         <v>44950</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35794,7 +35794,7 @@
         <v>45229</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45594.63747685185</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45756.49009259259</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35965,7 +35965,7 @@
         <v>45880</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36022,7 +36022,7 @@
         <v>45881.42791666667</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>45881.59550925926</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>45884.38858796296</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>45870</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36250,7 +36250,7 @@
         <v>45884</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         <v>45328</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>45227.31859953704</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>45357.34521990741</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>45769.98603009259</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45628.58975694444</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>45254.68105324074</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>45344.6027662037</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>45393.36060185185</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45768.49947916667</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45440</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>45034.5174537037</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>44753</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>45194</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>44231</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45369</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37182,7 +37182,7 @@
         <v>45645</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45009.64217592592</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>45520.32887731482</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>44503</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45845.75200231482</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45310.87931712963</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45145</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>45159.44525462963</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>45844.57527777777</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45477.70315972222</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45845.4855787037</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>45887.56101851852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>45845.49216435185</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>45844.5775</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>45488.41480324074</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         <v>45078.82620370371</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45845.76005787037</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>45274</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38238,7 +38238,7 @@
         <v>44970</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38295,7 +38295,7 @@
         <v>45729.65061342593</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>45844.57328703703</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38414,7 +38414,7 @@
         <v>45538.34193287037</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>44803.64361111111</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>45511.39445601852</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45511.40297453704</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45646</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>44951.5830324074</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>45642.66184027777</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>45265.49225694445</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         <v>45889.66935185185</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>45889.67577546297</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>44342.39703703704</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39066,7 +39066,7 @@
         <v>45889.67290509259</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>45831</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39185,7 +39185,7 @@
         <v>45272.57385416667</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>44791</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39299,7 +39299,7 @@
         <v>45079</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39361,7 +39361,7 @@
         <v>45079</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>45694</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45813.68209490741</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>44728</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45272.36168981482</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>45736.308125</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45670.69458333333</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>45684.5790162037</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>45574.65087962963</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>44161</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45537.64621527777</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40008,7 +40008,7 @@
         <v>45635.63706018519</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>45854</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>45895.47704861111</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>45895.4790625</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>45895.48394675926</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>45755.68247685185</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40365,7 +40365,7 @@
         <v>44665</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40422,7 +40422,7 @@
         <v>45149</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>45895.49994212963</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>45895.48927083334</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>45854</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>45870</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>45736</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>45646.63839120371</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45587</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45870</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40950,7 +40950,7 @@
         <v>45471.52072916667</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>45257.48188657407</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>45898.37138888889</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>45170</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45072</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41245,7 +41245,7 @@
         <v>45097.38688657407</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>44546.6679050926</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>45138</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>45113</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45769.17</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>45575.55570601852</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>44546.67222222222</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>44389</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45229</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>45048</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>45047.7181712963</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45471.42659722222</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>44990</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45530</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45547.36590277778</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>44175</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>44227</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45714</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42281,7 +42281,7 @@
         <v>45030</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45685</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>44473.6343287037</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45691.36253472222</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45749</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45194</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>44371.47609953704</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>44355</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>44900.36149305556</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>44449</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45008</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>44511</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45766.33309027777</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45211</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45744.32981481482</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45738.43714120371</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45082.31421296296</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>44566</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>44895</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>44916</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>44389</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>44979</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>44990</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45575.53690972222</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45575.56256944445</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45166.68493055556</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>44259</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45251</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45736.30940972222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>44431</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45077</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>45077</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45077</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>45075.44152777778</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>45744.57673611111</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>45404.55239583334</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>45404.55601851852</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>44946.54424768518</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>44902</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45107</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>44457</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45189</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>44306.6371412037</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45264.38084490741</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45393.35787037037</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>44564</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>44308</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>45106</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>45548</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>44928</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>44425.40297453704</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45769.66260416667</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>44853.79818287037</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45397,7 +45397,7 @@
         <v>45252.78021990741</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45454,7 +45454,7 @@
         <v>45497</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45511,7 +45511,7 @@
         <v>44927.72487268518</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45568,7 +45568,7 @@
         <v>45618.59456018519</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>44906.73321759259</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>44083</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45237.67819444444</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45344.623125</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45614.68083333333</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>45474.65005787037</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>45068</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46039,7 +46039,7 @@
         <v>45610.7466087963</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46096,7 +46096,7 @@
         <v>45749.42258101852</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46153,7 +46153,7 @@
         <v>44577.81121527778</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>45600.60071759259</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46267,7 +46267,7 @@
         <v>45707</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45628.94579861111</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46381,7 +46381,7 @@
         <v>45618.59219907408</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46443,7 +46443,7 @@
         <v>45316</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45177.31795138889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45751.50498842593</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45108.7553587963</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>45751.5056712963</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>45702</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>45211</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46852,7 +46852,7 @@
         <v>44721.52627314815</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>45119</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46971,7 +46971,7 @@
         <v>45583</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45453.36664351852</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>44734.64337962963</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>44946</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>44958.58982638889</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>44978</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45546.46497685185</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>44846</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>45376.70292824074</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>45327</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45590.39471064815</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47618,7 +47618,7 @@
         <v>45254</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45762.61817129629</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47737,7 +47737,7 @@
         <v>45074</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47794,7 +47794,7 @@
         <v>44431</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47851,7 +47851,7 @@
         <v>44868.36924768519</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45189.38135416667</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45749</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45139.64328703703</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45575.65721064815</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45575.57104166667</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45471.38995370371</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45057</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45085</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>45093.48221064815</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>44865.600625</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>45303</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>45523.31621527778</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>44865.87770833333</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>45667</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45170</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>45103.53614583334</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48845,7 +48845,7 @@
         <v>45036</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48902,7 +48902,7 @@
         <v>45699.65424768518</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48959,7 +48959,7 @@
         <v>45411.42858796296</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49016,7 +49016,7 @@
         <v>45072.42776620371</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49078,7 +49078,7 @@
         <v>44902</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49135,7 +49135,7 @@
         <v>45611.44960648148</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49192,7 +49192,7 @@
         <v>45043.40300925926</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45604.58837962963</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49306,7 +49306,7 @@
         <v>45749</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45525.7374537037</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49420,7 +49420,7 @@
         <v>45532</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>45667</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45719.52871527777</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>44276</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>45183.48666666666</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>45664</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>44833</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49824,7 +49824,7 @@
         <v>44484</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>45568.64523148148</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49943,7 +49943,7 @@
         <v>45341.56577546296</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50005,7 +50005,7 @@
         <v>45334</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>45273</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50119,7 +50119,7 @@
         <v>45404.55681712963</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45530</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45218</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>45462</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
         <v>44438</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50419,7 +50419,7 @@
         <v>45516.59447916667</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50476,7 +50476,7 @@
         <v>45568.62625</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50538,7 +50538,7 @@
         <v>45618.58962962963</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>44984</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50657,7 +50657,7 @@
         <v>45111</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>45471.40384259259</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45714.31533564815</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -567,7 +567,7 @@
         <v>45615</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         <v>45252</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>44850.83328703704</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>44375</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>45810.54824074074</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44406</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45568.63905092593</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>45099</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44320</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>45888.67560185185</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>45138</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>44484</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>45888.67765046296</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45887.5708912037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>45218</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>45099</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>45616.38605324074</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>44472</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44789</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>45615</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>44280</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45670</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>45021</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>45138</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>44375</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>44512</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44713.59363425926</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>44679</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>44320</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>45698.46697916667</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>45250</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>45782.5300462963</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45104.3483912037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>45783.66537037037</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>45475.92849537037</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>45614.68287037037</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>44536</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>45614.68596064814</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>45518</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44949</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>45827.53077546296</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>45832.56153935185</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>45881.42446759259</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>45440.3184375</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>45845.75751157408</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>45845.75491898148</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45537.64484953704</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>45575.54934027778</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>45281</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>45478.39592592593</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45645</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>45618.58876157407</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44522</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>45645</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>44151</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>44242</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>44260.30453703704</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>44295.61297453703</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>44123</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44889.5746875</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>44104</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>44126</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44267</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44431.69783564815</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>44853.61925925926</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>44495.87667824074</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>44447.51184027778</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44453</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>44228</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44445.4953587963</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44484</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>44126</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44508</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44284.70511574074</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44271</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44176</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>44327</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>44167</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>44503</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>44462</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>44613</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>44386</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>44210</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>44280</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44427.75243055556</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>44145</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44300</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44441.66886574074</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44431.69723379629</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>44332</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44722.78552083333</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>44721.53951388889</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44862</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>44577.82805555555</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>44171</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>44460</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>44481</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>44754</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44714</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>44627</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44790</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>44676</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44638</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44377</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>44377.44943287037</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44630</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>44862</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>44603</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>44629</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>44713.61145833333</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44123</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>44671</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44375</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44706.65927083333</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>44224</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>44113</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>44260.31335648148</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>44468.34099537037</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>44085</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>44102</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44102</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>44257</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44259</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44577.84596064815</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>44671</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>44505.36354166667</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>44273</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>44418.58454861111</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>44546.67978009259</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>44375</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>44187</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>44326</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>44325</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44823.37396990741</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>44378.55319444444</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>44073</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>44183</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44162</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>44076</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>44522.87423611111</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>44635.51386574074</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44126</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44130</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44357</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>44820</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>44085</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>44434.74203703704</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44693.66775462963</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>44484.56523148148</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44694.29309027778</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>44305</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>44691</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>44505</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44490</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>44629</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>44425.40128472223</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>44459.57613425926</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>44447</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>44665</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>44432.68241898148</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>44594</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>44432</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>44326.7296412037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>44487.51556712963</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>44332.74105324074</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44602</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>44463</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>44113</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>44497</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>44456</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>44819</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>44650.47945601852</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44384.56912037037</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>44733.71126157408</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>44076</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>44479.58512731481</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>44453</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>44536</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>44618</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>44420.60616898148</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>44860</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>44636.46935185185</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>44389</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>44672</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>44151</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>44098</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>44825.99293981482</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>44438.30614583333</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>44451</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>44873.47148148148</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>44114</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>44665</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44449</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44777</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>44622.69101851852</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44088</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>44451.78710648148</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>44875.47543981481</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>44334.60293981482</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>44491</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>44088</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>44536</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>44116</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>44179</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>44502.49809027778</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>44502</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44208</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>44481.34877314815</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>44107</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>44268.55900462963</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>44491</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>44088</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>44267</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>44376</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>44363</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>44607.64115740741</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>44784</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>44511.39611111111</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>44608</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>44526</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>44389</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>44539.31923611111</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>44539</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>44091</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>44389</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>44490</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>44698.62354166667</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>44446</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>44784.38697916667</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>44889.68100694445</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>44389</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>45338</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>45274</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>45168.92155092592</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45103</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45355.70009259259</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>45119.46452546296</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>45103</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45412.54541666667</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>45194</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>44378.46403935185</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>45729.65171296296</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>45107</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45091.39362268519</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>44300</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45439.56605324074</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>45694</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>44319</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45698</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45698</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>45698</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>45702</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>44301</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45534.54032407407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>45538</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>45615.69570601852</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45384.43418981481</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>45400.6709837963</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>45702</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45222</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>45433.58099537037</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>45776.65518518518</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>45384</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>45435.57399305556</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>44531.3575</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45777.41673611111</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>45243</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45777.43878472222</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45243.62420138889</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45243</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45733.60959490741</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>44890.46174768519</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45777.42628472222</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>45777</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>45554.71863425926</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45471.52878472222</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18433,7 +18433,7 @@
         <v>45518.71048611111</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>45575.53331018519</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>45575.54489583334</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>45061.52474537037</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>45162.5978125</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>45783.71833333333</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>45509.73383101852</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>45279</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>45461.62924768519</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>45519.51627314815</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>45519.52232638889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>44809</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45537.42240740741</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45567.68003472222</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>45460.46358796296</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45107</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>44876.35706018518</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>45104.34107638889</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45786</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>45569.3533912037</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45253</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>45203.45681712963</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>44866.79668981482</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45373.30434027778</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>45267.69052083333</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>45005</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45608</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>44445</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>44169</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>44424.61709490741</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45546.68743055555</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>45454.49679398148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>45785.4253125</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>44902</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>45537.665</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>45229.66430555555</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>45537.65305555556</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>45618</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>45099</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>44551</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45323</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>44480.58034722223</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>45289</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>44981</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45148</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>45141.76530092592</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>45788.42467592593</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>45113</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45546.28121527778</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>45112.67952546296</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>45518.71202546296</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>45518.71591435185</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>45274</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>45653.53664351852</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45791.50862268519</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>45593.59681712963</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>45152.34586805556</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>45643</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45518.71721064814</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45134.68158564815</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45399.56596064815</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>44410.61837962963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>45181</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45614.5968287037</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>45639.30934027778</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45140</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22325,7 +22325,7 @@
         <v>45646.63482638889</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45418.66800925926</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45440.5433912037</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>45667</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>45170.45921296296</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>45793.61047453704</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44389</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>45796.44885416667</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>44883</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45796</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45343.58587962963</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>45795.70912037037</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>45796</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45796.45054398148</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>45794.33498842592</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45794.3419212963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45795.71300925926</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45538.34460648148</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>45441.30899305556</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45441.30998842593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>45559</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>45795.71547453704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>45244</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>45456.48927083334</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>45219</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>45793.62422453704</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45005.35967592592</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45005.47820601852</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>45488.42258101852</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>45729.60775462963</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45330</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>44978</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>45586.55451388889</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>45729.76231481481</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24338,7 +24338,7 @@
         <v>45575.55273148148</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>45575.5547337963</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>45590.37590277778</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>45575.55684027778</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>45575.56686342593</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>45575.56820601852</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>45618</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>45155.5653125</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>45456.90869212963</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>45177.33091435185</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45441.48670138889</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>45618.58622685185</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>44602.45490740741</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>44602.45162037037</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>45373.34383101852</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45329</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>44522</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>45534.54596064815</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>45538</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44621.85737268518</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>45054</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45218</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>45738.42981481482</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>45804.45474537037</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>45803.39776620371</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>45803</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44988</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>45804.45584490741</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>45804.67795138889</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>45393.3562962963</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>45726.33763888889</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>45726.34090277777</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>45571.71736111111</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>44909</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>44544</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44841</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45538.34796296297</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>45218.488125</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>45645.3712037037</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>44124</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45280</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45541.66916666667</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>45519.52319444445</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>45411.65641203704</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>45131</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45310</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>44683</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45667</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>45610</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>44378.46857638889</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>45173</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>44908.49152777778</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45737.3846412037</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>45518.71482638889</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>45749</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>45749</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45812.57452546297</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>45812.57604166667</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45812.57143518519</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45618</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45812.56952546296</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>44574.50425925926</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>45741.64491898148</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>45642</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>45168.94197916667</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44553.35407407407</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>45372.40246527778</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44594.84091435185</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>45007</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>45645.3737962963</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>45400.66995370371</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>45628.59233796296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>45203.510625</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>45860.3857175926</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>45687</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>45574.65189814815</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>45188</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45817.6455324074</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>45201</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>45565</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>45860.36222222223</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45820.61684027778</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>44888.4577662037</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>45562.61158564815</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45565.40700231482</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45404.68190972223</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29410,7 +29410,7 @@
         <v>45553</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>44974.55693287037</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>44949</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>45821.37199074074</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29648,7 +29648,7 @@
         <v>45821.44521990741</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>45821.46486111111</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29772,7 +29772,7 @@
         <v>45586</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>45821.46135416667</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>44943.73792824074</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>45821.59353009259</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44577.83484953704</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>44979</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44675</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>45125.41458333333</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>45201</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>45201.60283564815</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>45061.53414351852</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>44822</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>45826.52024305556</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>45097.39893518519</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>45827.51862268519</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         <v>45173.39315972223</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>45229.66262731481</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>45744.57851851852</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>45194</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>44740.66997685185</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45827.51753472222</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>45827.51956018519</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>45827.56939814815</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>44441.70047453704</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>45394.51289351852</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>45554.7158912037</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>45582.57542824074</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45827.51628472222</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31448,7 +31448,7 @@
         <v>45769.98449074074</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31505,7 +31505,7 @@
         <v>45832.74418981482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>45177.33991898148</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45685</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45387.24732638889</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>45387.2521875</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>44236</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31877,7 +31877,7 @@
         <v>45523</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>45832.51028935185</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>45832.55810185185</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>44420</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45523.58565972222</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>45377.48265046296</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32229,7 +32229,7 @@
         <v>45831</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32286,7 +32286,7 @@
         <v>45832.49325231482</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>45832.51255787037</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>45548</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32472,7 +32472,7 @@
         <v>45548</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>45832.49579861111</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45832.5902662037</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>45569.35209490741</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>45874.40503472222</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>45832.72778935185</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>44445.55690972223</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>44258</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>45095</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>45095</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>45707</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>45251.696875</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44963.37709490741</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>45434.65854166666</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>45265.64142361111</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>45158.41768518519</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44735.62539351852</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>44425</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>45077</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>45266.58394675926</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>45194</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>44967.60165509259</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>45832.76491898148</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>45876.59166666667</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>45832.76100694444</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33952,7 +33952,7 @@
         <v>44267</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34009,7 +34009,7 @@
         <v>45139.63480324074</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34071,7 +34071,7 @@
         <v>44970.51849537037</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>45348</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45870</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>45877.64605324074</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>45880.46056712963</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45877.63989583333</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>45877.64144675926</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>45838.46456018519</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>45099.27354166667</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>45580.73525462963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34671,7 +34671,7 @@
         <v>45835.68443287037</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>45838.46408564815</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>45877.64847222222</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34852,7 +34852,7 @@
         <v>45880.28673611111</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>45233.42121527778</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45877.64230324074</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>45877.64431712963</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>45877.64776620371</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45877.65075231482</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45880.3172337963</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>45749.47251157407</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         <v>45305</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>45840</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35504,7 +35504,7 @@
         <v>45516.4221412037</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45635.69581018519</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45880</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>45881.43759259259</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35737,7 +35737,7 @@
         <v>44950</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35794,7 +35794,7 @@
         <v>45229</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45594.63747685185</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45756.49009259259</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35965,7 +35965,7 @@
         <v>45880</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36022,7 +36022,7 @@
         <v>45881.42791666667</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>45881.59550925926</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>45884.38858796296</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>45870</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36250,7 +36250,7 @@
         <v>45884</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         <v>45328</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>45227.31859953704</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>45357.34521990741</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>45769.98603009259</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45628.58975694444</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>45254.68105324074</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>45344.6027662037</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>45393.36060185185</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45768.49947916667</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45440</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>45034.5174537037</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>44753</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>45194</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>44231</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45369</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37182,7 +37182,7 @@
         <v>45645</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45009.64217592592</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>45520.32887731482</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>44503</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45845.75200231482</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45310.87931712963</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45145</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>45159.44525462963</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>45844.57527777777</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45477.70315972222</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45845.4855787037</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>45887.56101851852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>45845.49216435185</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>45844.5775</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>45488.41480324074</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         <v>45078.82620370371</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45845.76005787037</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>45274</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38238,7 +38238,7 @@
         <v>44970</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38295,7 +38295,7 @@
         <v>45729.65061342593</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>45844.57328703703</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38414,7 +38414,7 @@
         <v>45538.34193287037</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>44803.64361111111</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>45511.39445601852</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45511.40297453704</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45646</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>44951.5830324074</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>45642.66184027777</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>45265.49225694445</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         <v>45889.66935185185</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>45889.67577546297</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>44342.39703703704</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39066,7 +39066,7 @@
         <v>45889.67290509259</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>45831</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39185,7 +39185,7 @@
         <v>45272.57385416667</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>44791</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39299,7 +39299,7 @@
         <v>45079</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39361,7 +39361,7 @@
         <v>45079</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>45694</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45813.68209490741</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>44728</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45272.36168981482</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>45736.308125</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45670.69458333333</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>45684.5790162037</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>45574.65087962963</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>44161</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45537.64621527777</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40008,7 +40008,7 @@
         <v>45635.63706018519</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>45854</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>45895.47704861111</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>45895.4790625</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>45895.48394675926</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>45755.68247685185</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40365,7 +40365,7 @@
         <v>44665</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40422,7 +40422,7 @@
         <v>45149</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>45895.49994212963</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>45895.48927083334</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>45854</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>45870</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>45736</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>45646.63839120371</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45587</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45870</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40950,7 +40950,7 @@
         <v>45471.52072916667</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>45257.48188657407</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>45898.37138888889</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>45170</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45072</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41245,7 +41245,7 @@
         <v>45097.38688657407</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>44546.6679050926</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>45138</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>45113</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45769.17</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>45575.55570601852</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>44546.67222222222</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>44389</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45229</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>45048</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>45047.7181712963</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45471.42659722222</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>44990</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45530</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45547.36590277778</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>44175</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>44227</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45714</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42281,7 +42281,7 @@
         <v>45030</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45685</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>44473.6343287037</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45691.36253472222</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45749</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45194</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>44371.47609953704</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>44355</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>44900.36149305556</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>44449</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45008</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>44511</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45766.33309027777</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45211</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45744.32981481482</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45738.43714120371</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45082.31421296296</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>44566</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>44895</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>44916</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>44389</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>44979</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>44990</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45575.53690972222</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45575.56256944445</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45166.68493055556</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>44259</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45251</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45736.30940972222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>44431</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45077</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>45077</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45077</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>45075.44152777778</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>45744.57673611111</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>45404.55239583334</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>45404.55601851852</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>44946.54424768518</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>44902</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45107</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>44457</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45189</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>44306.6371412037</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45264.38084490741</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45393.35787037037</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>44564</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>44308</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>45106</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>45548</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>44928</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>44425.40297453704</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45769.66260416667</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>44853.79818287037</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45397,7 +45397,7 @@
         <v>45252.78021990741</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45454,7 +45454,7 @@
         <v>45497</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45511,7 +45511,7 @@
         <v>44927.72487268518</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45568,7 +45568,7 @@
         <v>45618.59456018519</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>44906.73321759259</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>44083</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45237.67819444444</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45344.623125</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45614.68083333333</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>45474.65005787037</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>45068</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46039,7 +46039,7 @@
         <v>45610.7466087963</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46096,7 +46096,7 @@
         <v>45749.42258101852</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46153,7 +46153,7 @@
         <v>44577.81121527778</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>45600.60071759259</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46267,7 +46267,7 @@
         <v>45707</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45628.94579861111</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46381,7 +46381,7 @@
         <v>45618.59219907408</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46443,7 +46443,7 @@
         <v>45316</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45177.31795138889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45751.50498842593</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45108.7553587963</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>45751.5056712963</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>45702</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>45211</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46852,7 +46852,7 @@
         <v>44721.52627314815</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>45119</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46971,7 +46971,7 @@
         <v>45583</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45453.36664351852</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>44734.64337962963</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>44946</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>44958.58982638889</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>44978</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45546.46497685185</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>44846</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>45376.70292824074</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>45327</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45590.39471064815</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47618,7 +47618,7 @@
         <v>45254</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45762.61817129629</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47737,7 +47737,7 @@
         <v>45074</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47794,7 +47794,7 @@
         <v>44431</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47851,7 +47851,7 @@
         <v>44868.36924768519</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45189.38135416667</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45749</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45139.64328703703</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45575.65721064815</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45575.57104166667</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45471.38995370371</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45057</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45085</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>45093.48221064815</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>44865.600625</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>45303</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>45523.31621527778</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>44865.87770833333</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>45667</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45170</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>45103.53614583334</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48845,7 +48845,7 @@
         <v>45036</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48902,7 +48902,7 @@
         <v>45699.65424768518</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48959,7 +48959,7 @@
         <v>45411.42858796296</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49016,7 +49016,7 @@
         <v>45072.42776620371</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49078,7 +49078,7 @@
         <v>44902</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49135,7 +49135,7 @@
         <v>45611.44960648148</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49192,7 +49192,7 @@
         <v>45043.40300925926</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45604.58837962963</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49306,7 +49306,7 @@
         <v>45749</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45525.7374537037</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49420,7 +49420,7 @@
         <v>45532</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>45667</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45719.52871527777</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>44276</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>45183.48666666666</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>45664</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>44833</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49824,7 +49824,7 @@
         <v>44484</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>45568.64523148148</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49943,7 +49943,7 @@
         <v>45341.56577546296</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50005,7 +50005,7 @@
         <v>45334</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>45273</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50119,7 +50119,7 @@
         <v>45404.55681712963</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45530</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45218</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>45462</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
         <v>44438</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50419,7 +50419,7 @@
         <v>45516.59447916667</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50476,7 +50476,7 @@
         <v>45568.62625</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50538,7 +50538,7 @@
         <v>45618.58962962963</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>44984</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50657,7 +50657,7 @@
         <v>45111</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>45471.40384259259</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45714.31533564815</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -567,7 +567,7 @@
         <v>45615</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         <v>45252</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>45905.90649305555</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>44850.83328703704</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44375</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>45810.54824074074</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>45905.90519675926</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44406</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45099</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>45905.89554398148</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45568.63905092593</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44320</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45138</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45888.67560185185</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>44484</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45099</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45887.5708912037</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>45888.67765046296</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>45616.38605324074</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>45905.90789351852</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>45905.83755787037</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45218</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>44472</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>44280</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>45138</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>45021</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>44789</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>45670</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>45905.88938657408</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>45615</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>44375</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>44512</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>44713.59363425926</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>44679</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>44320</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45518</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45782.5300462963</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>45783.66537037037</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>45575.54934027778</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>45645</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>45478.39592592593</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45614.68596064814</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>45827.53077546296</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>44949</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>45832.56153935185</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>44536</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>45881.42446759259</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>45845.75491898148</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>45845.75751157408</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>45537.64484953704</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>45250</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>45281</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>45645</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45104.3483912037</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>44522</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>45475.92849537037</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45440.3184375</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45614.68287037037</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>45618.58876157407</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>45698.46697916667</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>44151</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>44242</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>44260.30453703704</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>44295.61297453703</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>44123</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>44889.5746875</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>44104</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44126</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44267</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44431.69783564815</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>44853.61925925926</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>44495.87667824074</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>44447.51184027778</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44453</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44228</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>44445.4953587963</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44484</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>44126</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>44508</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>44284.70511574074</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>44271</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>44327</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>44176</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44167</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44503</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44613</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44386</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44462</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>44210</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>44280</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>44427.75243055556</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44145</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>44441.66886574074</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>44300</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>44431.69723379629</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>44332</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>44722.78552083333</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>44721.53951388889</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44862</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>44577.82805555555</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>44171</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>44460</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>44481</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>44754</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>44714</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>44627</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>44790</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>44638</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>44676</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>44377</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>44377.44943287037</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>44630</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>44603</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>44862</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>44629</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>44713.61145833333</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44123</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>44375</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>44671</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>44706.65927083333</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>44224</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>44260.31335648148</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>44102</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>44102</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>44113</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>44468.34099537037</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>44085</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>44257</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>44259</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>44577.84596064815</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>44418.58454861111</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>44671</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>44505.36354166667</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44273</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>44375</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>44546.67978009259</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>44187</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>44326</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44823.37396990741</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44325</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>44378.55319444444</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>44183</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>44162</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44522.87423611111</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44635.51386574074</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>44126</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>44130</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>44357</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44820</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>44085</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>44434.74203703704</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>44693.66775462963</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44484.56523148148</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>44694.29309027778</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>44691</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44305</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>44505</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44490</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44629</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44425.40128472223</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>44665</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44447</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>44459.57613425926</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>44432.68241898148</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>44432</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>44594</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>44326.7296412037</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>44463</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44487.51556712963</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>44497</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44456</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>44650.47945601852</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44819</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>44384.56912037037</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44733.71126157408</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>44453</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>44536</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>44420.60616898148</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>44860</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44479.58512731481</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44618</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>44389</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>44636.46935185185</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>44672</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>44098</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44825.99293981482</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44151</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>44438.30614583333</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>44114</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>44449</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>44622.69101851852</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>44665</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>44777</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>44875.47543981481</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>44334.60293981482</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>44451.78710648148</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>44451</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>44491</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>44873.47148148148</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>44088</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>44502.49809027778</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>44502</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>44208</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>44481.34877314815</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44088</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>44536</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>44107</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>44116</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>44179</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>44268.55900462963</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>44491</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>44088</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>44363</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>44784</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>44511.39611111111</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>44267</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>44376</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>44091</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>44607.64115740741</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>44608</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>44332.74105324074</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>44389</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>44539.31923611111</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>44539</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>44113</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>44490</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>44698.62354166667</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>44784.38697916667</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>45404.55681712963</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>44526</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44389</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45611.44960648148</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44446</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>44889.68100694445</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>44683</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45310</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>45736.30940972222</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45604.58837962963</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45411.65641203704</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>45518.71482638889</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>45355.70009259259</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>45702</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>44602</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>45384.43418981481</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>45646.63482638889</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>45702</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>44564</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45219</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>45755.68247685185</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45140</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>44979</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>44665</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44319</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>45211</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45593.59681712963</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45751.50498842593</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>45749</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
         <v>45453.36664351852</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>44445.55690972223</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>45777.42628472222</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>45777.41673611111</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45733.60959490741</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>45777</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>45777.43878472222</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>45769.98603009259</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45776.65518518518</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>44943.73792824074</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>45435.57399305556</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>45054</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44958.58982638889</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>45580.73525462963</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>45583</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>45783.71833333333</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>45043.40300925926</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45183.48666666666</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>45769.17</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45158.41768518519</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>45567.68003472222</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>45509.73383101852</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>45460.46358796296</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>45694</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45530</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45194</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45569.3533912037</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>45751.5056712963</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>45253</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>45074</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>45575.53690972222</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>45575.56256944445</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         <v>45203.45681712963</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>45289</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45233.42121527778</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>45785.4253125</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>44531.3575</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45488.41480324074</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>45229.66430555555</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45267.69052083333</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>44981</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>45642.66184027777</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>44853.79818287037</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45568.64523148148</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>44967.60165509259</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>44389</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>44445</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>45439.56605324074</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
         <v>45538.34193287037</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>45005.35967592592</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>45005.47820601852</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>45537.65305555556</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45628.59233796296</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>45112.67952546296</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>45075.44152777778</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>45404.55239583334</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45404.55601851852</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>45310.87931712963</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>44546.6679050926</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>45788.42467592593</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>45768.49947916667</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>45194</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>45537.665</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>44721.52627314815</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>44876.35706018518</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45104.34107638889</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45057</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45145</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45305</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45107</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>44378.46403935185</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45786</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>44410.61837962963</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>45097.38688657407</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>45344.6027662037</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>45330</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>45639.30934027778</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>45791.50862268519</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45532</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>45166.68493055556</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>44974.55693287037</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45327</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45030</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45749.42258101852</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>45181</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>45608</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45749</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>45418.66800925926</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45338</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>45618</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45635.63706018519</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>44441.70047453704</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>44259</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>45243</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45667</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>45726.33763888889</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45726.34090277777</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>45546.28121527778</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45440.5433912037</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45610.7466087963</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45243.62420138889</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>45243</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45177.31795138889</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45541.66916666667</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>45159.44525462963</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>45103.53614583334</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>45793.61047453704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>45749.47251157407</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>45061.53414351852</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23948,7 +23948,7 @@
         <v>45272.57385416667</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>45279</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24062,7 +24062,7 @@
         <v>45523.31621527778</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>44833</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>45272.36168981482</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>44927.72487268518</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45737.3846412037</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>45559</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>45274</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>45793.62422453704</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45456.90869212963</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>45795.71300925926</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>45149</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44988</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
         <v>45497</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45795.70912037037</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>45155.5653125</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45523.58565972222</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>45244</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>45766.33309027777</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>44803.64361111111</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>45007</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>45600.60071759259</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>45036</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>44258</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>45534.54032407407</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>45796.44885416667</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>45794.33498842592</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>45796</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>45534.54596064815</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45794.3419212963</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45369</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>45796</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>45796.45054398148</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>45741.64491898148</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44389</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>45518.71048611111</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>45518.71202546296</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>45518.71591435185</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26303,7 +26303,7 @@
         <v>45548</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45795.71547453704</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45456.48927083334</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45461.62924768519</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>44378.46857638889</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>45077</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>45162.5978125</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>45744.57851851852</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>45433.58099537037</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45691.36253472222</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45749</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44888.4577662037</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45729.60775462963</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44928</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>45618</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44902</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>45108.7553587963</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45590.37590277778</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>45125.41458333333</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>45113</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>45803</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>45744.57673611111</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>44841</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45061.52474537037</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45170</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>45803.39776620371</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>45562.61158564815</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45173.39315972223</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>44371.47609953704</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>45474.65005787037</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45511.40297453704</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>44978</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45168.92155092592</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>45168.94197916667</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28281,7 +28281,7 @@
         <v>45441.30899305556</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
         <v>45441.30998842593</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>44963.37709490741</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>45804.45474537037</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>45804.67795138889</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>44979</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28633,7 +28633,7 @@
         <v>44389</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45373.30434027778</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>45005</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>45804.45584490741</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>45645.3712037037</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>45034.5174537037</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>44300</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>44909</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>44480.58034722223</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>45582.57542824074</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44425</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45635.69581018519</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>45201</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>45201.60283564815</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>45329</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>45518.71721064814</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44740.66997685185</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45547.36590277778</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44431</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>45048</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44574.50425925926</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>45812.56952546296</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45411.42858796296</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>45194</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>45610</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45615.69570601852</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45628.58975694444</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>45812.57143518519</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45812.57452546297</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>45812.57604166667</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>45707</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44551</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30517,7 +30517,7 @@
         <v>45756.49009259259</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30574,7 +30574,7 @@
         <v>45817.6455324074</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>44675</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>45702</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>45575.55570601852</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45218</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>44457</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>44301</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>45590.39471064815</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>45820.61684027778</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>45821.59353009259</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>45821.37199074074</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>45821.46135416667</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>45821.46486111111</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>45821.44521990741</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45434.65854166666</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45082.31421296296</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45827.51862268519</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>45826.52024305556</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45376.70292824074</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>44865.600625</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45827.56939814815</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>45827.51753472222</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>45827.51956018519</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>45827.51628472222</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>45523</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>45831</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45874.40503472222</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>45103</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>45832.76100694444</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>45832.76491898148</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>45832.49325231482</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>45832.51255787037</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>45832.55810185185</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>44546.67222222222</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>45832.72778935185</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>45832.5902662037</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32746,7 +32746,7 @@
         <v>45832.74418981482</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45832.49579861111</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>45832.51028935185</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>45877.64847222222</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32994,7 +32994,7 @@
         <v>45877.63989583333</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>45877.64144675926</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33118,7 +33118,7 @@
         <v>45835.68443287037</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>45877.64230324074</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>45877.64431712963</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>45877.64776620371</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>45877.65075231482</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>45194</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44908.49152777778</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>45471.40384259259</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>45877.64605324074</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>45876.59166666667</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45870</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45881.43759259259</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33827,7 +33827,7 @@
         <v>45880.28673611111</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33884,7 +33884,7 @@
         <v>45880.46056712963</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>45072</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>45881.59550925926</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45880.3172337963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>45838.46456018519</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>45838.46408564815</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>45881.42791666667</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34298,7 +34298,7 @@
         <v>45516.4221412037</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34360,7 +34360,7 @@
         <v>45840</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34417,7 +34417,7 @@
         <v>45707</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>45880</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>45880</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34588,7 +34588,7 @@
         <v>45575.65721064815</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>45844.5775</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>45845.49216435185</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>45884.38858796296</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>45520.32887731482</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>45471.52878472222</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>45870</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45537.42240740741</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>45519.52319444445</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>45887.56101851852</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>45844.57328703703</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>45844.57527777777</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>45884</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>45845.4855787037</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>45148</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>45152.34586805556</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35540,7 +35540,7 @@
         <v>45412.54541666667</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>45845.76005787037</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
         <v>45387.24732638889</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>45387.2521875</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>45554.7158912037</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45845.75200231482</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>45889.66935185185</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>45889.67577546297</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>45889.67290509259</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36073,7 +36073,7 @@
         <v>45831</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         <v>45189.38135416667</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36187,7 +36187,7 @@
         <v>44577.81121527778</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36244,7 +36244,7 @@
         <v>45141.76530092592</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>45400.66995370371</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>45813.68209490741</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36420,7 +36420,7 @@
         <v>44389</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45738.42981481482</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>45519.51627314815</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>44728</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>45694</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36710,7 +36710,7 @@
         <v>44900.36149305556</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36767,7 +36767,7 @@
         <v>45895.49994212963</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36829,7 +36829,7 @@
         <v>45895.47704861111</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         <v>45895.4790625</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>45895.48394675926</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>45670.69458333333</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>45895.48927083334</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37134,7 +37134,7 @@
         <v>45537.64621527777</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>44970.51849537037</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>45854</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>45870</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37367,7 +37367,7 @@
         <v>45870</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45194</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>45854</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>45099</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>44503</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>45218.488125</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>45898.37138888889</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>44553.35407407407</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>45594.63747685185</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>45899.38057870371</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>44866.79668981482</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>44175</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>45538</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45860.3857175926</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>45860.36222222223</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38232,7 +38232,7 @@
         <v>45903.37475694445</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44951.5830324074</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45373.34383101852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>45587</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>45902.3406712963</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>45131</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>45078.82620370371</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45068</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38698,7 +38698,7 @@
         <v>45586</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>45905.89236111111</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45905.89329861111</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>45188</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45218</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>45266.58394675926</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>44621.85737268518</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>45170</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39179,7 +39179,7 @@
         <v>45009.64217592592</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>45905.89143518519</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>44566</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45227.31859953704</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>44083</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>45384</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39531,7 +39531,7 @@
         <v>45575.55273148148</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>45575.5547337963</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>45575.55684027778</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>45667</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>45714</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39831,7 +39831,7 @@
         <v>45667</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39893,7 +39893,7 @@
         <v>45642</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39950,7 +39950,7 @@
         <v>45139.63480324074</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45575.57104166667</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45091.39362268519</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45201</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45618.58962962963</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>45538</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44602.45162037037</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>45257.48188657407</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40426,7 +40426,7 @@
         <v>44420</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>45103</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40540,7 +40540,7 @@
         <v>45265.64142361111</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         <v>45685</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>45614.68083333333</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40711,7 +40711,7 @@
         <v>45511.39445601852</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>44735.62539351852</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>44431</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45119.46452546296</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40949,7 +40949,7 @@
         <v>45111</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41006,7 +41006,7 @@
         <v>44950</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>45348</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>44883</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45254.68105324074</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45729.65171296296</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45138</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41358,7 +41358,7 @@
         <v>45525.7374537037</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45177.33991898148</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41477,7 +41477,7 @@
         <v>45488.42258101852</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>45251</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>45316</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>45393.35787037037</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>45762.61817129629</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>45393.3562962963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>45393.36060185185</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>45107</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41948,7 +41948,7 @@
         <v>44902</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>45222</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42062,7 +42062,7 @@
         <v>44949</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42119,7 +42119,7 @@
         <v>44895</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42176,7 +42176,7 @@
         <v>45744.32981481482</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>45519.52232638889</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42295,7 +42295,7 @@
         <v>45323</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45106</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>44990</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>45357.34521990741</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42528,7 +42528,7 @@
         <v>45107</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42590,7 +42590,7 @@
         <v>45554.71863425926</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>45769.98449074074</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>45072.42776620371</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>45477.70315972222</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42828,7 +42828,7 @@
         <v>44169</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44822</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>45274</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>45687</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>45404.68190972223</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>44438</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>45252.78021990741</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43242,7 +43242,7 @@
         <v>44577.83484953704</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43299,7 +43299,7 @@
         <v>45077</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>45077</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43423,7 +43423,7 @@
         <v>45077</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>45254</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>45736.308125</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>45095</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43661,7 +43661,7 @@
         <v>45571.71736111111</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>45454.49679398148</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43780,7 +43780,7 @@
         <v>44846</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43837,7 +43837,7 @@
         <v>45719.52871527777</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43899,7 +43899,7 @@
         <v>45575.56686342593</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>45575.56820601852</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>45618</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         <v>44916</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44142,7 +44142,7 @@
         <v>45170.45921296296</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>44594.84091435185</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>45645.3737962963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         <v>45546.68743055555</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44385,7 +44385,7 @@
         <v>45211</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>45177.33091435185</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>45574.65189814815</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>44544</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>45093.48221064815</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>44473.6343287037</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>44484</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>45769.66260416667</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44856,7 +44856,7 @@
         <v>45471.42659722222</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45265.49225694445</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44970,7 +44970,7 @@
         <v>45344.623125</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>44425.40297453704</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>45699.65424768518</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45146,7 +45146,7 @@
         <v>45546.46497685185</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         <v>45471.52072916667</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45265,7 +45265,7 @@
         <v>44449</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45322,7 +45322,7 @@
         <v>44522</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>45698</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45441,7 +45441,7 @@
         <v>45698</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         <v>45343.58587962963</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>45189</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45617,7 +45617,7 @@
         <v>45684.5790162037</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45674,7 +45674,7 @@
         <v>45372.40246527778</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45731,7 +45731,7 @@
         <v>45134.68158564815</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45788,7 +45788,7 @@
         <v>45237.67819444444</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>45729.76231481481</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45902,7 +45902,7 @@
         <v>45079</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45964,7 +45964,7 @@
         <v>45079</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>45749</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>45462</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>44978</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>44868.36924768519</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>45645</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46321,7 +46321,7 @@
         <v>45667</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46378,7 +46378,7 @@
         <v>45575.53331018519</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46440,7 +46440,7 @@
         <v>45575.54489583334</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>44124</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>45530</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46616,7 +46616,7 @@
         <v>44865.87770833333</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46673,7 +46673,7 @@
         <v>44990</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>44946</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45400.6709837963</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>45173</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46906,7 +46906,7 @@
         <v>45441.48670138889</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>44791</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47020,7 +47020,7 @@
         <v>44902</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
         <v>44306.6371412037</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45553</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47201,7 +47201,7 @@
         <v>45646</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>45729.65061342593</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45008</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47382,7 +47382,7 @@
         <v>45113</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47439,7 +47439,7 @@
         <v>45399.56596064815</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45095</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45377.48265046296</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45099.27354166667</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>45685</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>44308</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>45586.55451388889</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47853,7 +47853,7 @@
         <v>45097.39893518519</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47910,7 +47910,7 @@
         <v>44342.39703703704</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>45664</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>45736</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45548</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48148,7 +48148,7 @@
         <v>45548</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48210,7 +48210,7 @@
         <v>45440</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48267,7 +48267,7 @@
         <v>45274</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48324,7 +48324,7 @@
         <v>45280</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48386,7 +48386,7 @@
         <v>45628.94579861111</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>45328</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>45646.63839120371</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48562,7 +48562,7 @@
         <v>45341.56577546296</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48624,7 +48624,7 @@
         <v>44227</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>45565</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48738,7 +48738,7 @@
         <v>44267</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>45714.31533564815</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48852,7 +48852,7 @@
         <v>44970</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48909,7 +48909,7 @@
         <v>44890.46174768519</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48966,7 +48966,7 @@
         <v>45334</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49023,7 +49023,7 @@
         <v>45516.59447916667</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>44276</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49137,7 +49137,7 @@
         <v>45229</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>44231</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>44753</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>45538.34460648148</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49370,7 +49370,7 @@
         <v>44355</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49432,7 +49432,7 @@
         <v>45614.5968287037</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49489,7 +49489,7 @@
         <v>44511</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49546,7 +49546,7 @@
         <v>45203.510625</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49603,7 +49603,7 @@
         <v>45251.696875</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>45229.66262731481</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49722,7 +49722,7 @@
         <v>45643</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49779,7 +49779,7 @@
         <v>45749</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49836,7 +49836,7 @@
         <v>44602.45490740741</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45569.35209490741</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>45574.65087962963</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45085</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45738.43714120371</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>45618.59456018519</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45119</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50250,7 +50250,7 @@
         <v>44946.54424768518</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45618.58622685185</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50369,7 +50369,7 @@
         <v>45229</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45565.40700231482</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50483,7 +50483,7 @@
         <v>45538.34796296297</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>44809</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50602,7 +50602,7 @@
         <v>45303</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50659,7 +50659,7 @@
         <v>45264.38084490741</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45471.38995370371</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>44161</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>44734.64337962963</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>44906.73321759259</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45047.7181712963</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>44424.61709490741</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45568.62625</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>44984</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45273</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45394.51289351852</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>44236</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51373,7 +51373,7 @@
         <v>45653.53664351852</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51430,7 +51430,7 @@
         <v>45139.64328703703</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>45618.59219907408</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51554,7 +51554,7 @@
         <v>45698</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -567,7 +567,7 @@
         <v>45615</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         <v>45252</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>45905.90649305555</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>44850.83328703704</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44375</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>45810.54824074074</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>45905.90519675926</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44406</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45568.63905092593</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>45099</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45905.89554398148</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44320</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45888.67560185185</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45138</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>44484</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45218</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45888.67765046296</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>45887.5708912037</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>45905.83755787037</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>45905.90789351852</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45099</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>45616.38605324074</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>44472</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>44789</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45615</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45670</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>44280</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>45905.88938657408</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>45021</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>45138</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>44375</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>44512</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>44713.59363425926</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>44679</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>44320</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45698.46697916667</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45250</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>45782.5300462963</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>45104.3483912037</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>45783.66537037037</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>45475.92849537037</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45614.68287037037</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>44536</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45614.68596064814</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>45518</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>44949</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>45827.53077546296</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45832.56153935185</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45440.3184375</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>45881.42446759259</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45845.75751157408</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>45845.75491898148</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>45537.64484953704</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>45575.54934027778</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>45281</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>45478.39592592593</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45645</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45618.58876157407</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>44522</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>45645</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>44151</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>44242</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>44260.30453703704</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>44295.61297453703</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>44123</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>44889.5746875</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>44104</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44126</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44267</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44431.69783564815</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>44495.87667824074</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>44447.51184027778</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>44453</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44228</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44853.61925925926</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>44445.4953587963</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44126</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>44484</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>44508</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>44284.70511574074</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>44271</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>44327</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>44176</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44167</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44503</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44462</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>44386</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>44613</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>44210</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>44280</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>44145</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>44427.75243055556</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>44300</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>44441.66886574074</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>44431.69723379629</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>44332</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>44721.53951388889</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>44722.78552083333</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44862</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>44577.82805555555</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>44171</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>44481</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>44460</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>44790</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>44754</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>44714</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>44676</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>44638</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>44627</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>44377</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>44377.44943287037</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>44630</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>44603</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>44862</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>44629</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>44713.61145833333</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44123</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>44375</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>44671</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>44706.65927083333</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>44224</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>44260.31335648148</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>44113</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>44468.34099537037</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>44102</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>44102</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>44257</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>44259</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>44577.84596064815</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>44505.36354166667</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>44671</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>44418.58454861111</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>44273</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44546.67978009259</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>44375</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>44187</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>44326</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>44823.37396990741</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44325</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44378.55319444444</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>44183</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>44162</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>44522.87423611111</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44635.51386574074</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44126</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>44357</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>44130</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>44820</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44434.74203703704</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>44693.66775462963</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>44694.29309027778</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44484.56523148148</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>44691</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44305</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>44505</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44490</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>44629</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44665</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44459.57613425926</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44447</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>44425.40128472223</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44432.68241898148</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>44594</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>44432</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>44326.7296412037</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>44602</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>44487.51556712963</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>44463</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44332.74105324074</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>44650.47945601852</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44497</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>44456</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44819</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>44479.58512731481</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44733.71126157408</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>44618</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>44113</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>44636.46935185185</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>44389</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>44151</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>44384.56912037037</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44088</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>44672</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>44098</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>44825.99293981482</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44453</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>44536</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>44420.60616898148</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44438.30614583333</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>44860</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>44114</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>44449</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>44622.69101851852</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>44665</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>44777</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>44875.47543981481</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>44451.78710648148</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>44334.60293981482</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>44491</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>44107</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>44088</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>44502.49809027778</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>44502</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>44363</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>44208</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>44481.34877314815</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>44268.55900462963</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>44511.39611111111</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>44491</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>44784</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>44490</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>44698.62354166667</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>44091</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>44451</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>44784.38697916667</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>44526</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>44873.47148148148</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>44389</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>44389</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45338</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>45274</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>44446</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>44889.68100694445</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>45355.70009259259</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45412.54541666667</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45091.39362268519</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>44300</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44319</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>45698</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>45698</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>45698</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>45194</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>44378.46403935185</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>44301</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45103</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45168.92155092592</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>45103</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45729.65171296296</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45119.46452546296</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45222</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
         <v>45107</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45439.56605324074</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>45433.58099537037</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>45694</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>45384</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>45435.57399305556</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16908,7 +16908,7 @@
         <v>45702</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>45538</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>45243</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>45243.62420138889</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>45243</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45615.69570601852</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>44088</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>44536</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17379,7 +17379,7 @@
         <v>45384.43418981481</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>45400.6709837963</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>44890.46174768519</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45554.71863425926</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>45702</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>45471.52878472222</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45518.71048611111</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>44531.3575</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45776.65518518518</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44116</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45777.41673611111</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45777.43878472222</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>44179</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>45061.52474537037</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>45733.60959490741</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>45777.42628472222</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45777</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>45575.53331018519</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45575.54489583334</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>45461.62924768519</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>44809</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>45162.5978125</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>45279</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>44876.35706018518</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45519.51627314815</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>45519.52232638889</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45537.42240740741</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>45107</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45783.71833333333</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45509.73383101852</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45567.68003472222</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45460.46358796296</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>45104.34107638889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45373.30434027778</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>45005</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45608</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>44866.79668981482</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45786</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45546.68743055555</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45569.3533912037</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45253</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>45203.45681712963</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>44445</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>44169</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>44551</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>45267.69052083333</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44480.58034722223</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>44424.61709490741</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45289</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>45454.49679398148</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>44981</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>44902</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45148</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>45785.4253125</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45141.76530092592</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45537.665</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>45229.66430555555</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45113</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>45537.65305555556</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>45618</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>45518.71202546296</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45518.71591435185</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45099</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>45653.53664351852</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45593.59681712963</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45643</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>45323</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>45399.56596064815</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45614.5968287037</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>45788.42467592593</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
         <v>44267</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>44376</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>45546.28121527778</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>45140</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>44607.64115740741</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45646.63482638889</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>45112.67952546296</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45274</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45152.34586805556</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>45791.50862268519</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>44608</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45518.71721064814</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>45134.68158564815</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22270,7 +22270,7 @@
         <v>45170.45921296296</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>44410.61837962963</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45181</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>45639.30934027778</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>45343.58587962963</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>44389</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44539.31923611111</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>44539</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>45418.66800925926</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>44389</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>44883</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>45440.5433912037</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>45667</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45793.61047453704</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>45559</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>45796.44885416667</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>45219</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45796</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>45795.70912037037</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>45796</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45796.45054398148</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>45538.34460648148</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45330</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>45441.30899305556</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>45441.30998842593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>45794.33498842592</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>45729.76231481481</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>45794.3419212963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45795.71300925926</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>45575.55273148148</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45575.5547337963</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>45575.55684027778</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>45575.56686342593</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45575.56820601852</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>45005.35967592592</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>45005.47820601852</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>45177.33091435185</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45795.71547453704</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>45488.42258101852</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45244</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45456.48927083334</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>44978</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>45586.55451388889</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>44522</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>45793.62422453704</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>44621.85737268518</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>45729.60775462963</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>45054</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>45218</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>45590.37590277778</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>45441.48670138889</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45618.58622685185</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>44602.45490740741</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>45618</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>45155.5653125</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>45456.90869212963</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>44602.45162037037</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>45373.34383101852</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>45329</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>45538</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>45411.65641203704</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>45131</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45310</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>44683</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45667</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45610</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45738.42981481482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>45804.45474537037</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44378.46857638889</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>45803.39776620371</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>45173</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>45803</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>45804.45584490741</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>45804.67795138889</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>44988</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>45737.3846412037</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>45393.3562962963</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>45726.33763888889</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>45726.34090277777</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>45571.71736111111</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>44909</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>45642</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>44544</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>45168.94197916667</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>44841</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         <v>45538.34796296297</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>45372.40246527778</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>45218.488125</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>45645.3737962963</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45645.3712037037</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>44124</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>45628.59233796296</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>45280</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>45541.66916666667</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         <v>45519.52319444445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27890,7 +27890,7 @@
         <v>45203.510625</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27947,7 +27947,7 @@
         <v>45188</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>44908.49152777778</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>45518.71482638889</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45749</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>45749</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>45618</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44574.50425925926</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>45741.64491898148</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44553.35407407407</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44594.84091435185</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>45812.57452546297</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>45812.57604166667</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>45812.57143518519</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>45007</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28770,7 +28770,7 @@
         <v>45812.56952546296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28832,7 +28832,7 @@
         <v>45400.66995370371</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>44577.83484953704</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>44675</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29013,7 +29013,7 @@
         <v>45125.41458333333</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45687</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45061.53414351852</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>44822</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>45574.65189814815</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>45097.39893518519</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>45173.39315972223</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>45201</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45565</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>44888.4577662037</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45562.61158564815</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45565.40700231482</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>45177.33991898148</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45685</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29826,7 +29826,7 @@
         <v>45817.6455324074</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>45404.68190972223</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>44420</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>45553</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>45523.58565972222</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
         <v>44974.55693287037</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45820.61684027778</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>44949</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>45586</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>44258</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>44943.73792824074</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>45707</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>45821.37199074074</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45821.44521990741</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45821.46486111111</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>44979</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>45821.46135416667</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>45265.64142361111</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>45821.59353009259</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>45158.41768518519</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>44425</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>45194</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>45826.52024305556</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>45201</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45201.60283564815</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31311,7 +31311,7 @@
         <v>45139.63480324074</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>45827.51862268519</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         <v>45229.66262731481</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
         <v>45744.57851851852</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>45827.51753472222</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>45827.51956018519</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31683,7 +31683,7 @@
         <v>45827.56939814815</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>45194</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>44740.66997685185</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>45827.51628472222</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>45233.42121527778</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45832.74418981482</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32045,7 +32045,7 @@
         <v>44441.70047453704</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32102,7 +32102,7 @@
         <v>45394.51289351852</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>45554.7158912037</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>45582.57542824074</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>45769.98449074074</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>45523</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>45832.51028935185</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>45749.47251157407</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>45305</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32630,7 +32630,7 @@
         <v>45832.55810185185</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>45832.49325231482</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45832.51255787037</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45387.24732638889</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>45387.2521875</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>45832.49579861111</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>45832.5902662037</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>45229</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33111,7 +33111,7 @@
         <v>44236</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>45874.40503472222</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>45832.72778935185</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>45756.49009259259</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>45377.48265046296</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>45548</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>45548</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33550,7 +33550,7 @@
         <v>45569.35209490741</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45832.76491898148</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>45328</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>45876.59166666667</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>45832.76100694444</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>44445.55690972223</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>45227.31859953704</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>45357.34521990741</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>45095</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>45095</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         <v>45251.696875</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>44963.37709490741</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>45434.65854166666</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34316,7 +34316,7 @@
         <v>44735.62539351852</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>45077</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>45266.58394675926</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44967.60165509259</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44267</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44970.51849537037</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>45254.68105324074</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>45348</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34787,7 +34787,7 @@
         <v>45877.64605324074</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>45768.49947916667</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>45440</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34963,7 +34963,7 @@
         <v>45880.46056712963</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>44753</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>45877.63989583333</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>45877.64144675926</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>45838.46456018519</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>45835.68443287037</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>45838.46408564815</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>45877.64847222222</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45880.28673611111</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45369</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45099.27354166667</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>45580.73525462963</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>45877.64230324074</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>45877.64431712963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>45877.64776620371</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>45877.65075231482</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>45880.3172337963</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>45635.69581018519</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>44950</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45594.63747685185</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>45310.87931712963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45628.58975694444</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45477.70315972222</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>45344.6027662037</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45393.36060185185</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>45840</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45034.5174537037</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>45516.4221412037</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>45194</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36681,7 +36681,7 @@
         <v>45274</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>44231</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>44970</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>45729.65061342593</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45645</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>44803.64361111111</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45880</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45881.43759259259</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>45009.64217592592</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37199,7 +37199,7 @@
         <v>44503</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>45265.49225694445</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>45145</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45159.44525462963</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45488.41480324074</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>45078.82620370371</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>45538.34193287037</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>45511.39445601852</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>45511.40297453704</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>45646</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37784,7 +37784,7 @@
         <v>44951.5830324074</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         <v>45642.66184027777</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>44342.39703703704</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>44791</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>45272.57385416667</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>45079</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>45079</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>44161</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>45635.63706018519</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>45272.36168981482</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>45736.308125</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>45684.5790162037</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>45880</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>45881.42791666667</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>45574.65087962963</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38664,7 +38664,7 @@
         <v>45755.68247685185</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>44665</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38778,7 +38778,7 @@
         <v>45149</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>45881.59550925926</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>45884.38858796296</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>45736</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>45646.63839120371</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39068,7 +39068,7 @@
         <v>45884</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>45170</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39187,7 +39187,7 @@
         <v>45072</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39249,7 +39249,7 @@
         <v>44546.6679050926</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>45138</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>45113</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39425,7 +39425,7 @@
         <v>44389</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>44990</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>45530</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>45714</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39653,7 +39653,7 @@
         <v>45030</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>45685</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>45691.36253472222</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45749</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>45194</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>44355</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40005,7 +40005,7 @@
         <v>44900.36149305556</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40062,7 +40062,7 @@
         <v>44511</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>45766.33309027777</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40176,7 +40176,7 @@
         <v>45211</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
         <v>45744.32981481482</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45471.52072916667</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40347,7 +40347,7 @@
         <v>45257.48188657407</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>45738.43714120371</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>45082.31421296296</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>44566</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         <v>44389</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>44990</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>45097.38688657407</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>45769.17</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>45251</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>45736.30940972222</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>44431</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>45077</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>45077</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
         <v>45077</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41170,7 +41170,7 @@
         <v>45075.44152777778</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>45744.57673611111</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>44946.54424768518</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>45575.55570601852</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>44546.67222222222</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>45229</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41527,7 +41527,7 @@
         <v>45048</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>45047.7181712963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>44457</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>45471.42659722222</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>45264.38084490741</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41812,7 +41812,7 @@
         <v>45393.35787037037</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41874,7 +41874,7 @@
         <v>44564</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>45106</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>45548</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>44928</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>44425.40297453704</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45769.66260416667</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45547.36590277778</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45252.78021990741</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42340,7 +42340,7 @@
         <v>44175</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>44227</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42454,7 +42454,7 @@
         <v>45520.32887731482</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>44927.72487268518</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42573,7 +42573,7 @@
         <v>45618.59456018519</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42635,7 +42635,7 @@
         <v>44473.6343287037</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42692,7 +42692,7 @@
         <v>45845.75200231482</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>45844.57527777777</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
         <v>45845.4855787037</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>45887.56101851852</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42930,7 +42930,7 @@
         <v>45845.49216435185</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42987,7 +42987,7 @@
         <v>45844.5775</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45344.623125</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>45845.76005787037</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43163,7 +43163,7 @@
         <v>45749.42258101852</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45600.60071759259</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43277,7 +43277,7 @@
         <v>45707</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>44371.47609953704</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43391,7 +43391,7 @@
         <v>45844.57328703703</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43453,7 +43453,7 @@
         <v>45316</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>44449</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>45008</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>45177.31795138889</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45751.50498842593</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45108.7553587963</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45751.5056712963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45702</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>45889.66935185185</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>45889.67577546297</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44043,7 +44043,7 @@
         <v>45889.67290509259</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44105,7 +44105,7 @@
         <v>45694</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>45813.68209490741</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>44728</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>44895</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>44916</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>44979</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>45670.69458333333</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44504,7 +44504,7 @@
         <v>45575.53690972222</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44566,7 +44566,7 @@
         <v>45575.56256944445</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>45537.64621527777</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44690,7 +44690,7 @@
         <v>45854</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44747,7 +44747,7 @@
         <v>45166.68493055556</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44809,7 +44809,7 @@
         <v>45895.47704861111</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44871,7 +44871,7 @@
         <v>45895.4790625</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>44259</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45895.48394675926</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45052,7 +45052,7 @@
         <v>45895.49994212963</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45895.48927083334</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45176,7 +45176,7 @@
         <v>45854</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45233,7 +45233,7 @@
         <v>45898.37138888889</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>45404.55239583334</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>45404.55601851852</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>44902</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>45107</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45528,7 +45528,7 @@
         <v>45189</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45585,7 +45585,7 @@
         <v>44306.6371412037</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45642,7 +45642,7 @@
         <v>45899.38057870371</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>44308</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>45860.36222222223</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>45860.3857175926</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45902.3406712963</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45587</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>44853.79818287037</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45497</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45903.37475694445</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>44906.73321759259</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>45237.67819444444</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46279,7 +46279,7 @@
         <v>45614.68083333333</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45905.89236111111</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46398,7 +46398,7 @@
         <v>45905.89329861111</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46460,7 +46460,7 @@
         <v>45474.65005787037</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45068</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45610.7466087963</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45905.89143518519</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>44577.81121527778</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45628.94579861111</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46812,7 +46812,7 @@
         <v>45618.59219907408</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45575.65721064815</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45211</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46998,7 +46998,7 @@
         <v>45831</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>44721.52627314815</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45534.54032407407</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45831</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>45119</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>45583</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47355,7 +47355,7 @@
         <v>45453.36664351852</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>44734.64337962963</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45912.63359953704</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>45912.63751157407</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>44946</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>44958.58982638889</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45912.63451388889</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>45870</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47831,7 +47831,7 @@
         <v>44978</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47888,7 +47888,7 @@
         <v>45870</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47945,7 +47945,7 @@
         <v>45870</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48002,7 +48002,7 @@
         <v>45546.46497685185</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48064,7 +48064,7 @@
         <v>45870</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48121,7 +48121,7 @@
         <v>44846</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48178,7 +48178,7 @@
         <v>45376.70292824074</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48235,7 +48235,7 @@
         <v>45327</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>45590.39471064815</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48354,7 +48354,7 @@
         <v>45254</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48416,7 +48416,7 @@
         <v>45762.61817129629</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48473,7 +48473,7 @@
         <v>45074</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48530,7 +48530,7 @@
         <v>44431</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48587,7 +48587,7 @@
         <v>44868.36924768519</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>45189.38135416667</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45749</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45139.64328703703</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>45575.57104166667</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>45471.38995370371</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45057</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>45085</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>45093.48221064815</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>44865.600625</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>45303</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         <v>45523.31621527778</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>44865.87770833333</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>45667</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49400,7 +49400,7 @@
         <v>45170</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49462,7 +49462,7 @@
         <v>45103.53614583334</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49519,7 +49519,7 @@
         <v>45036</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49576,7 +49576,7 @@
         <v>45699.65424768518</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49633,7 +49633,7 @@
         <v>45411.42858796296</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49690,7 +49690,7 @@
         <v>45072.42776620371</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>44902</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>45611.44960648148</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45043.40300925926</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45604.58837962963</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45749</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>45525.7374537037</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>45532</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45667</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>45719.52871527777</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50270,7 +50270,7 @@
         <v>44276</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50327,7 +50327,7 @@
         <v>45183.48666666666</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50384,7 +50384,7 @@
         <v>45664</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50441,7 +50441,7 @@
         <v>44833</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50498,7 +50498,7 @@
         <v>44484</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50555,7 +50555,7 @@
         <v>45568.64523148148</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50617,7 +50617,7 @@
         <v>45341.56577546296</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45334</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45273</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45404.55681712963</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50855,7 +50855,7 @@
         <v>45530</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50912,7 +50912,7 @@
         <v>45218</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50974,7 +50974,7 @@
         <v>45462</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51031,7 +51031,7 @@
         <v>44438</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45516.59447916667</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45568.62625</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>45618.58962962963</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51274,7 +51274,7 @@
         <v>44984</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>45111</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51388,7 +51388,7 @@
         <v>45471.40384259259</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>45714.31533564815</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -567,7 +567,7 @@
         <v>45615</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         <v>45252</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>45905.90649305555</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>44850.83328703704</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44375</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>45810.54824074074</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>45905.90519675926</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44406</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45568.63905092593</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>45099</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45905.89554398148</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44320</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45888.67560185185</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>45138</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>44484</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45218</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45888.67765046296</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>45887.5708912037</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>45905.83755787037</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>45905.90789351852</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45099</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>45616.38605324074</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>44472</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>44789</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45615</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45670</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>44280</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>45905.88938657408</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>45021</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>45138</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>44375</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>44512</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>44713.59363425926</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>44679</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>44320</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45698.46697916667</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45250</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>45782.5300462963</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>45104.3483912037</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>45783.66537037037</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>45475.92849537037</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45614.68287037037</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>44536</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45614.68596064814</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>45518</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>44949</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>45827.53077546296</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45832.56153935185</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45440.3184375</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>45881.42446759259</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45845.75751157408</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>45845.75491898148</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>45537.64484953704</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>45575.54934027778</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>45281</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>45478.39592592593</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45645</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45618.58876157407</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>44522</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>45645</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>44151</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>44242</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>44260.30453703704</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>44295.61297453703</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>44123</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>44889.5746875</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>44104</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44126</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44267</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44431.69783564815</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>44495.87667824074</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>44447.51184027778</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>44453</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44228</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44853.61925925926</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>44445.4953587963</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44126</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>44484</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>44508</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>44284.70511574074</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>44271</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>44327</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>44176</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44167</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44503</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44462</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>44386</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>44613</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>44210</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>44280</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>44145</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>44427.75243055556</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>44300</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>44441.66886574074</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>44431.69723379629</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>44332</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>44721.53951388889</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>44722.78552083333</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44862</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>44577.82805555555</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>44171</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>44481</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>44460</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>44790</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>44754</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>44714</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>44676</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>44638</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>44627</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>44377</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>44377.44943287037</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>44630</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>44603</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>44862</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>44629</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>44713.61145833333</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>44123</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>44375</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>44671</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>44706.65927083333</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>44224</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>44260.31335648148</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>44113</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>44468.34099537037</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>44102</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>44102</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>44257</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>44259</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>44577.84596064815</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>44505.36354166667</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>44671</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>44418.58454861111</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>44273</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44546.67978009259</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>44375</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>44187</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>44326</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>44823.37396990741</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44325</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44378.55319444444</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>44183</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>44162</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>44522.87423611111</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44635.51386574074</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44126</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>44357</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>44130</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>44820</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44434.74203703704</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>44693.66775462963</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>44694.29309027778</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44484.56523148148</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>44691</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44305</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>44505</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44490</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>44629</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44665</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44459.57613425926</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44447</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>44425.40128472223</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44432.68241898148</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>44594</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>44432</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>44326.7296412037</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>44602</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>44487.51556712963</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>44463</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44332.74105324074</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>44650.47945601852</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44497</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>44456</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44819</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>44479.58512731481</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44733.71126157408</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>44618</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>44113</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>44636.46935185185</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>44389</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>44151</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>44384.56912037037</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44088</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>44672</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>44098</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>44825.99293981482</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44453</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>44536</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>44420.60616898148</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44438.30614583333</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>44860</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>44114</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>44449</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>44622.69101851852</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>44665</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>44777</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>44875.47543981481</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>44451.78710648148</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>44334.60293981482</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>44491</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>44107</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>44088</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>44502.49809027778</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>44502</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>44363</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>44208</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>44481.34877314815</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>44268.55900462963</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>44511.39611111111</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>44491</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>44784</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>44490</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>44698.62354166667</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>44091</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>44451</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>44784.38697916667</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>44526</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>44873.47148148148</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>44389</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>44389</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45338</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>45274</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>44446</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>44889.68100694445</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>45355.70009259259</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45412.54541666667</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45091.39362268519</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>44300</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44319</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>45698</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>45698</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>45698</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>45194</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>44378.46403935185</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>44301</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45103</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45168.92155092592</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>45103</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45729.65171296296</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45119.46452546296</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45222</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
         <v>45107</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45439.56605324074</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>45433.58099537037</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>45694</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>45384</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>45435.57399305556</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16908,7 +16908,7 @@
         <v>45702</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>45538</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>45243</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>45243.62420138889</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>45243</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45615.69570601852</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>44088</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>44536</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17379,7 +17379,7 @@
         <v>45384.43418981481</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>45400.6709837963</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>44890.46174768519</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45554.71863425926</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>45702</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>45471.52878472222</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45518.71048611111</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>44531.3575</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45776.65518518518</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44116</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45777.41673611111</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45777.43878472222</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>44179</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>45061.52474537037</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>45733.60959490741</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>45777.42628472222</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45777</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>45575.53331018519</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45575.54489583334</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>45461.62924768519</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>44809</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>45162.5978125</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>45279</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>44876.35706018518</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45519.51627314815</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>45519.52232638889</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45537.42240740741</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>45107</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45783.71833333333</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45509.73383101852</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45567.68003472222</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45460.46358796296</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>45104.34107638889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45373.30434027778</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>45005</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45608</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>44866.79668981482</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45786</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45546.68743055555</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45569.3533912037</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45253</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>45203.45681712963</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>44445</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>44169</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>44551</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>45267.69052083333</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44480.58034722223</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>44424.61709490741</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45289</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>45454.49679398148</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>44981</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>44902</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45148</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>45785.4253125</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45141.76530092592</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45537.665</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>45229.66430555555</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45113</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>45537.65305555556</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>45618</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>45518.71202546296</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45518.71591435185</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45099</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>45653.53664351852</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45593.59681712963</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45643</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>45323</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>45399.56596064815</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45614.5968287037</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>45788.42467592593</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
         <v>44267</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>44376</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>45546.28121527778</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>45140</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>44607.64115740741</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45646.63482638889</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>45112.67952546296</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45274</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45152.34586805556</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>45791.50862268519</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>44608</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45518.71721064814</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>45134.68158564815</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22270,7 +22270,7 @@
         <v>45170.45921296296</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>44410.61837962963</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45181</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>45639.30934027778</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>45343.58587962963</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>44389</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44539.31923611111</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>44539</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>45418.66800925926</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>44389</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>44883</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>45440.5433912037</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>45667</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45793.61047453704</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>45559</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>45796.44885416667</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>45219</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45796</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>45795.70912037037</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>45796</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45796.45054398148</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>45538.34460648148</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45330</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>45441.30899305556</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>45441.30998842593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>45794.33498842592</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>45729.76231481481</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>45794.3419212963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45795.71300925926</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>45575.55273148148</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45575.5547337963</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>45575.55684027778</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>45575.56686342593</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45575.56820601852</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>45005.35967592592</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>45005.47820601852</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>45177.33091435185</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45795.71547453704</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>45488.42258101852</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45244</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45456.48927083334</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>44978</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>45586.55451388889</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>44522</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>45793.62422453704</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>44621.85737268518</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>45729.60775462963</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>45054</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>45218</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>45590.37590277778</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>45441.48670138889</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45618.58622685185</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>44602.45490740741</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>45618</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>45155.5653125</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>45456.90869212963</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>44602.45162037037</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>45373.34383101852</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>45329</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>45538</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>45411.65641203704</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>45131</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45310</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>44683</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45667</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45610</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45738.42981481482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>45804.45474537037</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44378.46857638889</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>45803.39776620371</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>45173</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>45803</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>45804.45584490741</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>45804.67795138889</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>44988</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>45737.3846412037</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>45393.3562962963</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>45726.33763888889</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>45726.34090277777</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>45571.71736111111</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>44909</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>45642</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>44544</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>45168.94197916667</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>44841</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         <v>45538.34796296297</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>45372.40246527778</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>45218.488125</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>45645.3737962963</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45645.3712037037</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>44124</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>45628.59233796296</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>45280</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>45541.66916666667</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         <v>45519.52319444445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27890,7 +27890,7 @@
         <v>45203.510625</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27947,7 +27947,7 @@
         <v>45188</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>44908.49152777778</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>45518.71482638889</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45749</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>45749</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>45618</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44574.50425925926</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>45741.64491898148</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44553.35407407407</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44594.84091435185</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>45812.57452546297</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>45812.57604166667</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>45812.57143518519</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>45007</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28770,7 +28770,7 @@
         <v>45812.56952546296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28832,7 +28832,7 @@
         <v>45400.66995370371</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>44577.83484953704</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>44675</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29013,7 +29013,7 @@
         <v>45125.41458333333</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45687</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45061.53414351852</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>44822</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>45574.65189814815</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>45097.39893518519</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>45173.39315972223</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>45201</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45565</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>44888.4577662037</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45562.61158564815</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45565.40700231482</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>45177.33991898148</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45685</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29826,7 +29826,7 @@
         <v>45817.6455324074</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>45404.68190972223</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>44420</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>45553</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>45523.58565972222</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
         <v>44974.55693287037</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45820.61684027778</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>44949</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>45586</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>44258</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>44943.73792824074</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>45707</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>45821.37199074074</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45821.44521990741</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45821.46486111111</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>44979</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>45821.46135416667</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>45265.64142361111</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>45821.59353009259</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>45158.41768518519</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>44425</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>45194</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>45826.52024305556</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>45201</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45201.60283564815</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31311,7 +31311,7 @@
         <v>45139.63480324074</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>45827.51862268519</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         <v>45229.66262731481</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
         <v>45744.57851851852</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>45827.51753472222</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>45827.51956018519</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31683,7 +31683,7 @@
         <v>45827.56939814815</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>45194</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>44740.66997685185</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>45827.51628472222</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>45233.42121527778</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45832.74418981482</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32045,7 +32045,7 @@
         <v>44441.70047453704</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32102,7 +32102,7 @@
         <v>45394.51289351852</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>45554.7158912037</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>45582.57542824074</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>45769.98449074074</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>45523</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>45832.51028935185</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>45749.47251157407</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>45305</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32630,7 +32630,7 @@
         <v>45832.55810185185</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>45832.49325231482</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45832.51255787037</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45387.24732638889</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>45387.2521875</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>45832.49579861111</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>45832.5902662037</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>45229</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33111,7 +33111,7 @@
         <v>44236</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>45874.40503472222</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>45832.72778935185</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>45756.49009259259</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>45377.48265046296</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>45548</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>45548</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33550,7 +33550,7 @@
         <v>45569.35209490741</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45832.76491898148</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>45328</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>45876.59166666667</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>45832.76100694444</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>44445.55690972223</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>45227.31859953704</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>45357.34521990741</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>45095</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>45095</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         <v>45251.696875</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>44963.37709490741</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>45434.65854166666</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34316,7 +34316,7 @@
         <v>44735.62539351852</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>45077</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>45266.58394675926</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44967.60165509259</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44267</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44970.51849537037</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>45254.68105324074</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>45348</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34787,7 +34787,7 @@
         <v>45877.64605324074</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>45768.49947916667</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>45440</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34963,7 +34963,7 @@
         <v>45880.46056712963</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>44753</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>45877.63989583333</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>45877.64144675926</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>45838.46456018519</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>45835.68443287037</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>45838.46408564815</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>45877.64847222222</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45880.28673611111</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45369</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45099.27354166667</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>45580.73525462963</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>45877.64230324074</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>45877.64431712963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>45877.64776620371</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>45877.65075231482</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>45880.3172337963</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>45635.69581018519</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>44950</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45594.63747685185</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>45310.87931712963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45628.58975694444</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45477.70315972222</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>45344.6027662037</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45393.36060185185</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>45840</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45034.5174537037</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>45516.4221412037</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>45194</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36681,7 +36681,7 @@
         <v>45274</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>44231</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>44970</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>45729.65061342593</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45645</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>44803.64361111111</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45880</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45881.43759259259</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>45009.64217592592</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37199,7 +37199,7 @@
         <v>44503</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>45265.49225694445</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>45145</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45159.44525462963</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45488.41480324074</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>45078.82620370371</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>45538.34193287037</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>45511.39445601852</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>45511.40297453704</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>45646</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37784,7 +37784,7 @@
         <v>44951.5830324074</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         <v>45642.66184027777</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>44342.39703703704</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>44791</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>45272.57385416667</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>45079</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>45079</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>44161</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>45635.63706018519</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>45272.36168981482</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>45736.308125</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>45684.5790162037</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>45880</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>45881.42791666667</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>45574.65087962963</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38664,7 +38664,7 @@
         <v>45755.68247685185</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>44665</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38778,7 +38778,7 @@
         <v>45149</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>45881.59550925926</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>45884.38858796296</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>45736</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>45646.63839120371</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39068,7 +39068,7 @@
         <v>45884</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>45170</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39187,7 +39187,7 @@
         <v>45072</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39249,7 +39249,7 @@
         <v>44546.6679050926</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>45138</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>45113</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39425,7 +39425,7 @@
         <v>44389</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>44990</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>45530</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>45714</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39653,7 +39653,7 @@
         <v>45030</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>45685</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>45691.36253472222</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45749</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>45194</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>44355</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40005,7 +40005,7 @@
         <v>44900.36149305556</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40062,7 +40062,7 @@
         <v>44511</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>45766.33309027777</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40176,7 +40176,7 @@
         <v>45211</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
         <v>45744.32981481482</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45471.52072916667</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40347,7 +40347,7 @@
         <v>45257.48188657407</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>45738.43714120371</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>45082.31421296296</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>44566</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         <v>44389</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>44990</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>45097.38688657407</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>45769.17</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>45251</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>45736.30940972222</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>44431</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>45077</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>45077</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
         <v>45077</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41170,7 +41170,7 @@
         <v>45075.44152777778</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>45744.57673611111</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>44946.54424768518</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>45575.55570601852</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>44546.67222222222</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>45229</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41527,7 +41527,7 @@
         <v>45048</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>45047.7181712963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>44457</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>45471.42659722222</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>45264.38084490741</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41812,7 +41812,7 @@
         <v>45393.35787037037</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41874,7 +41874,7 @@
         <v>44564</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>45106</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>45548</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>44928</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>44425.40297453704</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45769.66260416667</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45547.36590277778</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45252.78021990741</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42340,7 +42340,7 @@
         <v>44175</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>44227</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42454,7 +42454,7 @@
         <v>45520.32887731482</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>44927.72487268518</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42573,7 +42573,7 @@
         <v>45618.59456018519</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42635,7 +42635,7 @@
         <v>44473.6343287037</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42692,7 +42692,7 @@
         <v>45845.75200231482</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>45844.57527777777</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
         <v>45845.4855787037</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>45887.56101851852</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42930,7 +42930,7 @@
         <v>45845.49216435185</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42987,7 +42987,7 @@
         <v>45844.5775</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45344.623125</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>45845.76005787037</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43163,7 +43163,7 @@
         <v>45749.42258101852</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45600.60071759259</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43277,7 +43277,7 @@
         <v>45707</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>44371.47609953704</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43391,7 +43391,7 @@
         <v>45844.57328703703</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43453,7 +43453,7 @@
         <v>45316</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>44449</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>45008</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>45177.31795138889</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45751.50498842593</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45108.7553587963</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45751.5056712963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45702</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>45889.66935185185</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>45889.67577546297</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44043,7 +44043,7 @@
         <v>45889.67290509259</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44105,7 +44105,7 @@
         <v>45694</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>45813.68209490741</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>44728</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>44895</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>44916</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>44979</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>45670.69458333333</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44504,7 +44504,7 @@
         <v>45575.53690972222</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44566,7 +44566,7 @@
         <v>45575.56256944445</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>45537.64621527777</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44690,7 +44690,7 @@
         <v>45854</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44747,7 +44747,7 @@
         <v>45166.68493055556</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44809,7 +44809,7 @@
         <v>45895.47704861111</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44871,7 +44871,7 @@
         <v>45895.4790625</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>44259</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45895.48394675926</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45052,7 +45052,7 @@
         <v>45895.49994212963</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45895.48927083334</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45176,7 +45176,7 @@
         <v>45854</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45233,7 +45233,7 @@
         <v>45898.37138888889</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>45404.55239583334</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>45404.55601851852</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>44902</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>45107</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45528,7 +45528,7 @@
         <v>45189</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45585,7 +45585,7 @@
         <v>44306.6371412037</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45642,7 +45642,7 @@
         <v>45899.38057870371</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>44308</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>45860.36222222223</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>45860.3857175926</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45902.3406712963</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45587</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>44853.79818287037</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45497</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45903.37475694445</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>44906.73321759259</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>45237.67819444444</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46279,7 +46279,7 @@
         <v>45614.68083333333</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45905.89236111111</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46398,7 +46398,7 @@
         <v>45905.89329861111</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46460,7 +46460,7 @@
         <v>45474.65005787037</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45068</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45610.7466087963</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45905.89143518519</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>44577.81121527778</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45628.94579861111</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46812,7 +46812,7 @@
         <v>45618.59219907408</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45575.65721064815</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45211</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46998,7 +46998,7 @@
         <v>45831</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>44721.52627314815</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45534.54032407407</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45831</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>45119</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>45583</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47355,7 +47355,7 @@
         <v>45453.36664351852</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>44734.64337962963</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45912.63359953704</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>45912.63751157407</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>44946</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>44958.58982638889</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45912.63451388889</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>45870</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47831,7 +47831,7 @@
         <v>44978</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47888,7 +47888,7 @@
         <v>45870</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47945,7 +47945,7 @@
         <v>45870</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48002,7 +48002,7 @@
         <v>45546.46497685185</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48064,7 +48064,7 @@
         <v>45870</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48121,7 +48121,7 @@
         <v>44846</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48178,7 +48178,7 @@
         <v>45376.70292824074</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48235,7 +48235,7 @@
         <v>45327</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>45590.39471064815</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48354,7 +48354,7 @@
         <v>45254</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48416,7 +48416,7 @@
         <v>45762.61817129629</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48473,7 +48473,7 @@
         <v>45074</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48530,7 +48530,7 @@
         <v>44431</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48587,7 +48587,7 @@
         <v>44868.36924768519</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>45189.38135416667</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45749</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45139.64328703703</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>45575.57104166667</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>45471.38995370371</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45057</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>45085</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>45093.48221064815</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>44865.600625</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>45303</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         <v>45523.31621527778</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>44865.87770833333</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>45667</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49400,7 +49400,7 @@
         <v>45170</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49462,7 +49462,7 @@
         <v>45103.53614583334</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49519,7 +49519,7 @@
         <v>45036</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49576,7 +49576,7 @@
         <v>45699.65424768518</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49633,7 +49633,7 @@
         <v>45411.42858796296</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49690,7 +49690,7 @@
         <v>45072.42776620371</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>44902</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>45611.44960648148</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45043.40300925926</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45604.58837962963</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45749</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>45525.7374537037</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>45532</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45667</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>45719.52871527777</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50270,7 +50270,7 @@
         <v>44276</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50327,7 +50327,7 @@
         <v>45183.48666666666</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50384,7 +50384,7 @@
         <v>45664</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50441,7 +50441,7 @@
         <v>44833</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50498,7 +50498,7 @@
         <v>44484</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50555,7 +50555,7 @@
         <v>45568.64523148148</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50617,7 +50617,7 @@
         <v>45341.56577546296</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45334</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45273</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45404.55681712963</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50855,7 +50855,7 @@
         <v>45530</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50912,7 +50912,7 @@
         <v>45218</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50974,7 +50974,7 @@
         <v>45462</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51031,7 +51031,7 @@
         <v>44438</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45516.59447916667</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51150,7 +51150,7 @@
         <v>45568.62625</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>45618.58962962963</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51274,7 +51274,7 @@
         <v>44984</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>45111</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51388,7 +51388,7 @@
         <v>45471.40384259259</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>45714.31533564815</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -567,7 +567,7 @@
         <v>45615</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         <v>45252</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>45905.90649305555</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>44850.83328703704</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44375</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>45810.54824074074</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>45905.90519675926</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44406</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45099</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>45905.89554398148</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45568.63905092593</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>45138</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44320</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45888.67560185185</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>44484</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45616.38605324074</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>45099</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>45218</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45887.5708912037</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>45888.67765046296</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>45905.90789351852</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45905.83755787037</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>44472</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45138</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>44280</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>45021</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>44789</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>45670</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>45905.88938657408</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>45615</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>44375</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>44512</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>44713.59363425926</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>44679</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>44320</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45782.5300462963</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45783.66537037037</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>45575.54934027778</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>45645</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>45478.39592592593</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>45614.68596064814</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>45518</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>44536</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>44949</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>45250</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>45281</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>45645</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>45104.3483912037</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>45827.53077546296</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45832.56153935185</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>44522</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>45845.75491898148</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45845.75751157408</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45475.92849537037</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>45537.64484953704</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>45440.3184375</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>45614.68287037037</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45618.58876157407</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>45698.46697916667</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>45922.49990740741</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>45881.42446759259</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44151</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>44242</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44260.30453703704</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>44295.61297453703</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>44123</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>44889.5746875</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>44104</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>44126</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44267</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>44431.69783564815</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>44853.61925925926</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>44447.51184027778</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>44495.87667824074</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>44453</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>44228</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44445.4953587963</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>44484</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>44126</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>44508</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>44284.70511574074</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>44271</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>44176</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44327</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>44167</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>44503</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>44462</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>44613</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44386</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>44210</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>44280</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>44145</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>44427.75243055556</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>44300</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>44441.66886574074</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>44431.69723379629</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44332</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>44722.78552083333</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>44721.53951388889</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44862</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>44577.82805555555</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>44460</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>44481</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>44171</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>44754</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>44638</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>44790</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>44714</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>44627</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44676</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>44377</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>44377.44943287037</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>44603</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>44629</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>44630</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>44862</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>44713.61145833333</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>44123</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>44375</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>44671</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>44706.65927083333</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>44224</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>44260.31335648148</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>44113</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>44468.34099537037</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>44257</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>44102</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>44102</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>44577.84596064815</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>44418.58454861111</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44505.36354166667</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>44259</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44273</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44671</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44546.67978009259</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44375</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>44187</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44326</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>44823.37396990741</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>44325</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>44378.55319444444</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>44183</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>44162</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44522.87423611111</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>44635.51386574074</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>44126</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>44130</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>44357</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>44820</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>44434.74203703704</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>44484.56523148148</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>44694.29309027778</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>44691</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>44693.66775462963</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         <v>44305</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>44505</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>44490</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>44629</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>44425.40128472223</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>44665</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>44459.57613425926</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>44447</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>44432.68241898148</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>44432</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>44594</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>44326.7296412037</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>44332.74105324074</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44113</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>44602</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>44487.51556712963</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>44463</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>44497</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>44456</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>44819</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44384.56912037037</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>44733.71126157408</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>44453</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>44536</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>44420.60616898148</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>44860</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>44389</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>44672</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>44151</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>44825.99293981482</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>44438.30614583333</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>44114</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>44451</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>44873.47148148148</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>44449</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44622.69101851852</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>44665</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>44777</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>44451.78710648148</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>44875.47543981481</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>44334.60293981482</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>44491</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>44650.47945601852</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>44502.49809027778</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>44502</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44536</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>44208</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44116</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>44179</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44479.58512731481</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>44618</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>44481.34877314815</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>44267</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>44376</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>44268.55900462963</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>44491</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>44526</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>44607.64115740741</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44608</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>44389</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>44389</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>44539.31923611111</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>44539</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>44784</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>44446</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>44889.68100694445</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>44636.46935185185</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>44445</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>45439.56605324074</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>45702</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>44564</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45219</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>44665</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>45211</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45112.67952546296</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>45593.59681712963</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>45355.70009259259</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>45749</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>45702</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45453.36664351852</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>45107</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>44378.46403935185</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>44445.55690972223</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>45777.42628472222</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45777.41673611111</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>45532</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>44974.55693287037</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45733.60959490741</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>45777</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45777.43878472222</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>45030</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>44979</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>44319</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>45776.65518518518</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45404.55681712963</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45611.44960648148</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>44683</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>44958.58982638889</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>45604.58837962963</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>45783.71833333333</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>45043.40300925926</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>45567.68003472222</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>45509.73383101852</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>45460.46358796296</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>45694</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>45384.43418981481</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45646.63482638889</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>45755.68247685185</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>45140</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>45751.50498842593</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>45751.5056712963</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>45233.42121527778</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>44943.73792824074</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>45569.3533912037</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45253</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>45054</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>45203.45681712963</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>44981</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45642.66184027777</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>45785.4253125</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45229.66430555555</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>45580.73525462963</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>45583</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>45267.69052083333</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>45538.34193287037</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45005.35967592592</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>45005.47820601852</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45628.59233796296</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>45537.65305555556</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>45404.55239583334</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>45404.55601851852</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>45183.48666666666</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>45158.41768518519</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>44546.6679050926</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>45768.49947916667</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>45788.42467592593</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45194</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>44721.52627314815</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>44876.35706018518</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45537.665</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         <v>45057</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>45145</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44410.61837962963</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>45166.68493055556</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45104.34107638889</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45338</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>45194</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45074</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>45575.53690972222</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>45575.56256944445</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>45488.41480324074</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>45635.63706018519</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>44853.79818287037</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>45568.64523148148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>44441.70047453704</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45726.33763888889</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>45726.34090277777</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>45786</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>45159.44525462963</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>45103.53614583334</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>45075.44152777778</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45061.53414351852</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>45310.87931712963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>45305</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>45279</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>45639.30934027778</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>45791.50862268519</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>45523.31621527778</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21413,7 +21413,7 @@
         <v>44833</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>45181</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>45097.38688657407</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45418.66800925926</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>45272.36168981482</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44927.72487268518</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>45737.3846412037</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>45559</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
         <v>45618</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>45344.6027662037</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>45330</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45667</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>44107</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>45327</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45546.28121527778</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45440.5433912037</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>45749.42258101852</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45274</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>45608</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>45749</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>45149</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>45793.61047453704</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>44259</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>45243</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>45523.58565972222</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         <v>45766.33309027777</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>45610.7466087963</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>45243.62420138889</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>45243</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>45007</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45600.60071759259</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23235,7 +23235,7 @@
         <v>45036</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>44258</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
         <v>45177.31795138889</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44363</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>45541.66916666667</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>44511.39611111111</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45793.62422453704</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>45456.90869212963</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>45795.71300925926</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>45741.64491898148</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>44389</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>45518.71048611111</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23949,7 +23949,7 @@
         <v>45518.71202546296</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>45518.71591435185</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>45749.47251157407</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24120,7 +24120,7 @@
         <v>45795.70912037037</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>45155.5653125</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>45244</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45548</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>45272.57385416667</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45125.41458333333</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>45796.44885416667</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>45113</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>45794.33498842592</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>45796</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>45794.3419212963</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>44841</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>45061.52474537037</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>45170</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>45796</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>45796.45054398148</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>45562.61158564815</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>45749.4737962963</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>44371.47609953704</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>44988</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>45795.71547453704</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>45456.48927083334</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>45474.65005787037</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>44490</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>44698.62354166667</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45497</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>45511.40297453704</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44978</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>44803.64361111111</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>44784.38697916667</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>44963.37709490741</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45729.60775462963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45369</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>45618</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26103,7 +26103,7 @@
         <v>44389</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>45590.37590277778</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>45373.30434027778</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>45005</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>45803</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>45034.5174537037</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45803.39776620371</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>45310</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45461.62924768519</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>45736.30940972222</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44378.46857638889</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44909</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45077</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>45162.5978125</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45744.57851851852</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>45433.58099537037</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>45804.45474537037</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>45804.67795138889</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45691.36253472222</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>45582.57542824074</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>45749</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>44888.4577662037</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>44928</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>44902</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45411.65641203704</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44425</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>45108.7553587963</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>45804.45584490741</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>45635.69581018519</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>45744.57673611111</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>45173.39315972223</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>45168.92155092592</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>45168.94197916667</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>44740.66997685185</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>45441.30899305556</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28148,7 +28148,7 @@
         <v>45441.30998842593</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>44431</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>44979</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>45518.71482638889</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>45411.42858796296</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>45194</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>45645.3712037037</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28557,7 +28557,7 @@
         <v>45812.56952546296</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
         <v>45615.69570601852</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28676,7 +28676,7 @@
         <v>45628.58975694444</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>44300</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45812.57143518519</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45812.57452546297</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>45812.57604166667</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45707</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>44480.58034722223</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>45756.49009259259</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45817.6455324074</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45702</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45575.55570601852</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>45201</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>45201.60283564815</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>45329</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45518.71721064814</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>45547.36590277778</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>45218</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>45048</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>44574.50425925926</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>45610</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>44457</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>44301</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>45590.39471064815</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>44551</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>45530</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>45289</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>44531.3575</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>45434.65854166666</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>44675</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30379,7 +30379,7 @@
         <v>44967.60165509259</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>44389</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45082.31421296296</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>45820.61684027778</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>45072</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>45537.42240740741</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>45821.59353009259</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>45821.37199074074</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>45519.52319444445</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45412.54541666667</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45376.70292824074</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>44865.600625</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>45387.24732638889</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>45387.2521875</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31207,7 +31207,7 @@
         <v>45554.7158912037</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>45103</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>44546.67222222222</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>45141.76530092592</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>45400.66995370371</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>45194</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>44908.49152777778</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>45471.40384259259</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31673,7 +31673,7 @@
         <v>44389</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31730,7 +31730,7 @@
         <v>45821.46135416667</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31792,7 +31792,7 @@
         <v>45821.46486111111</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>45707</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>45471.52878472222</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31968,7 +31968,7 @@
         <v>44970.51849537037</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32025,7 +32025,7 @@
         <v>45821.44521990741</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32087,7 +32087,7 @@
         <v>45148</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32144,7 +32144,7 @@
         <v>45194</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>45152.34586805556</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32263,7 +32263,7 @@
         <v>45218.488125</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>44866.79668981482</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>44175</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45538</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45189.38135416667</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>44577.81121527778</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32610,7 +32610,7 @@
         <v>45738.42981481482</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>45519.51627314815</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44900.36149305556</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>45099</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>44503</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>44553.35407407407</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>45594.63747685185</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>45586</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33081,7 +33081,7 @@
         <v>44951.5830324074</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33138,7 +33138,7 @@
         <v>45373.34383101852</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>45131</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33257,7 +33257,7 @@
         <v>45078.82620370371</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33314,7 +33314,7 @@
         <v>45068</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>45188</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33428,7 +33428,7 @@
         <v>44621.85737268518</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33485,7 +33485,7 @@
         <v>45218</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>45266.58394675926</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>45009.64217592592</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>44566</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33718,7 +33718,7 @@
         <v>45170</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33780,7 +33780,7 @@
         <v>45227.31859953704</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>45384</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>45575.55273148148</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>45575.5547337963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34018,7 +34018,7 @@
         <v>45575.55684027778</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>45714</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45667</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34194,7 +34194,7 @@
         <v>45667</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34256,7 +34256,7 @@
         <v>45642</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>45139.63480324074</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34375,7 +34375,7 @@
         <v>45091.39362268519</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45201</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34494,7 +34494,7 @@
         <v>45618.58962962963</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45538</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>45575.57104166667</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45257.48188657407</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>44420</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45265.64142361111</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>45685</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>45614.68083333333</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>44602.45162037037</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>45103</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>44431</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35131,7 +35131,7 @@
         <v>45119.46452546296</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>45511.39445601852</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>45348</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>44735.62539351852</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35369,7 +35369,7 @@
         <v>45729.65171296296</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35426,7 +35426,7 @@
         <v>45111</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>45138</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>45488.42258101852</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35602,7 +35602,7 @@
         <v>44950</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>45316</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>44883</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>45393.3562962963</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>45254.68105324074</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>45393.36060185185</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>45525.7374537037</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>45827.51862268519</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36078,7 +36078,7 @@
         <v>45177.33991898148</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>45251</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>45826.52024305556</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>45393.35787037037</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>45762.61817129629</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>45222</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44949</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44895</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>45107</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>44902</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>45744.32981481482</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>45519.52232638889</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>45107</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>45323</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36901,7 +36901,7 @@
         <v>45106</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>44990</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>45357.34521990741</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>45827.56939814815</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37139,7 +37139,7 @@
         <v>45827.51753472222</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>45827.51956018519</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
         <v>45554.71863425926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>44169</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>44822</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>45274</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>45769.98449074074</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>45072.42776620371</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37620,7 +37620,7 @@
         <v>45827.51628472222</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45523</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>45477.70315972222</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>45687</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>44438</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>45404.68190972223</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45252.78021990741</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45254</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>44577.83484953704</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>45077</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38215,7 +38215,7 @@
         <v>45077</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38277,7 +38277,7 @@
         <v>45077</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45736.308125</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>45095</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38453,7 +38453,7 @@
         <v>45571.71736111111</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>45575.56686342593</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45575.56820601852</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>45454.49679398148</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>44846</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>45719.52871527777</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>44916</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45832.76100694444</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>45832.76491898148</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38996,7 +38996,7 @@
         <v>45618</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>45832.49325231482</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>45832.51255787037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>45832.55810185185</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39244,7 +39244,7 @@
         <v>45170.45921296296</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>45832.72778935185</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>44594.84091435185</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39425,7 +39425,7 @@
         <v>45832.5902662037</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>45832.74418981482</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39549,7 +39549,7 @@
         <v>45645.3737962963</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39611,7 +39611,7 @@
         <v>45832.49579861111</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>45832.51028935185</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39735,7 +39735,7 @@
         <v>45835.68443287037</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>45546.68743055555</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45177.33091435185</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>45574.65189814815</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>45211</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45093.48221064815</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>44544</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>45769.66260416667</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>45838.46456018519</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>45838.46408564815</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>45265.49225694445</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
         <v>45516.4221412037</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45344.623125</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>44425.40297453704</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>44473.6343287037</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>45699.65424768518</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40687,7 +40687,7 @@
         <v>45546.46497685185</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40749,7 +40749,7 @@
         <v>45840</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>44484</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>45471.42659722222</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>44449</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40977,7 +40977,7 @@
         <v>45844.5775</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45845.49216435185</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41096,7 +41096,7 @@
         <v>44522</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41153,7 +41153,7 @@
         <v>45884.38858796296</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>45520.32887731482</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>45343.58587962963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45684.5790162037</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41386,7 +41386,7 @@
         <v>45134.68158564815</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>45237.67819444444</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>45887.56101851852</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45471.52072916667</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45729.76231481481</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45749</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>44978</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>45698</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>45698</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>44868.36924768519</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41976,7 +41976,7 @@
         <v>45844.57328703703</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42038,7 +42038,7 @@
         <v>45844.57527777777</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45645</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45667</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45884</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45845.4855787037</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>44124</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45845.76005787037</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>45530</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>45845.75200231482</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>44865.87770833333</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>45189</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>44990</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>45889.66935185185</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42794,7 +42794,7 @@
         <v>45889.67577546297</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42856,7 +42856,7 @@
         <v>45889.67290509259</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45372.40246527778</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>44946</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45400.6709837963</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45173</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45079</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45079</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45462</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>44791</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>44902</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45575.53331018519</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45575.54489583334</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>45813.68209490741</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>44728</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45694</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45399.56596064815</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43808,7 +43808,7 @@
         <v>45895.49994212963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>45895.47704861111</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
         <v>45895.4790625</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45895.48394675926</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44056,7 +44056,7 @@
         <v>45099.27354166667</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>45685</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>44308</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
         <v>45670.69458333333</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45895.48927083334</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45537.64621527777</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>45854</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45441.48670138889</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44532,7 +44532,7 @@
         <v>45586.55451388889</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44589,7 +44589,7 @@
         <v>44306.6371412037</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44646,7 +44646,7 @@
         <v>45097.39893518519</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45854</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44760,7 +44760,7 @@
         <v>45548</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>45548</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>45553</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>45646</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45008,7 +45008,7 @@
         <v>45440</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45065,7 +45065,7 @@
         <v>45729.65061342593</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45122,7 +45122,7 @@
         <v>45898.37138888889</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>45328</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>45646.63839120371</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45298,7 +45298,7 @@
         <v>45341.56577546296</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>45008</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>45899.38057870371</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45479,7 +45479,7 @@
         <v>45113</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>44227</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45593,7 +45593,7 @@
         <v>45565</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>45860.3857175926</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>45714.31533564815</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45764,7 +45764,7 @@
         <v>45860.36222222223</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>45903.37475694445</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>44970</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45940,7 +45940,7 @@
         <v>45587</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>45902.3406712963</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>45229</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46111,7 +46111,7 @@
         <v>44231</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>45095</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46225,7 +46225,7 @@
         <v>45377.48265046296</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46282,7 +46282,7 @@
         <v>45905.89236111111</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46344,7 +46344,7 @@
         <v>45905.89329861111</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45538.34460648148</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>44342.39703703704</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45905.89143518519</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>44355</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45664</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46711,7 +46711,7 @@
         <v>45736</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46768,7 +46768,7 @@
         <v>44511</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>45203.510625</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>45229.66262731481</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>45534.54032407407</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>45274</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
         <v>45280</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45628.94579861111</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45831</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>44602.45490740741</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45575.65721064815</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>45574.65087962963</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47420,7 +47420,7 @@
         <v>45085</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>44267</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>44890.46174768519</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>45334</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47648,7 +47648,7 @@
         <v>45516.59447916667</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
         <v>44276</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47762,7 +47762,7 @@
         <v>45738.43714120371</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47819,7 +47819,7 @@
         <v>44753</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47876,7 +47876,7 @@
         <v>45831</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47933,7 +47933,7 @@
         <v>45229</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45912.63359953704</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45870</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48109,7 +48109,7 @@
         <v>45912.63751157407</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48171,7 +48171,7 @@
         <v>45565.40700231482</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48228,7 +48228,7 @@
         <v>45870</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48285,7 +48285,7 @@
         <v>45614.5968287037</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45538.34796296297</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45870</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45915.49238425926</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48518,7 +48518,7 @@
         <v>45251.696875</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48575,7 +48575,7 @@
         <v>45303</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>45471.38995370371</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>45915.54983796296</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48746,7 +48746,7 @@
         <v>45643</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48803,7 +48803,7 @@
         <v>45749</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48860,7 +48860,7 @@
         <v>44161</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>44734.64337962963</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48979,7 +48979,7 @@
         <v>44906.73321759259</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49036,7 +49036,7 @@
         <v>45047.7181712963</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>44424.61709490741</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>45912.63451388889</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45870</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45568.62625</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49331,7 +49331,7 @@
         <v>45569.35209490741</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49388,7 +49388,7 @@
         <v>45915.54439814815</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49445,7 +49445,7 @@
         <v>44984</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49502,7 +49502,7 @@
         <v>45273</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49559,7 +49559,7 @@
         <v>45394.51289351852</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>45618.59456018519</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49678,7 +49678,7 @@
         <v>45874.40503472222</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49740,7 +49740,7 @@
         <v>45119</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>44946.54424768518</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>44236</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>45917.31780092593</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49998,7 +49998,7 @@
         <v>45618.58622685185</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50060,7 +50060,7 @@
         <v>45877.64431712963</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50122,7 +50122,7 @@
         <v>45877.63989583333</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45877.64144675926</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45877.64605324074</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45653.53664351852</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50365,7 +50365,7 @@
         <v>45139.64328703703</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45618.59219907408</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45877.65075231482</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45877.64847222222</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45877.64776620371</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>44809</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>45876.59166666667</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50789,7 +50789,7 @@
         <v>45877.64230324074</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50851,7 +50851,7 @@
         <v>45698</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>45264.38084490741</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50965,7 +50965,7 @@
         <v>45880</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51022,7 +51022,7 @@
         <v>45881.42791666667</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51079,7 +51079,7 @@
         <v>45880</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45880.46056712963</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51193,7 +51193,7 @@
         <v>45880.28673611111</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51250,7 +51250,7 @@
         <v>45881.43759259259</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51307,7 +51307,7 @@
         <v>45881.59550925926</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51364,7 +51364,7 @@
         <v>45880.3172337963</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51421,7 +51421,7 @@
         <v>45925.56173611111</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51483,7 +51483,7 @@
         <v>45925.30702546296</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51540,7 +51540,7 @@
         <v>45925.70290509259</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -567,7 +567,7 @@
         <v>45615</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         <v>45252</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>45905.90649305555</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>44850.83328703704</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44375</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>45810.54824074074</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>45905.90519675926</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>44406</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45905.89554398148</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>45568.63905092593</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>45099</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44320</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45138</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45888.67560185185</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>44484</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45905.83755787037</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45905.90789351852</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>45099</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>45616.38605324074</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>45218</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>45888.67765046296</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>44472</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>44789</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>45905.88938657408</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44280</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>45021</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>45138</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45670</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>45615</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>44375</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>44512</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44713.59363425926</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>44679</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44320</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>45698.46697916667</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>45250</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>44949</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>45575.54934027778</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>45281</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>45478.39592592593</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>45645</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>45618.58876157407</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>45922.49990740741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>45518</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>45881.42446759259</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45928</v>
+        <v>45929<